--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-54.4699999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.74794e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.813</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4543801584321411</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9215050861285461</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.820639936678351</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.66907044972603</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-65.70931508433515</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = -2.216x + 7974.761</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.640397004616299e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3001.585328281391</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000001899757e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8140293700987243</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-77.71000000000004</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.77274e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.069</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1037725819299271</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9180530997660872</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.662100870717262</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22.8034049699186</v>
+      </c>
+      <c r="K3" t="n">
+        <v>68.25430857777698</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 2.507x + -4105.444</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.406035629773169e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2874.875828182493</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000067825e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.814521829023492</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-55.57000000000016</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.78196e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.193</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2950387924040814</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.152452908789304</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.227845063926751</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.61479762259942</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-33.53220000703727</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = -0.663x + 3667.351</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.713748635193583e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2824.137356664117</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000001881e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8146754569102467</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-46.97000000000025</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.78706e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.27500000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.397687786448148</v>
+      </c>
+      <c r="G5" t="n">
+        <v>730.2180776780416</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.242644028281791</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.393072511955302</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28.82280802736893</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-66.6106641159671</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = -2.312x + 7557.655</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.798274215678066e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2788.772242124763</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000615846e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8147582496974379</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-227.0300000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.92236e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.755</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4752620989306149</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.145349964446096</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.513414921905881</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.239048494630296</v>
+      </c>
+      <c r="J6" t="n">
+        <v>245.8475369518642</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.00077382004689</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 28.647x + -65630.981</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>8.545114213889972e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2761.7199542041</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000001421993e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8148045760751251</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-187.1900000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.90902e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.917</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3492574154833302</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.288621630941714</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.438124475179138</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.115440013575289</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.72752814586424</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 25.200x + -56895.362</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.847866497245891e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2733.489103789219</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000706327e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8148714646566978</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-192.27</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.90448e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.009</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06576810302047548</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6311631942841991</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.336571488270056</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.958910848646772</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14.29256977800766</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.3188431259309</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 21.354x + -47327.054</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.735499326061547e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2707.103229311077</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000070395e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8149580221425988</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-171.2199999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.89808e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.083</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4057434292168398</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.201337701024349</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.11348226407737</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.502531234474674</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.42226254303172</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 22.212x + -48963.474</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.43947090069047e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2683.432122226611</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000034529e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8150450636151971</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-161.4899999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.896299999999999e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.14700000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4170430816817713</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.104176681605816</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.184520022376841</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.475583762612138</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.36773313344881</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 21.751x + -47516.066</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>6.328699988977746e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2662.023493568865</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000004330382e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8151516295079959</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-159.2599999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.89257e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.194</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3267231200034272</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.167394342512154</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.087083520332675</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.461072396555181</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.39339591616216</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 21.966x + -47657.550</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.709030642352584e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2641.899796822844</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000022788e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8152982860708917</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-165.9400000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.88937e-08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.246</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.07923899417197085</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.768895196648223</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.867679425326893</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.376577545247151</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.14813825231388</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 20.074x + -43038.867</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.241992900452892e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2623.157901990913</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000379033e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8154835925613381</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-160.2200000000003</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.88594e-08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.271</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3396301654230586</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.311910016073335</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.490980897022942</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.529336409683285</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.51984458494603</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 23.087x + -49505.182</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.842324758274235e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2604.469220382614</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000140426e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8156713198400521</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-167.8699999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.88173e-08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.32299999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1615815026312842</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8175045119208715</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.901732320712659</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.24644200621972</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.30288265207135</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 21.228x + -44963.832</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.030577065505473e-07</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2584.732100695554</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000003581505e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8159098350356051</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-57.24000000000024</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.84767e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.633</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3950762642919339</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.06886658176147</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.911590063092414</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19.36734462883731</v>
+      </c>
+      <c r="K15" t="n">
+        <v>38.01064789776142</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 0.782x + 243.587</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.126298726775029e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2563.776064966605</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000002325532e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8161456690907986</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-50.32999999999993</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.84863e-08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.70399999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.340441269891429</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.868853761696838</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.396633520415679</v>
+      </c>
+      <c r="J16" t="n">
+        <v>17.88554306623543</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-44.80258112615174</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = -0.993x + 4049.962</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.236013066885747e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2542.982383236801</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000321449e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8163903954638848</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-96.28999999999996</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.854860000000001e-08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.622</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3350962199162855</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.011986509205258</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.14446529658988</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>18.04726569633489</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.32949883650566</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.071x + -19840.830</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>4.1592652297334e-10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2522.901797562265</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000049537e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8166355055745373</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-22.11999999999989</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.841669999999999e-08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.845</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5057244567015815</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.533178215643016</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.171655739701199</v>
+      </c>
+      <c r="J18" t="n">
+        <v>14.46562109079477</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-83.05180615951504</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = -8.206x + 19519.920</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.126577163053326e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2500.26313363378</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.00000000036226e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8168914354971314</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-22.56999999999994</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.840150000000001e-08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.911</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.03489195936144598</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.769939064847059</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.977302990787715</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16.7810493556606</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-81.85952438131247</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = -6.991x + 16628.510</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.262996572198026e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2478.894211949943</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000344816e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8171500330217488</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-29.53999999999996</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.8376e-08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.94199999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2196242105599186</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.949549549663012</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.295906355342668</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16.65922768774281</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-80.39838400769001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = -5.911x + 14239.270</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.226941585207567e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2457.371874773199</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000338555e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8174073760261732</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-44.36000000000013</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6.84333e-08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.949</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1186803508687396</v>
+      </c>
+      <c r="G21" t="n">
+        <v>465.0771447642225</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.216270597819965</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.576697513857683</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-63.09955057614199</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = -1.971x + 5873.204</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.197617281222268e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2435.480744332806</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000135527e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8176774955586625</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-41.73000000000002</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.84467e-08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.998</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1275635332353491</v>
+      </c>
+      <c r="G22" t="n">
+        <v>345.3732642513999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.273493165225116</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.824408559035502</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-69.62958949863966</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = -2.693x + 7324.253</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.988510286001275e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2413.714908084446</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000435508e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8179412466224817</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1973.24</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.807770000000001e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.313</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04550344814309736</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5580797666755246</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.418663878511529</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.766487141873533</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.40332360891977</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.79996252394287</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.988x + -33913.173</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.335479054312013e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3724.855063932422</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000185512e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.811194722778607</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-965.1299999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.74003e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.084</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3245242578422265</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8567645075295822</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.780614927576904</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.002013520060604</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28.80511722086773</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.39422175177619</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 21.973x + -59676.987</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.15787692821595e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3272.142500169624</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000007171e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8123093237459992</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-491.8200000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.617129999999999e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.651</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3970203475726921</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9920027205718991</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.88447485836918</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.574334311713713</v>
+      </c>
+      <c r="J4" t="n">
+        <v>70.40106069079212</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.30846062536317</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 33.862x + -88793.058</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.535052391839412e-13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3149.705858993187</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000011272e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8125806612880909</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-325.9099999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.55808e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.285</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.222679911297436</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8959392974463951</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.153423847076427</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.626900353123343</v>
+      </c>
+      <c r="J5" t="n">
+        <v>216.2076776011839</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.14230204396958</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 30.832x + -78445.743</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.007370219226665e-13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3082.660736637521</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.00000000001852e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8127328977220692</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-218.8099999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.53113e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.646</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4112659140558896</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.289500538285351</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.050059766324692</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.326048107358549</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.86450806269114</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 26.818x + -66733.285</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.136330487606972e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3026.970313126165</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000149396e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8128842293572777</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-164.5100000000002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.51838e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.913</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08243634189666081</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7861537736643299</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.134458874961983</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.302076675158259</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.64282388502379</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.047x + -40833.412</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.773676998252171e-12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2975.443512917976</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000152931e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8130514773053217</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-124.8099999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.51042e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.09699999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1230264301439157</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9809079507791082</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.129788354064586</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.80932746228655</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.03898339160779</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.520x + -26478.520</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.706624408938204e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2928.207222118213</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000125036e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8132137327329829</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-83.80999999999995</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.50668e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.259</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3359268731767412</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.248549101683565</v>
+      </c>
+      <c r="H9" t="n">
+        <v>255.8684253981218</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.390230129602131</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.97194545176075</v>
+      </c>
+      <c r="K9" t="n">
+        <v>77.96061947910844</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 4.689x + -9327.409</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.010949242543768e-14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2884.750338449863</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.00000000026676e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8133796058844598</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-58.71000000000004</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.50538e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.387</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4156084745312651</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.511120816133291</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.44365165026855</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19.01463507159734</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-24.75953327825828</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = -0.461x + 3264.069</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.975261471801174e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2844.982276807901</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000002224216e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8135550389336141</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-38.94000000000005</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.50517e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.497</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4801716831424558</v>
+      </c>
+      <c r="G11" t="n">
+        <v>233.9765723461011</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.267426904202037</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.625076270868216</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12.35932724304997</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-78.31701812655305</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = -4.836x + 13687.387</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.682352462606695e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2807.938141447114</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000023074e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8137422252644344</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-635.7600000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.68646e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.277</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5224662395404657</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8596903279918767</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.779849853921197</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.451980227520143</v>
+      </c>
+      <c r="J2" t="n">
+        <v>49.58616221477614</v>
+      </c>
+      <c r="K2" t="n">
+        <v>88.10408525269288</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 30.210x + -78594.548</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.503713272876611e-14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3100.80941084509</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000923e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8127349193393201</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-255.6599999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.56379e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.631</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2299875267411905</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9765537385766515</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.435031411780813</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.15973285987229</v>
+      </c>
+      <c r="J3" t="n">
+        <v>300.4750651305349</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.00266796165695</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 28.675x + -70461.339</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.232455212980571e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2978.445253380965</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000002362421e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8130220748634609</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-144.7199999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.53195e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.038</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2186282747559263</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.006599740111411</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.01788693361006</v>
+      </c>
+      <c r="I4" t="n">
+        <v>454.9545991151126</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24.2013184924612</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.09871374465523</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.664x + -34260.851</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.334338909097358e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2926.702183851483</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000626478e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8131284198321581</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-83.1899999999996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.51826e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.254</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2132916421850715</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.074112447211002</v>
+      </c>
+      <c r="H5" t="n">
+        <v>701.332437404939</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.768126543859957</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23.27308236530344</v>
+      </c>
+      <c r="K5" t="n">
+        <v>78.10228108292959</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 4.746x + -9528.855</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.341261710476093e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2889.113656267828</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000459937e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8132293587807676</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-46.30999999999995</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.51337e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.405</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.150290940774579</v>
+      </c>
+      <c r="G6" t="n">
+        <v>997.7145411517471</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.110722426395651</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.957266499651763</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21.91682704374759</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-69.68331444941018</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = -2.701x + 8611.959</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.121758090205614e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2856.524373585025</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000139599e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8133959097042963</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-18.26999999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.51319e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.51600000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>963.9600873800287</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.056855734435787</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.375406652913493</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.566344750190809</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15.23016660033596</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-84.17006358102275</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = -9.794x + 25634.435</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.727928214626339e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2825.827724083491</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000130665e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.813588395598457</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-15.23999999999978</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.512e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="F8" t="n">
+        <v>859.7398174529048</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9450573178502284</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.691040537328041</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.82080385896931</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.46936484995584</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-84.17881511505529</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = -9.809x + 25320.983</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.024607990855834e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2796.404053660201</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000002077736e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8138108417260976</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4.259999999999764</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.512470000000001e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.68899999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2159452420063499</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.192938989066114</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.363034497360235</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.954927296358205</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.604128231278341</v>
+      </c>
+      <c r="K9" t="n">
+        <v>82.72326703628727</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 7.831x + -17405.608</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.457729395873112e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2767.214036768366</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000059899e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8140396719454193</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>13.22000000000025</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.51447e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.785</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1539813821686699</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7247079262969177</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.738583694049607</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.333325695998801</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.38893480456041</v>
+      </c>
+      <c r="K10" t="n">
+        <v>82.2923416967986</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 7.389x + -16172.143</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.79788051483419e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2738.675985261965</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000003111544e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8142978253090731</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>28.91000000000031</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.5148e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.87</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0570491373193269</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.689910969529472</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.677377225359953</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.386536921154347</v>
+      </c>
+      <c r="J11" t="n">
+        <v>17.29287226173624</v>
+      </c>
+      <c r="K11" t="n">
+        <v>82.32897058829273</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 7.424x + -16097.178</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.925899905588307e-14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2710.199659339391</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000013651e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.814566077357348</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>48.98000000000002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.514770000000001e-08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.919</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6926409794846983</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.378933562063089</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.876763641746646</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.020939149231372</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>83.32285369878258</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 8.542x + -18538.407</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.698792079256109e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2682.979306390135</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000019037e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8148507923077259</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>44.5300000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.51546e-08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-85.005</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.08430795675470899</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8693581035100446</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.892837839986041</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.346879071618357</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12.68698203670818</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82.36623349893193</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 7.461x + -15863.743</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.294911995502573e-07</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2655.560599979192</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000029963e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8151318643277632</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>68.44000000000005</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.515700000000001e-08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-85.078</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4538014456128008</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.270728528200539</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.588698396316813</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.264117793118986</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>83.07434174599595</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 8.233x + -17467.628</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.02898540932662e-14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2628.621820032761</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000496e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.815424033264312</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>67.47000000000025</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.51468e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-85.13800000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2807208115207647</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9320509599010536</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.562637252825413</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.090386287698845</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>82.72754687888354</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 7.836x + -16404.743</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.129029427930446e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2602.193960973588</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.00000000008681e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8157111145780713</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83.53999999999996</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.51408e-08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-85.209</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4671266925861034</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.507284691641977</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.600534237754687</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.478308216028103</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>83.11804821964103</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 8.285x + -17247.905</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.467782092261909e-07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2575.984614183384</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000003920471e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8160036355184819</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>77.29999999999995</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.516190000000001e-08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.26900000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1924618333284086</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8569416684325321</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.891929918773218</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.760301571238977</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.464175592813915</v>
+      </c>
+      <c r="K17" t="n">
+        <v>82.54717801170752</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 7.644x + -15655.706</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.655215230294291e-07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2549.524310452643</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000001989374e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8163055244018254</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>84.45000000000027</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.514720000000001e-08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.339</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2192511755180279</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.069544199669198</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.262563459775259</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.933499878697754</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>82.53719370838013</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 7.634x + -15475.953</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.294975845472857e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2522.962256241677</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000003885e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8166031456178153</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>82.81999999999994</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.516729999999999e-08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.413</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.01077199133467825</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5623969768540781</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.925911354952493</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.351554236717937</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>81.78827322698132</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 6.929x + -13788.508</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>7.333281535670074e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2496.178754784095</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000080488e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8169071089293406</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>113.4400000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.51763e-08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.47799999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3230803326864015</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.11745834705278</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.710850112336614</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.586149634659372</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>82.94100422387126</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 8.076x + -16107.919</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.963439150436547e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2469.600454719319</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000008409e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8172039036849513</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>110.6099999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6.517709999999999e-08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.536</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4063705285693058</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.753871161041425</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.212174743685456</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.686132008045209</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>82.68857782797556</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 7.794x + -15340.878</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.457985090775765e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2442.754711392271</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000080993e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.817526089437753</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>110.1399999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.51972e-08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.59399999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2336070175640058</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.800136050538975</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.651468209523168</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.352616131184802</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>82.33801949786105</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 7.433x + -14424.350</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>7.38743871202838e-12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2415.841176766926</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.0000000000519e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8178419656413997</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1809.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.869109999999999e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.56399999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.368670535899603</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.018778616827501</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.104693583118042</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.079354626743005</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.73429738230535</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.20881726625123</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.931x + -37181.958</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.489649772884224e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3707.894080356654</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000006821e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8109729998283166</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-796.6599999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.773579999999999e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.58</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1428075333806495</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.112463845473705</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.433034428350365</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.253716394962943</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.92582888887071</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.68078154358194</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 24.691x + -66059.701</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.517787105115126e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3218.210291151423</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001999e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8122060551240007</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-441.6199999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.68213e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.824</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3060606607977521</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.26235226147249</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.621115819462565</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.907755154428532</v>
+      </c>
+      <c r="J4" t="n">
+        <v>114.5159154914054</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.24301206018693</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 32.600x + -83852.576</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.276089341358065e-13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3095.380351498084</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000005625e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8124861103466645</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-294.9400000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.6444e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.35599999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1474345053483577</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9258873759680991</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.281035562291068</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.711910285079546</v>
+      </c>
+      <c r="J5" t="n">
+        <v>248.6927140617362</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.06285369564924</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 29.566x + -74013.201</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.01561900948159e-13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3033.146864149631</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000004289e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8126131828785502</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-217.5900000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.62592e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.666</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1076303433884637</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7515393588475775</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.036844956890463</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.904420255761019</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.46376315789631</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 22.576x + -55004.404</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.5955133763302e-13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2983.824621989874</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000004206e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8127358872415184</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-144.8800000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.61719e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.893</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4700390066022139</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.407290598965406</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.87943595928412</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37.20917935819942</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.66071576043031</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.139x + -40656.913</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.415628643110699e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2938.874907182456</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000029043e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8128738039469225</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-111.3400000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.61369e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.071</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.339361609702095</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.291496295870567</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.824557720328762</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.60731814421631</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.41402179195856</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.225x + -23038.004</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.368461865905526e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2897.045874698175</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000001490659e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8130346229438706</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-88.4699999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.6136e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.217</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2804282024296779</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.015041879947511</v>
+      </c>
+      <c r="H9" t="n">
+        <v>775.7964998472776</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.818694001047188</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23.11977899084852</v>
+      </c>
+      <c r="K9" t="n">
+        <v>79.19560156564935</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 5.240x + -10650.117</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.976068441226693e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2857.294100960475</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000002348099e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8132137836730984</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-56.40000000000009</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.61349e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.33799999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4938244097451646</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.385171385396958</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.376952961017122</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.40035351755466</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-21.92849277603647</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = -0.403x + 3080.166</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.647331413136195e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2820.477322753758</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000497801e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8134093161771635</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-40.61999999999989</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.61646e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.455</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3549174609987874</v>
+      </c>
+      <c r="G11" t="n">
+        <v>569.5643109027702</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.156861594970937</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.68174851275586</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.14222002904654</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-75.28400969379423</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = -3.807x + 11047.615</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.453884835213759e-13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2785.960762766516</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000097333e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8136157439402472</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-962.1799999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.923909999999999e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.149</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02004990114195903</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8035893550285281</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.057892972621946</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.016597909889322</v>
+      </c>
+      <c r="J2" t="n">
+        <v>29.87246431620744</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.26965780233698</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 20.969x + -54464.963</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.826779095373975e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3112.206535620435</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000068123e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8126956674502752</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-370.8200000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.73327e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.215</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2966307433737653</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.118247964962843</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.424259341866376</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.820198313833394</v>
+      </c>
+      <c r="J3" t="n">
+        <v>144.6082177062939</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.25526778769634</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 32.829x + -80669.629</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.514337441707183e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2953.37503172122</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.0000000037225e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8130326148565623</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-214.6599999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.688940000000001e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.748</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2816896166728754</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.095836514455185</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.393509347176842</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.351802816360049</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.76978611891255</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 25.678x + -61257.100</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.668005610458705e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2898.741819339024</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000018462e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8131080792903281</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-134.8800000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.67038e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.01000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6222679677783994</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.606568660345036</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.024282822529965</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38.47842985017402</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.51862535185441</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.438x + -37930.709</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.935896412075662e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2862.201244899916</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000016909e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8131771093337712</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-109.0799999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.66288e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.17700000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1964211091759708</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8676938478135484</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.399829657718957</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.04510424740899</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.72447086690875</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.093x + -19817.841</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.94204070804713e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2829.966957799847</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000001365048e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.813283468521506</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-75.75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.66054e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.309</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3621063804832538</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.059122115772579</v>
+      </c>
+      <c r="H7" t="n">
+        <v>308.5689945119358</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.803049152916322</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23.09022103703036</v>
+      </c>
+      <c r="K7" t="n">
+        <v>73.19361397958819</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 3.311x + -5842.658</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.830260427125439e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2800.232420436188</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000016682e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.813419236779981</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-55.01000000000022</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.65822e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.413</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2268032068809779</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.186848658609656</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.813202662031709</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.36606636500764</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-40.3947259605872</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = -0.851x + 4033.184</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.189804074923447e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2772.05319856209</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000106446e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8135655042494276</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-38.23000000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.65943e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.501</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2826317231400974</v>
+      </c>
+      <c r="G9" t="n">
+        <v>109.2245808686943</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.963253499786657</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.718578786218772</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.01638682371835</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-77.34308860832034</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = -4.453x + 12418.750</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>361.9679600828741</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6900.748144565289</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.211874841429044e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.5000563328564563</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-21.71000000000004</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.66098e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.58</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2315372922585823</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.08247889450443</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.978139712027799</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.59286806384119</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-82.75673564432105</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = -7.868x + 20229.592</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>359.2523461034974</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6834.244800307194</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.217394013992102e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.5001064745672358</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-4.159999999999854</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.66092e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.649</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.299504293409823</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.436665893629074</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.433580754824138</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11.81036933400633</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-85.45352960590004</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = -12.576x + 30999.364</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>357.2408689988711</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6775.33087665479</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.223676434887456e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.50017299514923</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-2.279999999999745</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.66359e-08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.724</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8551203760470256</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.138101622679569</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.392742334305396</v>
+      </c>
+      <c r="J12" t="n">
+        <v>18.61633231269152</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-84.77772390229033</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = -10.941x + 26805.845</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.022873543275556e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2673.595039786875</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000125491e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.814220548455625</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6.839999999999691</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.66293e-08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.788</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3556182464170944</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9013461880111284</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.06800882454366</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.006150566351298</v>
+      </c>
+      <c r="J13" t="n">
+        <v>15.56188178462839</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82.6544099938159</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 7.757x + -16552.665</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>4.55369299566428e-14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2651.228810142732</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000079327e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.814409419532958</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.450000000000273</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.66455e-08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.834</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.09067411212974082</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7301172327593519</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.834602953475233</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.661961976684862</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16.93992091927861</v>
+      </c>
+      <c r="K14" t="n">
+        <v>82.44241758664617</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 7.537x + -15918.011</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.841104674228749e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2629.495411274605</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000677394e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8145926991059536</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>27.71000000000004</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.66379e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.90000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6009831210715595</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.29942970736833</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.349827811549894</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.20014064547841</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>83.03310516837367</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 8.183x + -17260.476</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.299561483160774e-12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2608.163674743105</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000339211e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8147965180180896</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>22.32999999999993</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.665789999999999e-08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.953</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.06389166504155996</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6513750290726031</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.893547474470874</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.477157933901059</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16.06042716245127</v>
+      </c>
+      <c r="K16" t="n">
+        <v>82.60768981812728</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 7.708x + -16043.517</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.511844908860799e-14</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2586.717452900827</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000001428e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8149999008664018</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>33.84000000000015</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.66758e-08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.01600000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1377992568548741</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8762971873701927</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.998365500248114</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.513496791042947</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14.62220492627065</v>
+      </c>
+      <c r="K17" t="n">
+        <v>82.63848551794553</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 7.740x + -15988.568</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>4.959987999328106e-15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2565.091971097781</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000049384e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8152138345291587</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>29.68999999999983</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.66753e-08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.06399999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.02655801514781532</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7082250939778825</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.538852989939429</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.165731556708198</v>
+      </c>
+      <c r="J18" t="n">
+        <v>15.0133880260605</v>
+      </c>
+      <c r="K18" t="n">
+        <v>82.26139441669933</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 7.359x + -15020.971</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.980759872087457e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2543.337884805379</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000470609e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8154361702375132</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>47.94000000000005</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.66815e-08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.13</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2564876377721994</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.311710739826169</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.264759311502441</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.321101042772916</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10.17954756538399</v>
+      </c>
+      <c r="K19" t="n">
+        <v>82.65286823427783</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 7.756x + -15768.304</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.488568489960556e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2521.96677157164</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000001431337e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8156650072255058</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56.62000000000012</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.669580000000001e-08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.191</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4041347779387621</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9885907263208565</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.03488031465544</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.521479353136618</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9.462410376914907</v>
+      </c>
+      <c r="K20" t="n">
+        <v>82.6918934023077</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 7.797x + -15725.084</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.700793949221654e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2499.991973103609</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000115598e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8159059118651605</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>63.18000000000006</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6.66883e-08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.236</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6769081605682188</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.081698154366681</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.477570224587692</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.420716546159114</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>82.9750707414034</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 8.115x + -16279.860</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.322849944898881e-07</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2478.3568299565</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000122447e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8161470324889236</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>62.73000000000002</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.670460000000001e-08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.282</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3236187105159638</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.006439306796309</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.934430624337532</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.735956474553339</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.138305574860983</v>
+      </c>
+      <c r="K22" t="n">
+        <v>82.74285413621382</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 7.853x + -15583.050</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.226996704798019e-06</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2456.830313811909</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000651405e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8163970762775339</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1673.63</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.91829e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-78.08799999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1507859628811743</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6177702821860518</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.414045305593257</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.873604743728017</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.98246298996102</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.48188522029676</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.655x + -38450.908</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.07231523396653e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3614.404843408442</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000011803e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8117315975817562</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-679.6599999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.82448e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.959</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.366529369684826</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.18735328371593</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.421192071913405</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.212501709435249</v>
+      </c>
+      <c r="J3" t="n">
+        <v>51.19744776468411</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.88601646475465</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 27.091x + -70861.417</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.497936375118675e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3136.862093895567</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000032086e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.81292692789788</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-415.0699999999997</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.7658e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.965</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1582738692751219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8906564995293111</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.941097417989595</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.833620391452242</v>
+      </c>
+      <c r="J4" t="n">
+        <v>104.1681940172663</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.11393833010669</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 30.368x + -76005.015</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.42339174985863e-15</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3023.552290229102</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8131766875636037</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-280.1599999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.74376e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.40900000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2857586519309162</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.202547601720134</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.466333956844432</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.08227940907242</v>
+      </c>
+      <c r="J5" t="n">
+        <v>232.4892354275298</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.03663367816085</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 29.171x + -71552.841</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.143507990293474e-14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2967.407414415672</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8132854401415903</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-204.9200000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.73161e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.669</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3432175223911441</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.439450354451037</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.979532990486014</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.266523352283243</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.75455022508199</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 25.503x + -61388.757</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.029002508925277e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2924.041814009404</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000067729e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8133819292230474</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-158.3999999999996</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.72919e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.875</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3014830486555876</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.317913560757482</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.818844475697312</v>
+      </c>
+      <c r="I7" t="n">
+        <v>388.6483740889115</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.7077924193736</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.82365294782925</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.020x + -42135.531</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.147892250672547e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2884.832626894152</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000131622e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8134824101818988</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-136.6700000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.72747e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.03100000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.189237962850408</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6481616128829926</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.810399884598161</v>
+      </c>
+      <c r="I8" t="n">
+        <v>542.7333257581946</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.17988428401341</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.56209972795442</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 12.885x + -29135.044</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.542677087333395e-12</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2846.94606088787</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000059907e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.813631498832315</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-109.2099999999996</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.73049e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.164</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7507441875963021</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.998280013819313</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.33630994868374</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.4304374773666</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 8.683x + -18746.466</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.620224228637031e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2810.683657324257</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000002254781e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8137990104894609</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-78.17000000000007</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.735029999999999e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.28</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.339959095832626</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.089457285798444</v>
+      </c>
+      <c r="H10" t="n">
+        <v>685.2920039241777</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.53124288802452</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.131877218872</v>
+      </c>
+      <c r="K10" t="n">
+        <v>76.36115780742992</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 4.121x + -7718.772</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.085343435594107e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2776.174489074143</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000144727e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8139823526587866</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-64.16000000000031</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.73891e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.383</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1080129742320917</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8061938340154953</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.199025840572133</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19.64202469201001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>56.86706397072344</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 1.532x + -1625.862</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22764211002573e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2742.974615010593</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000042788e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8141579711116839</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-664.3099999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.92013e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.962</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.149019776143625</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9020912942264847</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.922770461998279</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.947341720341467</v>
+      </c>
+      <c r="J2" t="n">
+        <v>51.69585794131459</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.82536700448766</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 26.335x + -68198.247</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.829881893687128e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3091.679560445009</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000000209e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8142497834061933</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-306.04</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.80859e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.355</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2568897387725408</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9268745436661409</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.452055849352705</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.138375679620622</v>
+      </c>
+      <c r="J3" t="n">
+        <v>217.198129114172</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.13974500407826</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 30.789x + -74739.214</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.233381463419685e-15</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2924.594950167621</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000826e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8148335769186714</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-202.2400000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.778620000000001e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.776</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2356139946578558</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8521226995791511</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.170401919061648</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.295420168987744</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.44616200928361</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 22.420x + -52595.860</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.081375275611036e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2867.690734657103</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000172454e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8149709646965708</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-131.3400000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.76946e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.989</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5720529013685448</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.492957437111186</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.110204491806964</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>39.02498526963041</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.36506850289545</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.741x + -35860.551</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.271012226955511e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2831.573809693018</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000161538e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8150196790466799</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-101.1299999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.76566e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.14700000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3254002834221367</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.169477700922569</v>
+      </c>
+      <c r="H6" t="n">
+        <v>597.1456948160962</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.580254778789731</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.08332207557138</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.45830143272448</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 8.720x + -18705.004</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.250746024137434e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2800.137047970031</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000051283e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8150958478252835</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-84.78999999999996</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.76498e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.256</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.335790419329053</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.015795867225263</v>
+      </c>
+      <c r="H7" t="n">
+        <v>825.8650751434966</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.528706184254155</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23.80400877783512</v>
+      </c>
+      <c r="K7" t="n">
+        <v>79.02687767896758</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 5.157x + -10140.514</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.161438124980658e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2770.184456181625</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000070569e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8151890374926833</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-63.07999999999993</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.7673e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.35599999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3752798538672363</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9513848585906586</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.639053780187206</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.54241683501726</v>
+      </c>
+      <c r="K8" t="n">
+        <v>49.39061239768655</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 1.166x + -720.876</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.994395494709667e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2742.295703597552</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000136758e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8153074815972636</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-45.96000000000004</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.76783e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.43300000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4530159373364709</v>
+      </c>
+      <c r="G9" t="n">
+        <v>841.1356626291577</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.388960142340645</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.741530698407517</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.06123553208269</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-71.43905883096647</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = -2.978x + 8953.916</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.162018812113588e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2715.893592132777</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000123253e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8154335627502167</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-45.44999999999982</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.77146e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.505</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1725916255981519</v>
+      </c>
+      <c r="G10" t="n">
+        <v>870.6151578699885</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.712578809096599</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.283714745821711</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.94923716760701</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-66.9712138136609</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = -2.353x + 7306.178</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>351.7880185803672</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6799.144643573309</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.23751993603162e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.5000346600109846</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-19.65999999999985</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.77324e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.578</v>
+      </c>
+      <c r="F11" t="n">
+        <v>998.4767946535482</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.12038720749781</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.513404792485672</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.845466429092866</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15.87043411487534</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-83.93837649205827</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = -9.417x + 23491.018</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>346.1510907044591</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6714.992890909984</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.238171565523057e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.5000167426251596</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-33.17000000000007</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.77558e-08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.626</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.03657034054935201</v>
+      </c>
+      <c r="G12" t="n">
+        <v>148.9019984030941</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.392727779805485</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.769887471428</v>
+      </c>
+      <c r="J12" t="n">
+        <v>18.38891638791599</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-77.73337620723176</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = -4.599x + 12203.160</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>344.4505887722594</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6670.094166821037</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.244512812326237e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.5000455978319578</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-14.65000000000009</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.77394e-08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.694</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1239.616648331558</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.732800894764317</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.591674627416158</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.459706020377286</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18.40495000334692</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-83.56554620747558</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = -8.867x + 21744.659</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>341.094315649004</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6610.936832671729</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.248090006956523e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.5000900777831849</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-8.739999999999782</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.77677e-08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.746</v>
+      </c>
+      <c r="F14" t="n">
+        <v>395.6789696188638</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6215045798424088</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.841838478171974</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.459130873142708</v>
+      </c>
+      <c r="J14" t="n">
+        <v>17.90725685315073</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-84.57163450077203</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = -10.523x + 25276.479</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>337.9733616294421</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6553.353565219952</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.252345813924323e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.5001469922418816</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-3.599999999999909</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.77724e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.794</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8081998909903286</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.798960099853693</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.338672632768938</v>
+      </c>
+      <c r="J15" t="n">
+        <v>17.21761121296656</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-85.01465463204343</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = -11.464x + 27172.028</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.445652138653639e-12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2588.31182980137</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000401e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8164955951202296</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14.53999999999996</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.779280000000001e-08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.855</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6648349606413062</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.318603758969618</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.514313476228472</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.252830268963025</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>83.04760759347671</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 8.201x + -17039.262</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.330838232036492e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2567.327131939855</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000370885e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8167523881424483</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.8099999999999454</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.77997e-08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.90600000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8256388811553174</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.160303032824029</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.496818193287538</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-84.87169996115252</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = -11.143x + 25895.835</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.587055930497271e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2545.968779739195</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000003167629e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8170067791979968</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>20.34000000000015</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.78108e-08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.968</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4320753514346465</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.218701549364747</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.211765834399351</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.329884495467545</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.778934440490884</v>
+      </c>
+      <c r="K18" t="n">
+        <v>82.85972290162067</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 7.983x + -16280.100</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.133077636823484e-14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2523.784958011967</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000562e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.817265665735262</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>31.18000000000029</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.782240000000001e-08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.036</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3223028079771063</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9678492693181057</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.249760011366952</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.236942156605306</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.943119772395903</v>
+      </c>
+      <c r="K19" t="n">
+        <v>82.79080654594047</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 7.906x + -15977.312</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.380659697293558e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2501.133789106292</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000001017485e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8175398446551458</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>24.10000000000014</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.7829e-08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.074</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1960312090680863</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8295135783392453</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.747012412154817</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.579603760540048</v>
+      </c>
+      <c r="J20" t="n">
+        <v>11.84242384179716</v>
+      </c>
+      <c r="K20" t="n">
+        <v>82.60370770065516</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 7.703x + -15401.097</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>7.040343705032971e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2479.168081807108</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000091103e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8178109244701777</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>45.01999999999998</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6.78533e-08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.15000000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6397224988899025</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.086644017967895</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.154492310862361</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.06658635293568</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.938371026378151</v>
+      </c>
+      <c r="K21" t="n">
+        <v>82.94408448505635</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 8.079x + -16066.364</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.406043277467845e-11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2455.792518640102</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000644234e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8180944798607266</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>39.91000000000008</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.78604e-08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.19799999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2640462351083021</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9879814495532626</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.040348336571709</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.429614059870137</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.701145127078962</v>
+      </c>
+      <c r="K22" t="n">
+        <v>82.68646213065504</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 7.792x + -15307.757</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.087449055633758e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2432.288536473511</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000039001e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8183732794413768</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1059.15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.01467e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.991</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4267624522103485</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.102701408200988</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.22603756486703</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.020908154463403</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26.56756768901168</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.03140294551621</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 19.283x + -48579.760</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>392.3858647214501</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8098.63783532979</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.239915336039771e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000510379219727</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-378.5599999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.901170000000001e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.79900000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3059311414599616</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.037202371463649</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.150801384362104</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.744932581537854</v>
+      </c>
+      <c r="J3" t="n">
+        <v>101.1404161628298</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.33591378870584</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 34.421x + -74058.001</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.236782568648663e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2543.975356323464</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000119147e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8151763217885174</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-228.29</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.871849999999999e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.483120916666645</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9828615346316528</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.154426128745831</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.708559918519405</v>
+      </c>
+      <c r="J4" t="n">
+        <v>128.8231460712351</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.12244898454843</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 30.505x + -62609.482</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.10297097509419e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2452.546557468798</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000630069e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.81544558927731</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-162.3100000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.859489999999999e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.70099999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1099357458289902</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8962108437912022</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.302543450741216</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.637925908124771</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.30883991372554</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 21.275x + -42130.121</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.553022794014832e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2403.962535507002</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000059433e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8156291108516524</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-105.8899999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.85015e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.901</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4107056104855488</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.091831608113072</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.276186969290611</v>
+      </c>
+      <c r="I6" t="n">
+        <v>714.149801440537</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.92784147262004</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.86794355697477</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.842x + -26346.410</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.385596207340135e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2363.838351958109</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000045021e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8158345403340916</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-83.75999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.84917e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.036</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4533791679066642</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.255517993071364</v>
+      </c>
+      <c r="H7" t="n">
+        <v>538.7038099188688</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.222394279477252</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.46772212690485</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.65473983312367</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 8.993x + -16231.464</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1074.040966319842</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>186810696.507831</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.630490183183693e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8649589617869202</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-62.77000000000021</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.84907e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-85.169</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3586923193976381</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.14278178015128</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.266579218978331</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22.29757453523105</v>
+      </c>
+      <c r="K8" t="n">
+        <v>74.7550085595128</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 3.669x + -5512.860</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1068.374948206254</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>114722952.871877</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.562612724679226e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8714784495588442</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-46.34000000000015</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.850089999999999e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-85.262</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5757036115365949</v>
+      </c>
+      <c r="G9" t="n">
+        <v>801.2488493911743</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.628870449363887</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.160138365996004</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-4.423922731858651</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = -0.077x + 1903.285</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1062.039745893575</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>141810577.8011816</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.510729130812662e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.876697387913545</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-49.26999999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.853689999999999e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-85.349</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.07703503292990613</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9195799478776939</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.399311406553563</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.42329063236644</v>
+      </c>
+      <c r="K10" t="n">
+        <v>22.16267462696134</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 0.407x + 835.052</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1055.946185732522</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>111482269.904886</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.467170916714975e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8812835313565098</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-21.18000000000006</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.85614e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-85.43899999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5787937372500107</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.564752128530336</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.393767800667235</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-82.14450195535515</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = -7.248x + 15461.405</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1049.882941234716</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>180933920.122557</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.428077054446047e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8855000882939355</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-567.27</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.61225e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.506</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2343743442742951</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9244809474002373</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.000964525761355</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.51104332856812</v>
+      </c>
+      <c r="J2" t="n">
+        <v>70.38157436576104</v>
+      </c>
+      <c r="K2" t="n">
+        <v>88.05130521994244</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 29.391x + -76840.012</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-76840.01227654665</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.685909701608607e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>567.27</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000024562e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8126238409191623</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-326.5899999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.50528e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.354</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2208548089908971</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.928123848445807</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.471708876600364</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.691970342702316</v>
+      </c>
+      <c r="J3" t="n">
+        <v>223.0329343442915</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.104591265172</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 30.218x + -76671.137</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-76671.13656891391</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.70066461649694e-13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>326.5899999999997</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000112659e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8127361061187315</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-221.3199999999997</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.45043e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.764</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3485611616468593</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.032955248312594</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.327046050758152</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.148091272999795</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.69000005984699</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 24.790x + -61176.132</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-61176.13245778675</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.23662972393889e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>249.9200000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000001930405e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8128312407084796</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-162.5799999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.417e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.044</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.07252787191573158</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8703976778886107</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.110336336973675</v>
+      </c>
+      <c r="I5" t="n">
+        <v>412.004742687768</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.16149309536137</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.63989011974138</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 17.032x + -40546.823</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-40546.82309079404</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.709181305967928e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>244.6700000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000127682e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8129965467384119</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-118.6799999999998</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.395500000000001e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.253</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1826653508224224</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8847209752962711</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.275462215865676</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.23593455563406</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.55807236546769</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 10.497x + -23748.454</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-23748.45357520839</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.277472911906481e-13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>236.3499999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001034e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8132103789963276</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-77.92000000000007</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.38219e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.42</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3410522827334818</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.213144910882809</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.657552267463065</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.52771544897151</v>
+      </c>
+      <c r="K7" t="n">
+        <v>74.19145667576016</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 3.532x + -6398.589</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-6398.589481440563</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.201259017102285e-14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>219.0099999999998</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000026023e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8134185748916484</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-68.57000000000016</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.372e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.559</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1960542176726415</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7785697247593172</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.004897586342347</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.06744247813327</v>
+      </c>
+      <c r="K8" t="n">
+        <v>45.98535052200963</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 1.035x + -420.647</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-420.6473918224783</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.141136021500345e-14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>227.5700000000002</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000016933e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8136481426912326</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-40.01999999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.364490000000001e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.68899999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.264161670762313</v>
+      </c>
+      <c r="G9" t="n">
+        <v>987.7210559440875</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.383235449790547</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.342407330990516</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.8528027549354</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-76.78609877128874</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = -4.259x + 12090.362</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>12090.36223906311</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.55905770065459e-14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>214.8200000000002</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000025275e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.813854540302587</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-23.42000000000007</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.357000000000001e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.812</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05923809152265091</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.488137063290126</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.12536331376819</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16.27770217327346</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-82.43159977400823</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = -7.526x + 19482.546</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>19482.54587506013</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6.941494330057665e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>217.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000116808e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8140451335626275</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9.940000000000055</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.35288e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.929</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3421487716741068</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6703626165829071</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.093152184851112</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.937072895074832</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.471852087896089</v>
+      </c>
+      <c r="K11" t="n">
+        <v>82.65589182473957</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 7.759x + -16897.911</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-16897.91057253166</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.869407702567255e-14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>203.4099999999999</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000467e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.814230204809796</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>-65.70931508433515</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = -2.216x + 7974.761</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>7974.760763267007</v>
       </c>
       <c r="Y2" t="n">
         <v>6.640397004616299e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>3001.585328281391</v>
+        <v>250.6799999999998</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000001899757e-08</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>68.25430857777698</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 2.507x + -4105.444</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-4105.444491448474</v>
       </c>
       <c r="Y3" t="n">
         <v>1.406035629773169e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>2874.875828182493</v>
+        <v>250.8200000000002</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000067825e-08</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>-33.53220000703727</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = -0.663x + 3667.351</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>3667.350732222937</v>
       </c>
       <c r="Y4" t="n">
         <v>6.713748635193583e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2824.137356664117</v>
+        <v>230.1800000000003</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000001881e-08</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>-66.6106641159671</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = -2.312x + 7557.655</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>7557.655430969498</v>
       </c>
       <c r="Y5" t="n">
         <v>1.798274215678066e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2788.772242124763</v>
+        <v>224.2800000000002</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000615846e-08</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>88.00077382004689</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 28.647x + -65630.981</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-65630.98061932939</v>
       </c>
       <c r="Y6" t="n">
         <v>8.545114213889972e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2761.7199542041</v>
+        <v>228.21</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000001421993e-08</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>87.72752814586424</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 25.200x + -56895.362</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-56895.36174195277</v>
       </c>
       <c r="Y7" t="n">
         <v>7.847866497245891e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2733.489103789219</v>
+        <v>221.3699999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000706327e-08</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>87.3188431259309</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 21.354x + -47327.054</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-47327.05424900413</v>
       </c>
       <c r="Y8" t="n">
         <v>3.735499326061547e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2707.103229311077</v>
+        <v>236.6199999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000070395e-08</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>87.42226254303172</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 22.212x + -48963.474</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-48963.4742857961</v>
       </c>
       <c r="Y9" t="n">
         <v>2.43947090069047e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2683.432122226611</v>
+        <v>221.1100000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000034529e-08</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>87.36773313344881</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 21.751x + -47516.066</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-47516.06608020557</v>
       </c>
       <c r="Y10" t="n">
         <v>6.328699988977746e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2662.023493568865</v>
+        <v>216.0799999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000004330382e-08</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>87.39339591616216</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 21.966x + -47657.550</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-47657.55043392426</v>
       </c>
       <c r="Y11" t="n">
         <v>6.709030642352584e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2641.899796822844</v>
+        <v>212.3399999999997</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000022788e-08</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>87.14813825231388</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 20.074x + -43038.867</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-43038.86747210872</v>
       </c>
       <c r="Y12" t="n">
         <v>5.241992900452892e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>2623.157901990913</v>
+        <v>221.5299999999997</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000379033e-08</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>87.51984458494603</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 23.087x + -49505.182</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-49505.18196301869</v>
       </c>
       <c r="Y13" t="n">
         <v>5.842324758274235e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>2604.469220382614</v>
+        <v>207.5800000000004</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000140426e-08</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>87.30288265207135</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 21.228x + -44963.832</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-44963.83211327767</v>
       </c>
       <c r="Y14" t="n">
         <v>1.030577065505473e-07</v>
       </c>
       <c r="Z14" t="n">
-        <v>2584.732100695554</v>
+        <v>216.77</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000003581505e-08</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>38.01064789776142</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 0.782x + 243.587</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>243.5865482251355</v>
       </c>
       <c r="Y15" t="n">
         <v>2.126298726775029e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2563.776064966605</v>
+        <v>198.8800000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000002325532e-08</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>-44.80258112615174</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = -0.993x + 4049.962</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>4049.962157504391</v>
       </c>
       <c r="Y16" t="n">
         <v>5.236013066885747e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2542.982383236801</v>
+        <v>202.8299999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000321449e-08</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>84.32949883650566</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 10.071x + -19840.830</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-19840.82956715482</v>
       </c>
       <c r="Y17" t="n">
         <v>4.1592652297334e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>2522.901797562265</v>
+        <v>200.4099999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000049537e-08</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>-83.05180615951504</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = -8.206x + 19519.920</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>19519.92006611818</v>
       </c>
       <c r="Y18" t="n">
         <v>1.126577163053326e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2500.26313363378</v>
+        <v>189.79</v>
       </c>
       <c r="AA18" t="n">
         <v>1.00000000036226e-08</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>-81.85952438131247</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = -6.991x + 16628.510</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>16628.51016872962</v>
       </c>
       <c r="Y19" t="n">
         <v>3.262996572198026e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>2478.894211949943</v>
+        <v>196.8599999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000344816e-08</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>-80.39838400769001</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = -5.911x + 14239.270</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>14239.27019081562</v>
       </c>
       <c r="Y20" t="n">
         <v>2.226941585207567e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>2457.371874773199</v>
+        <v>195.2800000000002</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000338555e-08</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>-63.09955057614199</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = -1.971x + 5873.204</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>5873.204082927272</v>
       </c>
       <c r="Y21" t="n">
         <v>3.197617281222268e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>2435.480744332806</v>
+        <v>196.1500000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000135527e-08</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>-69.62958949863966</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = -2.693x + 7324.253</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>7324.253338262391</v>
       </c>
       <c r="Y22" t="n">
         <v>2.988510286001275e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2413.714908084446</v>
+        <v>194.5799999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000435508e-08</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-961.6500000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.740070000000001e-08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.35899999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1580295787236385</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.069636761434954</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.316777065036722</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.359598161451792</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30.40500353390687</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.40808114583562</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 22.090x + -57612.375</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-57612.37529112391</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.935639218335637e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>961.6500000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000353349e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8130108639113784</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-372.3099999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.55186e-08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.377</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.15597662669536</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.804448181899402</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.964976895865203</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.839260274199415</v>
+      </c>
+      <c r="J3" t="n">
+        <v>136.0127590362873</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.23777067129679</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 32.503x + -80256.391</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-80256.39060911685</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.997280937048963e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>372.3099999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000160544e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8133994860999627</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-167.6900000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.47311e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.00700000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4214937090948205</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.532845405562863</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.303454962172879</v>
+      </c>
+      <c r="I4" t="n">
+        <v>322.4729132133072</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.29149545690387</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.34884385921778</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 21.596x + -51535.258</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-51535.25844373357</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.577927479512069e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>226.3299999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000092494e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8135096614813595</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-96.36999999999989</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.434270000000001e-08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.289</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3990947454883627</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.04718887486033</v>
+      </c>
+      <c r="H5" t="n">
+        <v>562.4458520221332</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.348477644807508</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.25388086006874</v>
+      </c>
+      <c r="K5" t="n">
+        <v>82.20491213081031</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 7.305x + -15732.085</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-15732.08497911205</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.068582775005646e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>224.54</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000130792e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8135940824648769</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-62.8100000000004</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.414810000000001e-08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.47</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1958259552771341</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7575991155664278</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.197567526764884</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.87413801614347</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10.14312710119752</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 0.179x + 1610.646</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>1610.646372966079</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8.294856708039462e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>227.8400000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000141992e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8137013118070346</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-27.75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.399980000000001e-08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.622</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1630152208283609</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.686931970383128</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.216059520728476</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17.3349869625258</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-82.04743849485872</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = -7.158x + 19151.648</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>19151.64821697749</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.790135062023177e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>223.7800000000002</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000168204e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.813818146844563</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4.869999999999891</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.39136e-08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.72799999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.293593661308444</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.062945521271499</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.316385048721868</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.562918941348437</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>82.6468918039423</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 7.749x + -17379.515</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-17379.51475196866</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.024899505934977e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>206.4699999999998</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000858937e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8139686487906279</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>34.38999999999987</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.385170000000001e-08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.837</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.658982534001837</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.296508888095846</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.53453796222686</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.806789448732688</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.03672626642278</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 8.188x + -18265.966</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-18265.96631159286</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.898674031924192e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>197.3400000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000152786e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8141281714136135</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>34.97000000000025</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.38007e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.902</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.32984824405361</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.296957869396333</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.423771901983319</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.625267641330924</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>82.79216215529004</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 7.907x + -17429.167</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-17429.16732465491</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.021404550313151e-12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000450889e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8143032206753101</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>48.30999999999995</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.37627e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2729264226267282</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.03906723245154</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.078088519867189</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.024956456466199</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>82.56310257964626</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 7.661x + -16688.274</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-16688.27394000787</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.680692204652808e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>203.73</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000717e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8144778646036316</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>45.83000000000038</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.373989999999999e-08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-85.056</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.06609625557926974</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.712282329320996</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.821712515724188</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.601343412375206</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.49972096216698</v>
+      </c>
+      <c r="K12" t="n">
+        <v>82.23306190620703</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 7.332x + -15769.062</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-15769.0620547541</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.944154481043606e-12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>205.8599999999997</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.00000000052814e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8146771151968254</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>68.75999999999976</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.3729e-08</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-85.133</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3933404076447223</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.071486841442027</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.472536317713148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.153526135518121</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82.50606800820141</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 7.602x + -16253.522</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-16253.52181116075</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.449466072159275e-14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>195.0100000000002</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000209167e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8148807343212996</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83.41999999999962</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.3716e-08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-85.203</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4654544198926757</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.555597913374986</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.521592688617574</v>
+      </c>
+      <c r="I14" t="n">
+        <v>84.86890251743107</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22.42573878765785</v>
+      </c>
+      <c r="K14" t="n">
+        <v>82.75603483147846</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 7.867x + -16715.067</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-16715.06673198813</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.609665042640764e-07</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>187.2000000000003</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000003700823e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8151006963176228</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>84.80000000000018</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.36922e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-85.25700000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1584921865606517</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.175420956246815</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.117284836218874</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.387009919038376</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>82.57422742846562</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 7.673x + -16117.769</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-16117.76919812736</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.756212343463959e-12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>187.23</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000114633e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8153244681154601</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>88.12000000000012</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.36945e-08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-85.322</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2133279147626263</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8213329672743404</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.990190307023456</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.950945897487208</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>82.31096173310172</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 7.407x + -15374.215</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-15374.21500809582</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.496960890675319e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>191.4499999999998</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.00000000642978e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8155510463640283</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>103.4399999999998</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.36918e-08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-85.401</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3419949327900979</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.857407207973485</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.003504997896159</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.842874762838925</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>82.39128011185888</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 7.486x + -15401.710</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-15401.70994721583</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.389098823756533e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>187.3000000000002</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.00000000006778e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8157929667660343</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99.11999999999989</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.36817e-08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.45</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1967301522627209</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6414688705217806</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.813678695379959</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.134069767441859</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>82.07863491517216</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 7.187x + -14606.284</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-14606.28364334215</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.446120653530682e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>190.9300000000003</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000001617385e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.816027122175902</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106.8999999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.36817e-08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.50700000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1604204294412884</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.669975273499428</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.757336367665618</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.220499864432375</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>82.01049780865009</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 7.125x + -14335.545</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-14335.54501288281</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.198463456871953e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>188.9700000000003</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000075597e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8162853293675241</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>112.1200000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.36643e-08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.56399999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.04889432344159064</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7731944817870466</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.675676841011736</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.281008539207324</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>82.03847132861051</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 7.150x + -14260.049</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-14260.04878831147</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.231359391734711e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>185.48</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000010916e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8165295367997146</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>130.9200000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6.36642e-08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.619</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6540865509207645</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.316073894541076</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.484518542411394</v>
+      </c>
+      <c r="I21" t="n">
+        <v>88.26794817049611</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20.14386897762218</v>
+      </c>
+      <c r="K21" t="n">
+        <v>82.58977545658749</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 7.689x + -15288.695</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-15288.69473552221</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.990481872477043e-11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>171.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000005916e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8167862150656783</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>128.25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.366399999999999e-08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.66800000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.397888051238116</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9804175531918452</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.135804950262686</v>
+      </c>
+      <c r="I22" t="n">
+        <v>106.2490284567456</v>
+      </c>
+      <c r="J22" t="n">
+        <v>16.91258002358736</v>
+      </c>
+      <c r="K22" t="n">
+        <v>82.28823448463952</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 7.385x + -14503.358</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-14503.35821236979</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.640809110827982e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>174.8799999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000089927e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8170488691685506</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>84.79996252394287</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.988x + -33913.173</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-33913.17346430986</v>
       </c>
       <c r="Y2" t="n">
         <v>1.335479054312013e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>3724.855063932422</v>
+        <v>1973.24</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000185512e-08</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>87.39422175177619</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 21.973x + -59676.987</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-59676.98683048016</v>
       </c>
       <c r="Y3" t="n">
         <v>4.15787692821595e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3272.142500169624</v>
+        <v>965.1299999999997</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000007171e-08</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>88.30846062536317</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 33.862x + -88793.058</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-88793.05783803968</v>
       </c>
       <c r="Y4" t="n">
         <v>5.535052391839412e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>3149.705858993187</v>
+        <v>491.8200000000002</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000011272e-08</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>88.14230204396958</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 30.832x + -78445.743</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-78445.74332960373</v>
       </c>
       <c r="Y5" t="n">
         <v>2.007370219226665e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>3082.660736637521</v>
+        <v>325.9099999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000001852e-08</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>87.86450806269114</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 26.818x + -66733.285</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-66733.2851430825</v>
       </c>
       <c r="Y6" t="n">
         <v>1.136330487606972e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>3026.970313126165</v>
+        <v>242.1399999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000149396e-08</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>86.64282388502379</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.047x + -40833.412</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-40833.41244077377</v>
       </c>
       <c r="Y7" t="n">
         <v>2.773676998252171e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>2975.443512917976</v>
+        <v>246.9400000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000152931e-08</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>85.03898339160779</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.520x + -26478.520</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-26478.52027116762</v>
       </c>
       <c r="Y8" t="n">
         <v>1.706624408938204e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>2928.207222118213</v>
+        <v>237.3500000000004</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000125036e-08</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>77.96061947910844</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 4.689x + -9327.409</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9327.408867039567</v>
       </c>
       <c r="Y9" t="n">
         <v>9.010949242543768e-14</v>
       </c>
       <c r="Z9" t="n">
-        <v>2884.750338449863</v>
+        <v>224.1700000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000026676e-08</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>-24.75953327825828</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = -0.461x + 3264.069</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>3264.069165949725</v>
       </c>
       <c r="Y10" t="n">
         <v>7.975261471801174e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2844.982276807901</v>
+        <v>216.2600000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000002224216e-08</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>-78.31701812655305</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = -4.836x + 13687.387</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>13687.38722258985</v>
       </c>
       <c r="Y11" t="n">
         <v>4.682352462606695e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2807.938141447114</v>
+        <v>208.1100000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000023074e-08</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>88.10408525269288</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 30.210x + -78594.548</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-78594.54834015714</v>
       </c>
       <c r="Y2" t="n">
         <v>2.503713272876611e-14</v>
       </c>
       <c r="Z2" t="n">
-        <v>3100.80941084509</v>
+        <v>635.7600000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000923e-08</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>88.00266796165695</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 28.675x + -70461.339</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-70461.33876678524</v>
       </c>
       <c r="Y3" t="n">
         <v>5.232455212980571e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2978.445253380965</v>
+        <v>255.6599999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000002362421e-08</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>86.09871374465523</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.664x + -34260.851</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-34260.85119992684</v>
       </c>
       <c r="Y4" t="n">
         <v>3.334338909097358e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2926.702183851483</v>
+        <v>241.6899999999996</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000626478e-08</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>78.10228108292959</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 4.746x + -9528.855</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9528.855288247358</v>
       </c>
       <c r="Y5" t="n">
         <v>3.341261710476093e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2889.113656267828</v>
+        <v>228.3899999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000459937e-08</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>-69.68331444941018</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = -2.701x + 8611.959</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>8611.958834524094</v>
       </c>
       <c r="Y6" t="n">
         <v>2.121758090205614e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2856.524373585025</v>
+        <v>222.98</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000139599e-08</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>-84.17006358102275</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = -9.794x + 25634.435</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>25634.43472015978</v>
       </c>
       <c r="Y7" t="n">
         <v>3.727928214626339e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2825.827724083491</v>
+        <v>214.3200000000002</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000130665e-08</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>-84.17881511505529</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = -9.809x + 25320.983</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>25320.98282286995</v>
       </c>
       <c r="Y8" t="n">
         <v>1.024607990855834e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2796.404053660201</v>
+        <v>216.4499999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000002077736e-08</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>82.72326703628727</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 7.831x + -17405.608</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-17405.60786540977</v>
       </c>
       <c r="Y9" t="n">
         <v>1.457729395873112e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2767.214036768366</v>
+        <v>211.96</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000059899e-08</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>82.2923416967986</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 7.389x + -16172.143</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-16172.14336217859</v>
       </c>
       <c r="Y10" t="n">
         <v>1.79788051483419e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2738.675985261965</v>
+        <v>218.5500000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000003111544e-08</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>82.32897058829273</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 7.424x + -16097.178</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-16097.17823252997</v>
       </c>
       <c r="Y11" t="n">
         <v>6.925899905588307e-14</v>
       </c>
       <c r="Z11" t="n">
-        <v>2710.199659339391</v>
+        <v>212.9499999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000013651e-08</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>83.32285369878258</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 8.542x + -18538.407</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-18538.40743180953</v>
       </c>
       <c r="Y12" t="n">
         <v>8.698792079256109e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2682.979306390135</v>
+        <v>189.8499999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000019037e-08</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>82.36623349893193</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 7.461x + -15863.743</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-15863.74319316536</v>
       </c>
       <c r="Y13" t="n">
         <v>1.294911995502573e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>2655.560599979192</v>
+        <v>205.5500000000002</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000029963e-08</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>83.07434174599595</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 8.233x + -17467.628</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-17467.62813982737</v>
       </c>
       <c r="Y14" t="n">
         <v>5.02898540932662e-14</v>
       </c>
       <c r="Z14" t="n">
-        <v>2628.621820032761</v>
+        <v>188.5699999999997</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000496e-08</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>82.72754687888354</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 7.836x + -16404.743</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-16404.74254993359</v>
       </c>
       <c r="Y15" t="n">
         <v>2.129029427930446e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>2602.193960973588</v>
+        <v>190.8999999999996</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000008681e-08</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>83.11804821964103</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 8.285x + -17247.905</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-17247.90450462234</v>
       </c>
       <c r="Y16" t="n">
         <v>1.467782092261909e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>2575.984614183384</v>
+        <v>183.02</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000003920471e-08</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>82.54717801170752</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 7.644x + -15655.706</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-15655.70638275604</v>
       </c>
       <c r="Y17" t="n">
         <v>1.655215230294291e-07</v>
       </c>
       <c r="Z17" t="n">
-        <v>2549.524310452643</v>
+        <v>191.4700000000003</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000001989374e-08</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>82.53719370838013</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 7.634x + -15475.953</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-15475.9528379699</v>
       </c>
       <c r="Y18" t="n">
         <v>1.294975845472857e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2522.962256241677</v>
+        <v>190.0099999999998</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000003885e-08</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>81.78827322698132</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 6.929x + -13788.508</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-13788.50815160075</v>
       </c>
       <c r="Y19" t="n">
         <v>7.333281535670074e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2496.178754784095</v>
+        <v>202.9299999999998</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000080488e-08</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>82.94100422387126</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 8.076x + -16107.919</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-16107.91924259595</v>
       </c>
       <c r="Y20" t="n">
         <v>1.963439150436547e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2469.600454719319</v>
+        <v>175.3799999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000008409e-08</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>82.68857782797556</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 7.794x + -15340.878</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-15340.87843996631</v>
       </c>
       <c r="Y21" t="n">
         <v>7.457985090775765e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>2442.754711392271</v>
+        <v>180.6399999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000080993e-08</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>82.33801949786105</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 7.433x + -14424.350</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-14424.35012449286</v>
       </c>
       <c r="Y22" t="n">
         <v>7.38743871202838e-12</v>
       </c>
       <c r="Z22" t="n">
-        <v>2415.841176766926</v>
+        <v>182.6900000000003</v>
       </c>
       <c r="AA22" t="n">
         <v>1.0000000000519e-08</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>85.20881726625123</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.931x + -37181.958</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-37181.95774067543</v>
       </c>
       <c r="Y2" t="n">
         <v>9.489649772884224e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>3707.894080356654</v>
+        <v>1809.8</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000006821e-08</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>87.68078154358194</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 24.691x + -66059.701</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-66059.70141254611</v>
       </c>
       <c r="Y3" t="n">
         <v>5.517787105115126e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3218.210291151423</v>
+        <v>796.6599999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001999e-08</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>88.24301206018693</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 32.600x + -83852.576</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-83852.57578949022</v>
       </c>
       <c r="Y4" t="n">
         <v>6.276089341358065e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>3095.380351498084</v>
+        <v>441.6199999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000005625e-08</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>88.06285369564924</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 29.566x + -74013.201</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-74013.20132172584</v>
       </c>
       <c r="Y5" t="n">
         <v>6.01561900948159e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>3033.146864149631</v>
+        <v>294.9400000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000004289e-08</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>87.46376315789631</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 22.576x + -55004.404</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-55004.40421502014</v>
       </c>
       <c r="Y6" t="n">
         <v>9.5955133763302e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>2983.824621989874</v>
+        <v>253.73</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000004206e-08</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>86.66071576043031</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.139x + -40656.913</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-40656.91250923482</v>
       </c>
       <c r="Y7" t="n">
         <v>1.415628643110699e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2938.874907182456</v>
+        <v>229.8500000000004</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000029043e-08</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>84.41402179195856</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.225x + -23038.004</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-23038.00394133735</v>
       </c>
       <c r="Y8" t="n">
         <v>3.368461865905526e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2897.045874698175</v>
+        <v>229.3199999999997</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000001490659e-08</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>79.19560156564935</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 5.240x + -10650.117</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10650.116553725</v>
       </c>
       <c r="Y9" t="n">
         <v>1.976068441226693e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2857.294100960475</v>
+        <v>231.6099999999997</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000002348099e-08</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>-21.92849277603647</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = -0.403x + 3080.166</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>3080.166053908959</v>
       </c>
       <c r="Y10" t="n">
         <v>1.647331413136195e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2820.477322753758</v>
+        <v>216.9900000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000497801e-08</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>-75.28400969379423</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = -3.807x + 11047.615</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>11047.61525274087</v>
       </c>
       <c r="Y11" t="n">
         <v>2.453884835213759e-13</v>
       </c>
       <c r="Z11" t="n">
-        <v>2785.960762766516</v>
+        <v>220.3699999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000097333e-08</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>87.26965780233698</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 20.969x + -54464.963</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-54464.96287665951</v>
       </c>
       <c r="Y2" t="n">
         <v>6.826779095373975e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>3112.206535620435</v>
+        <v>962.1799999999998</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000068123e-08</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>88.25526778769634</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 32.829x + -80669.629</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-80669.62904581991</v>
       </c>
       <c r="Y3" t="n">
         <v>4.514337441707183e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2953.37503172122</v>
+        <v>370.8200000000002</v>
       </c>
       <c r="AA3" t="n">
         <v>1.0000000037225e-08</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>87.76978611891255</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 25.678x + -61257.100</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-61257.09970802224</v>
       </c>
       <c r="Y4" t="n">
         <v>3.668005610458705e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2898.741819339024</v>
+        <v>238.8199999999997</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000018462e-08</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>86.51862535185441</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.438x + -37930.709</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-37930.7087741549</v>
       </c>
       <c r="Y5" t="n">
         <v>3.935896412075662e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2862.201244899916</v>
+        <v>222.1800000000003</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000016909e-08</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>83.72447086690875</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.093x + -19817.841</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-19817.84052044459</v>
       </c>
       <c r="Y6" t="n">
         <v>1.94204070804713e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2829.966957799847</v>
+        <v>234.5299999999997</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000001365048e-08</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>73.19361397958819</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 3.311x + -5842.658</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-5842.658061940697</v>
       </c>
       <c r="Y7" t="n">
         <v>2.830260427125439e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2800.232420436188</v>
+        <v>226.0800000000004</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000016682e-08</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>-40.3947259605872</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = -0.851x + 4033.184</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>4033.184208893517</v>
       </c>
       <c r="Y8" t="n">
         <v>3.189804074923447e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2772.05319856209</v>
+        <v>221.0700000000002</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000106446e-08</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>-77.34308860832034</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = -4.453x + 12418.750</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>12418.75004068838</v>
       </c>
       <c r="Y9" t="n">
         <v>361.9679600828741</v>
       </c>
       <c r="Z9" t="n">
-        <v>6900.748144565289</v>
+        <v>216.3099999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.211874841429044e-06</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>-82.75673564432105</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = -7.868x + 20229.592</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>20229.59207957098</v>
       </c>
       <c r="Y10" t="n">
         <v>359.2523461034974</v>
       </c>
       <c r="Z10" t="n">
-        <v>6834.244800307194</v>
+        <v>211.9500000000003</v>
       </c>
       <c r="AA10" t="n">
         <v>1.217394013992102e-06</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>-85.45352960590004</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = -12.576x + 30999.364</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>30999.36380989699</v>
       </c>
       <c r="Y11" t="n">
         <v>357.2408689988711</v>
       </c>
       <c r="Z11" t="n">
-        <v>6775.33087665479</v>
+        <v>200.6599999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.223676434887456e-06</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>-84.77772390229033</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = -10.941x + 26805.845</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>26805.84484575409</v>
       </c>
       <c r="Y12" t="n">
         <v>1.022873543275556e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2673.595039786875</v>
+        <v>210.29</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000125491e-08</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>82.6544099938159</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 7.757x + -16552.665</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-16552.66532110814</v>
       </c>
       <c r="Y13" t="n">
         <v>4.55369299566428e-14</v>
       </c>
       <c r="Z13" t="n">
-        <v>2651.228810142732</v>
+        <v>206.0599999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000079327e-08</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>82.44241758664617</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 7.537x + -15918.011</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-15918.01141821042</v>
       </c>
       <c r="Y14" t="n">
         <v>8.841104674228749e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>2629.495411274605</v>
+        <v>208.9699999999998</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000677394e-08</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>83.03310516837367</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 8.183x + -17260.476</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-17260.47574685215</v>
       </c>
       <c r="Y15" t="n">
         <v>3.299561483160774e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>2608.163674743105</v>
+        <v>194.9899999999998</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000339211e-08</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>82.60768981812728</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 7.708x + -16043.517</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-16043.51675191806</v>
       </c>
       <c r="Y16" t="n">
         <v>3.511844908860799e-14</v>
       </c>
       <c r="Z16" t="n">
-        <v>2586.717452900827</v>
+        <v>202.0999999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000001428e-08</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>82.63848551794553</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 7.740x + -15988.568</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-15988.56842160121</v>
       </c>
       <c r="Y17" t="n">
         <v>4.959987999328106e-15</v>
       </c>
       <c r="Z17" t="n">
-        <v>2565.091971097781</v>
+        <v>198.5599999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000049384e-08</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>82.26139441669933</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 7.359x + -15020.971</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-15020.97071327513</v>
       </c>
       <c r="Y18" t="n">
         <v>6.980759872087457e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2543.337884805379</v>
+        <v>202.6599999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000470609e-08</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>82.65286823427783</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 7.756x + -15768.304</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-15768.30395494532</v>
       </c>
       <c r="Y19" t="n">
         <v>8.488568489960556e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>2521.96677157164</v>
+        <v>193.6599999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000001431337e-08</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>82.6918934023077</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 7.797x + -15725.084</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-15725.08428232545</v>
       </c>
       <c r="Y20" t="n">
         <v>9.700793949221654e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>2499.991973103609</v>
+        <v>190.1199999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000115598e-08</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>82.9750707414034</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 8.115x + -16279.860</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-16279.86037098733</v>
       </c>
       <c r="Y21" t="n">
         <v>2.322849944898881e-07</v>
       </c>
       <c r="Z21" t="n">
-        <v>2478.3568299565</v>
+        <v>183.3100000000002</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000122447e-08</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>82.74285413621382</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 7.853x + -15583.050</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-15583.04995540379</v>
       </c>
       <c r="Y22" t="n">
         <v>1.226996704798019e-06</v>
       </c>
       <c r="Z22" t="n">
-        <v>2456.830313811909</v>
+        <v>185.9299999999998</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000651405e-08</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>85.48188522029676</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.655x + -38450.908</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-38450.90750279372</v>
       </c>
       <c r="Y2" t="n">
         <v>4.07231523396653e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>3614.404843408442</v>
+        <v>1673.63</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000011803e-08</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>87.88601646475465</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 27.091x + -70861.417</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-70861.41668822135</v>
       </c>
       <c r="Y3" t="n">
         <v>8.497936375118675e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3136.862093895567</v>
+        <v>679.6599999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000032086e-08</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>88.11393833010669</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 30.368x + -76005.015</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-76005.01470573906</v>
       </c>
       <c r="Y4" t="n">
         <v>5.42339174985863e-15</v>
       </c>
       <c r="Z4" t="n">
-        <v>3023.552290229102</v>
+        <v>415.0699999999997</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000009e-08</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>88.03663367816085</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 29.171x + -71552.841</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-71552.84095192752</v>
       </c>
       <c r="Y5" t="n">
         <v>1.143507990293474e-14</v>
       </c>
       <c r="Z5" t="n">
-        <v>2967.407414415672</v>
+        <v>280.1599999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000004e-08</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>87.75455022508199</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 25.503x + -61388.757</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-61388.75708529154</v>
       </c>
       <c r="Y6" t="n">
         <v>1.029002508925277e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2924.041814009404</v>
+        <v>237.6100000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000067729e-08</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>86.82365294782925</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.020x + -42135.531</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-42135.53109468762</v>
       </c>
       <c r="Y7" t="n">
         <v>9.147892250672547e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2884.832626894152</v>
+        <v>237.1499999999996</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000131622e-08</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>85.56209972795442</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 12.885x + -29135.044</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-29135.04419632994</v>
       </c>
       <c r="Y8" t="n">
         <v>5.542677087333395e-12</v>
       </c>
       <c r="Z8" t="n">
-        <v>2846.94606088787</v>
+        <v>244.4900000000002</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000059907e-08</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>83.4304374773666</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 8.683x + -18746.466</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-18746.46588649466</v>
       </c>
       <c r="Y9" t="n">
         <v>9.620224228637031e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2810.683657324257</v>
+        <v>240.3899999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000002254781e-08</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>76.36115780742992</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 4.121x + -7718.772</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7718.772412372305</v>
       </c>
       <c r="Y10" t="n">
         <v>1.085343435594107e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2776.174489074143</v>
+        <v>227.0500000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000144727e-08</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>56.86706397072344</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 1.532x + -1625.862</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-1625.861673355688</v>
       </c>
       <c r="Y11" t="n">
         <v>1.22764211002573e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2742.974615010593</v>
+        <v>226.8500000000004</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000042788e-08</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>87.82536700448766</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 26.335x + -68198.247</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-68198.24688085998</v>
       </c>
       <c r="Y2" t="n">
         <v>7.829881893687128e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>3091.679560445009</v>
+        <v>664.3099999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000209e-08</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>88.13974500407826</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 30.789x + -74739.214</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-74739.21361180568</v>
       </c>
       <c r="Y3" t="n">
         <v>1.233381463419685e-15</v>
       </c>
       <c r="Z3" t="n">
-        <v>2924.594950167621</v>
+        <v>306.04</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000826e-08</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>87.44616200928361</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 22.420x + -52595.860</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-52595.86030621087</v>
       </c>
       <c r="Y4" t="n">
         <v>8.081375275611036e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2867.690734657103</v>
+        <v>245.4700000000003</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000172454e-08</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>86.36506850289545</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.741x + -35860.551</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-35860.55058012691</v>
       </c>
       <c r="Y5" t="n">
         <v>3.271012226955511e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2831.573809693018</v>
+        <v>220.8400000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000161538e-08</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>83.45830143272448</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 8.720x + -18705.004</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-18705.0035130191</v>
       </c>
       <c r="Y6" t="n">
         <v>9.250746024137434e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2800.137047970031</v>
+        <v>224.52</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000051283e-08</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>79.02687767896758</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 5.157x + -10140.514</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10140.51409358245</v>
       </c>
       <c r="Y7" t="n">
         <v>1.161438124980658e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2770.184456181625</v>
+        <v>224.5</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000070569e-08</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>49.39061239768655</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 1.166x + -720.876</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-720.8756938429007</v>
       </c>
       <c r="Y8" t="n">
         <v>2.994395494709667e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2742.295703597552</v>
+        <v>218.3800000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000136758e-08</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>-71.43905883096647</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = -2.978x + 8953.916</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>8953.91573369358</v>
       </c>
       <c r="Y9" t="n">
         <v>3.162018812113588e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2715.893592132777</v>
+        <v>208.4899999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000123253e-08</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>-66.9712138136609</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = -2.353x + 7306.178</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>7306.178078909699</v>
       </c>
       <c r="Y10" t="n">
         <v>351.7880185803672</v>
       </c>
       <c r="Z10" t="n">
-        <v>6799.144643573309</v>
+        <v>215.9899999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1.23751993603162e-06</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>-83.93837649205827</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = -9.417x + 23491.018</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>23491.01751536819</v>
       </c>
       <c r="Y11" t="n">
         <v>346.1510907044591</v>
       </c>
       <c r="Z11" t="n">
-        <v>6714.992890909984</v>
+        <v>199.0099999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1.238171565523057e-06</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>-77.73337620723176</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = -4.599x + 12203.160</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>12203.16032319662</v>
       </c>
       <c r="Y12" t="n">
         <v>344.4505887722594</v>
       </c>
       <c r="Z12" t="n">
-        <v>6670.094166821037</v>
+        <v>215.02</v>
       </c>
       <c r="AA12" t="n">
         <v>1.244512812326237e-06</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>-83.56554620747558</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = -8.867x + 21744.659</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>21744.6586949834</v>
       </c>
       <c r="Y13" t="n">
         <v>341.094315649004</v>
       </c>
       <c r="Z13" t="n">
-        <v>6610.936832671729</v>
+        <v>207.73</v>
       </c>
       <c r="AA13" t="n">
         <v>1.248090006956523e-06</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>-84.57163450077203</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = -10.523x + 25276.479</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>25276.47871324407</v>
       </c>
       <c r="Y14" t="n">
         <v>337.9733616294421</v>
       </c>
       <c r="Z14" t="n">
-        <v>6553.353565219952</v>
+        <v>205.6900000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1.252345813924323e-06</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>-85.01465463204343</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = -11.464x + 27172.028</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>27172.02773873126</v>
       </c>
       <c r="Y15" t="n">
         <v>3.445652138653639e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>2588.31182980137</v>
+        <v>200.5799999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000401e-08</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>83.04760759347671</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 8.201x + -17039.262</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-17039.26185377737</v>
       </c>
       <c r="Y16" t="n">
         <v>1.330838232036492e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2567.327131939855</v>
+        <v>190.5900000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000370885e-08</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>-84.87169996115252</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = -11.143x + 25895.835</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>25895.83522968648</v>
       </c>
       <c r="Y17" t="n">
         <v>2.587055930497271e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>2545.968779739195</v>
+        <v>205.7600000000002</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000003167629e-08</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>82.85972290162067</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 7.983x + -16280.100</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-16280.10041114738</v>
       </c>
       <c r="Y18" t="n">
         <v>1.133077636823484e-14</v>
       </c>
       <c r="Z18" t="n">
-        <v>2523.784958011967</v>
+        <v>192.21</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000562e-08</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>82.79080654594047</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 7.906x + -15977.312</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-15977.31195387075</v>
       </c>
       <c r="Y19" t="n">
         <v>1.380659697293558e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>2501.133789106292</v>
+        <v>188.79</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000001017485e-08</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>82.60370770065516</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 7.703x + -15401.097</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-15401.09675989566</v>
       </c>
       <c r="Y20" t="n">
         <v>7.040343705032971e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>2479.168081807108</v>
+        <v>191.4300000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000091103e-08</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>82.94408448505635</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 8.079x + -16066.364</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-16066.36387276008</v>
       </c>
       <c r="Y21" t="n">
         <v>6.406043277467845e-11</v>
       </c>
       <c r="Z21" t="n">
-        <v>2455.792518640102</v>
+        <v>182</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000644234e-08</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>82.68646213065504</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 7.792x + -15307.757</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-15307.75665610602</v>
       </c>
       <c r="Y22" t="n">
         <v>2.087449055633758e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2432.288536473511</v>
+        <v>186.2800000000002</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000039001e-08</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>87.03140294551621</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 19.283x + -48579.760</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-48579.76033740994</v>
       </c>
       <c r="Y2" t="n">
         <v>392.3858647214501</v>
       </c>
       <c r="Z2" t="n">
-        <v>8098.63783532979</v>
+        <v>1059.15</v>
       </c>
       <c r="AA2" t="n">
         <v>1.239915336039771e-06</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>88.33591378870584</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 34.421x + -74058.001</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-74058.00108082524</v>
       </c>
       <c r="Y3" t="n">
         <v>2.236782568648663e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>2543.975356323464</v>
+        <v>378.5599999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000119147e-08</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>88.12244898454843</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 30.505x + -62609.482</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-62609.48196086705</v>
       </c>
       <c r="Y4" t="n">
         <v>2.10297097509419e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2452.546557468798</v>
+        <v>228.29</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000630069e-08</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>87.30883991372554</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 21.275x + -42130.121</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-42130.12097098723</v>
       </c>
       <c r="Y5" t="n">
         <v>3.553022794014832e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2403.962535507002</v>
+        <v>210.24</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000059433e-08</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>85.86794355697477</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.842x + -26346.410</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-26346.40992308271</v>
       </c>
       <c r="Y6" t="n">
         <v>2.385596207340135e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2363.838351958109</v>
+        <v>193.96</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000045021e-08</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>83.65473983312367</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 8.993x + -16231.464</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16231.46414564901</v>
       </c>
       <c r="Y7" t="n">
         <v>1074.040966319842</v>
       </c>
       <c r="Z7" t="n">
-        <v>186810696.507831</v>
+        <v>190.4399999999998</v>
       </c>
       <c r="AA7" t="n">
         <v>1.630490183183693e-07</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>74.7550085595128</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 3.669x + -5512.860</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-5512.859662034151</v>
       </c>
       <c r="Y8" t="n">
         <v>1068.374948206254</v>
       </c>
       <c r="Z8" t="n">
-        <v>114722952.871877</v>
+        <v>190.55</v>
       </c>
       <c r="AA8" t="n">
         <v>1.562612724679226e-07</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>-4.423922731858651</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = -0.077x + 1903.285</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>1903.285491749938</v>
       </c>
       <c r="Y9" t="n">
         <v>1062.039745893575</v>
       </c>
       <c r="Z9" t="n">
-        <v>141810577.8011816</v>
+        <v>179.6200000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.510729130812662e-07</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>22.16267462696134</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 0.407x + 835.052</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>835.0519703303619</v>
       </c>
       <c r="Y10" t="n">
         <v>1055.946185732522</v>
       </c>
       <c r="Z10" t="n">
-        <v>111482269.904886</v>
+        <v>188.71</v>
       </c>
       <c r="AA10" t="n">
         <v>1.467170916714975e-07</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>-82.14450195535515</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = -7.248x + 15461.405</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>15461.40481727142</v>
       </c>
       <c r="Y11" t="n">
         <v>1049.882941234716</v>
       </c>
       <c r="Z11" t="n">
-        <v>180933920.122557</v>
+        <v>170.3199999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.428077054446047e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>88.05130521994244</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 29.391x + -76840.012</t>
-        </is>
+      <c r="W2" t="n">
+        <v>29.3907932384448</v>
       </c>
       <c r="X2" t="n">
         <v>-76840.01227654665</v>
@@ -600,7 +598,7 @@
         <v>1.685909701608607e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>567.27</v>
+        <v>3154.322157603146</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000024562e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>88.104591265172</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 30.218x + -76671.137</t>
-        </is>
+      <c r="W3" t="n">
+        <v>30.21769193406556</v>
       </c>
       <c r="X3" t="n">
         <v>-76671.13656891391</v>
@@ -652,7 +648,7 @@
         <v>7.70066461649694e-13</v>
       </c>
       <c r="Z3" t="n">
-        <v>326.5899999999997</v>
+        <v>3073.389084395707</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000112659e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>87.69000005984699</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 24.790x + -61176.132</t>
-        </is>
+      <c r="W4" t="n">
+        <v>24.78992790574833</v>
       </c>
       <c r="X4" t="n">
         <v>-61176.13245778675</v>
@@ -704,7 +698,7 @@
         <v>2.23662972393889e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>249.9200000000001</v>
+        <v>3011.901859888208</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000001930405e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>86.63989011974138</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.032x + -40546.823</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.03220488645321</v>
       </c>
       <c r="X5" t="n">
         <v>-40546.82309079404</v>
@@ -756,7 +748,7 @@
         <v>1.709181305967928e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>244.6700000000001</v>
+        <v>2958.173639205987</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000127682e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>84.55807236546769</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.497x + -23748.454</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.49690275613332</v>
       </c>
       <c r="X6" t="n">
         <v>-23748.45357520839</v>
@@ -808,7 +798,7 @@
         <v>9.277472911906481e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>236.3499999999999</v>
+        <v>2908.799405817799</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001034e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>74.19145667576016</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 3.532x + -6398.589</t>
-        </is>
+      <c r="W7" t="n">
+        <v>3.531914860784846</v>
       </c>
       <c r="X7" t="n">
         <v>-6398.589481440563</v>
@@ -860,7 +848,7 @@
         <v>2.201259017102285e-14</v>
       </c>
       <c r="Z7" t="n">
-        <v>219.0099999999998</v>
+        <v>2863.506652860962</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000026023e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>45.98535052200963</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 1.035x + -420.647</t>
-        </is>
+      <c r="W8" t="n">
+        <v>1.035000599110234</v>
       </c>
       <c r="X8" t="n">
         <v>-420.6473918224783</v>
@@ -912,7 +898,7 @@
         <v>1.141136021500345e-14</v>
       </c>
       <c r="Z8" t="n">
-        <v>227.5700000000002</v>
+        <v>2821.656266362052</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000016933e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>-76.78609877128874</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = -4.259x + 12090.362</t>
-        </is>
+      <c r="W9" t="n">
+        <v>-4.258873648679776</v>
       </c>
       <c r="X9" t="n">
         <v>12090.36223906311</v>
@@ -964,7 +948,7 @@
         <v>7.55905770065459e-14</v>
       </c>
       <c r="Z9" t="n">
-        <v>214.8200000000002</v>
+        <v>2784.444589544122</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000025275e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>-82.43159977400823</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = -7.526x + 19482.546</t>
-        </is>
+      <c r="W10" t="n">
+        <v>-7.526312565517713</v>
       </c>
       <c r="X10" t="n">
         <v>19482.54587506013</v>
@@ -1016,7 +998,7 @@
         <v>6.941494330057665e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>217.75</v>
+        <v>2749.097279000534</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000116808e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>82.65589182473957</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 7.759x + -16897.911</t>
-        </is>
+      <c r="W11" t="n">
+        <v>7.758824819299897</v>
       </c>
       <c r="X11" t="n">
         <v>-16897.91057253166</v>
@@ -1068,7 +1048,7 @@
         <v>1.869407702567255e-14</v>
       </c>
       <c r="Z11" t="n">
-        <v>203.4099999999999</v>
+        <v>2717.97926798109</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000467e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>-65.70931508433515</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = -2.216x + 7974.761</t>
-        </is>
+      <c r="W2" t="n">
+        <v>-2.215714894342073</v>
       </c>
       <c r="X2" t="n">
         <v>7974.760763267007</v>
@@ -1266,7 +1244,7 @@
         <v>6.640397004616299e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>250.6799999999998</v>
+        <v>3001.585328281391</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000001899757e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>68.25430857777698</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 2.507x + -4105.444</t>
-        </is>
+      <c r="W3" t="n">
+        <v>2.507067546178828</v>
       </c>
       <c r="X3" t="n">
         <v>-4105.444491448474</v>
@@ -1318,7 +1294,7 @@
         <v>1.406035629773169e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>250.8200000000002</v>
+        <v>2874.875828182493</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000067825e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>-33.53220000703727</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = -0.663x + 3667.351</t>
-        </is>
+      <c r="W4" t="n">
+        <v>-0.6626940644601449</v>
       </c>
       <c r="X4" t="n">
         <v>3667.350732222937</v>
@@ -1370,7 +1344,7 @@
         <v>6.713748635193583e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>230.1800000000003</v>
+        <v>2824.137356664117</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000001881e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>-66.6106641159671</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = -2.312x + 7557.655</t>
-        </is>
+      <c r="W5" t="n">
+        <v>-2.312044204314832</v>
       </c>
       <c r="X5" t="n">
         <v>7557.655430969498</v>
@@ -1422,7 +1394,7 @@
         <v>1.798274215678066e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>224.2800000000002</v>
+        <v>2788.772242124763</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000615846e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>88.00077382004689</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 28.647x + -65630.981</t>
-        </is>
+      <c r="W6" t="n">
+        <v>28.64734623184315</v>
       </c>
       <c r="X6" t="n">
         <v>-65630.98061932939</v>
@@ -1474,7 +1444,7 @@
         <v>8.545114213889972e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>228.21</v>
+        <v>2761.7199542041</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000001421993e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>87.72752814586424</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 25.200x + -56895.362</t>
-        </is>
+      <c r="W7" t="n">
+        <v>25.19975443342456</v>
       </c>
       <c r="X7" t="n">
         <v>-56895.36174195277</v>
@@ -1526,7 +1494,7 @@
         <v>7.847866497245891e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>221.3699999999999</v>
+        <v>2733.489103789219</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000706327e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>87.3188431259309</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 21.354x + -47327.054</t>
-        </is>
+      <c r="W8" t="n">
+        <v>21.35419690208468</v>
       </c>
       <c r="X8" t="n">
         <v>-47327.05424900413</v>
@@ -1578,7 +1544,7 @@
         <v>3.735499326061547e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>236.6199999999999</v>
+        <v>2707.103229311077</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000070395e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>87.42226254303172</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 22.212x + -48963.474</t>
-        </is>
+      <c r="W9" t="n">
+        <v>22.21215999573946</v>
       </c>
       <c r="X9" t="n">
         <v>-48963.4742857961</v>
@@ -1630,7 +1594,7 @@
         <v>2.43947090069047e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>221.1100000000001</v>
+        <v>2683.432122226611</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000034529e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>87.36773313344881</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 21.751x + -47516.066</t>
-        </is>
+      <c r="W10" t="n">
+        <v>21.75139013265514</v>
       </c>
       <c r="X10" t="n">
         <v>-47516.06608020557</v>
@@ -1682,7 +1644,7 @@
         <v>6.328699988977746e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>216.0799999999999</v>
+        <v>2662.023493568865</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000004330382e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>87.39339591616216</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 21.966x + -47657.550</t>
-        </is>
+      <c r="W11" t="n">
+        <v>21.96583911005257</v>
       </c>
       <c r="X11" t="n">
         <v>-47657.55043392426</v>
@@ -1734,7 +1694,7 @@
         <v>6.709030642352584e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>212.3399999999997</v>
+        <v>2641.899796822844</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000022788e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>87.14813825231388</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 20.074x + -43038.867</t>
-        </is>
+      <c r="W12" t="n">
+        <v>20.07406396717945</v>
       </c>
       <c r="X12" t="n">
         <v>-43038.86747210872</v>
@@ -1786,7 +1744,7 @@
         <v>5.241992900452892e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>221.5299999999997</v>
+        <v>2623.157901990913</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000379033e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>87.51984458494603</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 23.087x + -49505.182</t>
-        </is>
+      <c r="W13" t="n">
+        <v>23.08725841649229</v>
       </c>
       <c r="X13" t="n">
         <v>-49505.18196301869</v>
@@ -1838,7 +1794,7 @@
         <v>5.842324758274235e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>207.5800000000004</v>
+        <v>2604.469220382614</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000140426e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>87.30288265207135</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 21.228x + -44963.832</t>
-        </is>
+      <c r="W14" t="n">
+        <v>21.2276459961044</v>
       </c>
       <c r="X14" t="n">
         <v>-44963.83211327767</v>
@@ -1890,7 +1844,7 @@
         <v>1.030577065505473e-07</v>
       </c>
       <c r="Z14" t="n">
-        <v>216.77</v>
+        <v>2584.732100695554</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000003581505e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>38.01064789776142</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 0.782x + 243.587</t>
-        </is>
+      <c r="W15" t="n">
+        <v>0.7815849494580217</v>
       </c>
       <c r="X15" t="n">
         <v>243.5865482251355</v>
@@ -1942,7 +1894,7 @@
         <v>2.126298726775029e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>198.8800000000001</v>
+        <v>2563.776064966605</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000002325532e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>-44.80258112615174</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = -0.993x + 4049.962</t>
-        </is>
+      <c r="W16" t="n">
+        <v>-0.9931324171214956</v>
       </c>
       <c r="X16" t="n">
         <v>4049.962157504391</v>
@@ -1994,7 +1944,7 @@
         <v>5.236013066885747e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>202.8299999999999</v>
+        <v>2542.982383236801</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000321449e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>84.32949883650566</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 10.071x + -19840.830</t>
-        </is>
+      <c r="W17" t="n">
+        <v>10.07117145654693</v>
       </c>
       <c r="X17" t="n">
         <v>-19840.82956715482</v>
@@ -2046,7 +1994,7 @@
         <v>4.1592652297334e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>200.4099999999999</v>
+        <v>2522.901797562265</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000049537e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>-83.05180615951504</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = -8.206x + 19519.920</t>
-        </is>
+      <c r="W18" t="n">
+        <v>-8.205677411610846</v>
       </c>
       <c r="X18" t="n">
         <v>19519.92006611818</v>
@@ -2098,7 +2044,7 @@
         <v>1.126577163053326e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>189.79</v>
+        <v>2500.26313363378</v>
       </c>
       <c r="AA18" t="n">
         <v>1.00000000036226e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>-81.85952438131247</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = -6.991x + 16628.510</t>
-        </is>
+      <c r="W19" t="n">
+        <v>-6.990959076751902</v>
       </c>
       <c r="X19" t="n">
         <v>16628.51016872962</v>
@@ -2150,7 +2094,7 @@
         <v>3.262996572198026e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>196.8599999999999</v>
+        <v>2478.894211949943</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000344816e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>-80.39838400769001</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = -5.911x + 14239.270</t>
-        </is>
+      <c r="W20" t="n">
+        <v>-5.911341075263284</v>
       </c>
       <c r="X20" t="n">
         <v>14239.27019081562</v>
@@ -2202,7 +2144,7 @@
         <v>2.226941585207567e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>195.2800000000002</v>
+        <v>2457.371874773199</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000338555e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>-63.09955057614199</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = -1.971x + 5873.204</t>
-        </is>
+      <c r="W21" t="n">
+        <v>-1.971069359565729</v>
       </c>
       <c r="X21" t="n">
         <v>5873.204082927272</v>
@@ -2254,7 +2194,7 @@
         <v>3.197617281222268e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>196.1500000000001</v>
+        <v>2435.480744332806</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000135527e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>-69.62958949863966</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = -2.693x + 7324.253</t>
-        </is>
+      <c r="W22" t="n">
+        <v>-2.693175278695681</v>
       </c>
       <c r="X22" t="n">
         <v>7324.253338262391</v>
@@ -2306,7 +2244,7 @@
         <v>2.988510286001275e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>194.5799999999999</v>
+        <v>2413.714908084446</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000435508e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>87.40808114583562</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 22.090x + -57612.375</t>
-        </is>
+      <c r="W2" t="n">
+        <v>22.09046401895205</v>
       </c>
       <c r="X2" t="n">
         <v>-57612.37529112391</v>
@@ -2504,7 +2440,7 @@
         <v>3.935639218335637e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>961.6500000000001</v>
+        <v>3124.097576951988</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000353349e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>88.23777067129679</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 32.503x + -80256.391</t>
-        </is>
+      <c r="W3" t="n">
+        <v>32.5029839488345</v>
       </c>
       <c r="X3" t="n">
         <v>-80256.39060911685</v>
@@ -2556,7 +2490,7 @@
         <v>1.997280937048963e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>372.3099999999999</v>
+        <v>2980.686290916395</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000160544e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>87.34884385921778</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 21.596x + -51535.258</t>
-        </is>
+      <c r="W4" t="n">
+        <v>21.5961941619497</v>
       </c>
       <c r="X4" t="n">
         <v>-51535.25844373357</v>
@@ -2608,7 +2540,7 @@
         <v>6.577927479512069e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>226.3299999999999</v>
+        <v>2926.924640818975</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000092494e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>82.20491213081031</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 7.305x + -15732.085</t>
-        </is>
+      <c r="W5" t="n">
+        <v>7.304835606516962</v>
       </c>
       <c r="X5" t="n">
         <v>-15732.08497911205</v>
@@ -2660,7 +2590,7 @@
         <v>1.068582775005646e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>224.54</v>
+        <v>2889.730856509508</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000130792e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>10.14312710119752</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 0.179x + 1610.646</t>
-        </is>
+      <c r="W6" t="n">
+        <v>0.1789038273068075</v>
       </c>
       <c r="X6" t="n">
         <v>1610.646372966079</v>
@@ -2712,7 +2640,7 @@
         <v>8.294856708039462e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>227.8400000000001</v>
+        <v>2857.708439011398</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000141992e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>-82.04743849485872</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = -7.158x + 19151.648</t>
-        </is>
+      <c r="W7" t="n">
+        <v>-7.158369266781004</v>
       </c>
       <c r="X7" t="n">
         <v>19151.64821697749</v>
@@ -2764,7 +2690,7 @@
         <v>6.790135062023177e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>223.7800000000002</v>
+        <v>2827.965888007551</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000168204e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>82.6468918039423</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 7.749x + -17379.515</t>
-        </is>
+      <c r="W8" t="n">
+        <v>7.749223325492801</v>
       </c>
       <c r="X8" t="n">
         <v>-17379.51475196866</v>
@@ -2816,7 +2740,7 @@
         <v>2.024899505934977e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>206.4699999999998</v>
+        <v>2799.830358196889</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000858937e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>83.03672626642278</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 8.188x + -18265.966</t>
-        </is>
+      <c r="W9" t="n">
+        <v>8.187731310842549</v>
       </c>
       <c r="X9" t="n">
         <v>-18265.96631159286</v>
@@ -2868,7 +2790,7 @@
         <v>6.898674031924192e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>197.3400000000001</v>
+        <v>2772.536949719294</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000152786e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>82.79216215529004</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 7.907x + -17429.167</t>
-        </is>
+      <c r="W10" t="n">
+        <v>7.907116044594668</v>
       </c>
       <c r="X10" t="n">
         <v>-17429.16732465491</v>
@@ -2920,7 +2840,7 @@
         <v>1.021404550313151e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>198.75</v>
+        <v>2746.10559054189</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000450889e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>82.56310257964626</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 7.661x + -16688.274</t>
-        </is>
+      <c r="W11" t="n">
+        <v>7.660943623567285</v>
       </c>
       <c r="X11" t="n">
         <v>-16688.27394000787</v>
@@ -2972,7 +2890,7 @@
         <v>3.680692204652808e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>203.73</v>
+        <v>2720.32384039339</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000717e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>82.23306190620703</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 7.332x + -15769.062</t>
-        </is>
+      <c r="W12" t="n">
+        <v>7.331639520279781</v>
       </c>
       <c r="X12" t="n">
         <v>-15769.0620547541</v>
@@ -3024,7 +2940,7 @@
         <v>8.944154481043606e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>205.8599999999997</v>
+        <v>2694.545242986159</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000052814e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>82.50606800820141</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 7.602x + -16253.522</t>
-        </is>
+      <c r="W13" t="n">
+        <v>7.601975363329343</v>
       </c>
       <c r="X13" t="n">
         <v>-16253.52181116075</v>
@@ -3076,7 +2990,7 @@
         <v>5.449466072159275e-14</v>
       </c>
       <c r="Z13" t="n">
-        <v>195.0100000000002</v>
+        <v>2669.333430884795</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000209167e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>82.75603483147846</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 7.867x + -16715.067</t>
-        </is>
+      <c r="W14" t="n">
+        <v>7.867261230982351</v>
       </c>
       <c r="X14" t="n">
         <v>-16715.06673198813</v>
@@ -3128,7 +3040,7 @@
         <v>1.609665042640764e-07</v>
       </c>
       <c r="Z14" t="n">
-        <v>187.2000000000003</v>
+        <v>2644.386817820363</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000003700823e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>82.57422742846562</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 7.673x + -16117.769</t>
-        </is>
+      <c r="W15" t="n">
+        <v>7.672550623320563</v>
       </c>
       <c r="X15" t="n">
         <v>-16117.76919812736</v>
@@ -3180,7 +3090,7 @@
         <v>2.756212343463959e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>187.23</v>
+        <v>2619.210287062468</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000114633e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>82.31096173310172</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 7.407x + -15374.215</t>
-        </is>
+      <c r="W16" t="n">
+        <v>7.406831651867853</v>
       </c>
       <c r="X16" t="n">
         <v>-15374.21500809582</v>
@@ -3232,7 +3140,7 @@
         <v>5.496960890675319e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>191.4499999999998</v>
+        <v>2594.29855900179</v>
       </c>
       <c r="AA16" t="n">
         <v>1.00000000642978e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>82.39128011185888</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 7.486x + -15401.710</t>
-        </is>
+      <c r="W17" t="n">
+        <v>7.4859605965272</v>
       </c>
       <c r="X17" t="n">
         <v>-15401.70994721583</v>
@@ -3284,7 +3190,7 @@
         <v>1.389098823756533e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>187.3000000000002</v>
+        <v>2569.430394762981</v>
       </c>
       <c r="AA17" t="n">
         <v>1.00000000006778e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>82.07863491517216</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 7.187x + -14606.284</t>
-        </is>
+      <c r="W18" t="n">
+        <v>7.186925443500214</v>
       </c>
       <c r="X18" t="n">
         <v>-14606.28364334215</v>
@@ -3336,7 +3240,7 @@
         <v>9.446120653530682e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>190.9300000000003</v>
+        <v>2545.384582301588</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000001617385e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>82.01049780865009</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 7.125x + -14335.545</t>
-        </is>
+      <c r="W19" t="n">
+        <v>7.1248415104164</v>
       </c>
       <c r="X19" t="n">
         <v>-14335.54501288281</v>
@@ -3388,7 +3290,7 @@
         <v>1.198463456871953e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>188.9700000000003</v>
+        <v>2521.233104624443</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000075597e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>82.03847132861051</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 7.150x + -14260.049</t>
-        </is>
+      <c r="W20" t="n">
+        <v>7.150202160846341</v>
       </c>
       <c r="X20" t="n">
         <v>-14260.04878831147</v>
@@ -3440,7 +3340,7 @@
         <v>2.231359391734711e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>185.48</v>
+        <v>2497.263868741764</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000010916e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>82.58977545658749</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 7.689x + -15288.695</t>
-        </is>
+      <c r="W21" t="n">
+        <v>7.688830565337469</v>
       </c>
       <c r="X21" t="n">
         <v>-15288.69473552221</v>
@@ -3492,7 +3390,7 @@
         <v>2.990481872477043e-11</v>
       </c>
       <c r="Z21" t="n">
-        <v>171.3</v>
+        <v>2474.079850377143</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000005916e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>82.28823448463952</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 7.385x + -14503.358</t>
-        </is>
+      <c r="W22" t="n">
+        <v>7.384738378755111</v>
       </c>
       <c r="X22" t="n">
         <v>-14503.35821236979</v>
@@ -3544,7 +3440,7 @@
         <v>3.640809110827982e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>174.8799999999999</v>
+        <v>2450.656159830546</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000089927e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.79996252394287</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.988x + -33913.173</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.98807051125864</v>
       </c>
       <c r="X2" t="n">
         <v>-33913.17346430986</v>
@@ -3742,7 +3636,7 @@
         <v>1.335479054312013e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1973.24</v>
+        <v>3724.855063932422</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000185512e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>87.39422175177619</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 21.973x + -59676.987</t>
-        </is>
+      <c r="W3" t="n">
+        <v>21.97281024128023</v>
       </c>
       <c r="X3" t="n">
         <v>-59676.98683048016</v>
@@ -3794,7 +3686,7 @@
         <v>4.15787692821595e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>965.1299999999997</v>
+        <v>3272.142500169624</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000007171e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>88.30846062536317</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 33.862x + -88793.058</t>
-        </is>
+      <c r="W4" t="n">
+        <v>33.86213351235661</v>
       </c>
       <c r="X4" t="n">
         <v>-88793.05783803968</v>
@@ -3846,7 +3736,7 @@
         <v>5.535052391839412e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>491.8200000000002</v>
+        <v>3149.705858993187</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000011272e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>88.14230204396958</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 30.832x + -78445.743</t>
-        </is>
+      <c r="W5" t="n">
+        <v>30.83154641646207</v>
       </c>
       <c r="X5" t="n">
         <v>-78445.74332960373</v>
@@ -3898,7 +3786,7 @@
         <v>2.007370219226665e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>325.9099999999999</v>
+        <v>3082.660736637521</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000001852e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>87.86450806269114</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 26.818x + -66733.285</t>
-        </is>
+      <c r="W6" t="n">
+        <v>26.81782363821599</v>
       </c>
       <c r="X6" t="n">
         <v>-66733.2851430825</v>
@@ -3950,7 +3836,7 @@
         <v>1.136330487606972e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>242.1399999999999</v>
+        <v>3026.970313126165</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000149396e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.64282388502379</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.047x + -40833.412</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.04712313695595</v>
       </c>
       <c r="X7" t="n">
         <v>-40833.41244077377</v>
@@ -4002,7 +3886,7 @@
         <v>2.773676998252171e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>246.9400000000001</v>
+        <v>2975.443512917976</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000152931e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>85.03898339160779</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.520x + -26478.520</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.52032484958182</v>
       </c>
       <c r="X8" t="n">
         <v>-26478.52027116762</v>
@@ -4054,7 +3936,7 @@
         <v>1.706624408938204e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>237.3500000000004</v>
+        <v>2928.207222118213</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000125036e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>77.96061947910844</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 4.689x + -9327.409</t>
-        </is>
+      <c r="W9" t="n">
+        <v>4.688781213721339</v>
       </c>
       <c r="X9" t="n">
         <v>-9327.408867039567</v>
@@ -4106,7 +3986,7 @@
         <v>9.010949242543768e-14</v>
       </c>
       <c r="Z9" t="n">
-        <v>224.1700000000001</v>
+        <v>2884.750338449863</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000026676e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>-24.75953327825828</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = -0.461x + 3264.069</t>
-        </is>
+      <c r="W10" t="n">
+        <v>-0.4612080787200517</v>
       </c>
       <c r="X10" t="n">
         <v>3264.069165949725</v>
@@ -4158,7 +4036,7 @@
         <v>7.975261471801174e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>216.2600000000002</v>
+        <v>2844.982276807901</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000002224216e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>-78.31701812655305</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = -4.836x + 13687.387</t>
-        </is>
+      <c r="W11" t="n">
+        <v>-4.836050560703918</v>
       </c>
       <c r="X11" t="n">
         <v>13687.38722258985</v>
@@ -4210,7 +4086,7 @@
         <v>4.682352462606695e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>208.1100000000001</v>
+        <v>2807.938141447114</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000023074e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>88.10408525269288</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 30.210x + -78594.548</t>
-        </is>
+      <c r="W2" t="n">
+        <v>30.20962105852097</v>
       </c>
       <c r="X2" t="n">
         <v>-78594.54834015714</v>
@@ -4408,7 +4282,7 @@
         <v>2.503713272876611e-14</v>
       </c>
       <c r="Z2" t="n">
-        <v>635.7600000000002</v>
+        <v>3100.80941084509</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000923e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>88.00266796165695</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 28.675x + -70461.339</t>
-        </is>
+      <c r="W3" t="n">
+        <v>28.67453559113178</v>
       </c>
       <c r="X3" t="n">
         <v>-70461.33876678524</v>
@@ -4460,7 +4332,7 @@
         <v>5.232455212980571e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>255.6599999999999</v>
+        <v>2978.445253380965</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000002362421e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>86.09871374465523</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.664x + -34260.851</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.66367803259995</v>
       </c>
       <c r="X4" t="n">
         <v>-34260.85119992684</v>
@@ -4512,7 +4382,7 @@
         <v>3.334338909097358e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>241.6899999999996</v>
+        <v>2926.702183851483</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000626478e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>78.10228108292959</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 4.746x + -9528.855</t>
-        </is>
+      <c r="W5" t="n">
+        <v>4.746276572635655</v>
       </c>
       <c r="X5" t="n">
         <v>-9528.855288247358</v>
@@ -4564,7 +4432,7 @@
         <v>3.341261710476093e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>228.3899999999999</v>
+        <v>2889.113656267828</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000459937e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>-69.68331444941018</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = -2.701x + 8611.959</t>
-        </is>
+      <c r="W6" t="n">
+        <v>-2.700933705203028</v>
       </c>
       <c r="X6" t="n">
         <v>8611.958834524094</v>
@@ -4616,7 +4482,7 @@
         <v>2.121758090205614e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>222.98</v>
+        <v>2856.524373585025</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000139599e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>-84.17006358102275</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = -9.794x + 25634.435</t>
-        </is>
+      <c r="W7" t="n">
+        <v>-9.793916039797647</v>
       </c>
       <c r="X7" t="n">
         <v>25634.43472015978</v>
@@ -4668,7 +4532,7 @@
         <v>3.727928214626339e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>214.3200000000002</v>
+        <v>2825.827724083491</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000130665e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>-84.17881511505529</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = -9.809x + 25320.983</t>
-        </is>
+      <c r="W8" t="n">
+        <v>-9.808742199680122</v>
       </c>
       <c r="X8" t="n">
         <v>25320.98282286995</v>
@@ -4720,7 +4582,7 @@
         <v>1.024607990855834e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>216.4499999999998</v>
+        <v>2796.404053660201</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000002077736e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>82.72326703628727</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 7.831x + -17405.608</t>
-        </is>
+      <c r="W9" t="n">
+        <v>7.831453004417508</v>
       </c>
       <c r="X9" t="n">
         <v>-17405.60786540977</v>
@@ -4772,7 +4632,7 @@
         <v>1.457729395873112e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>211.96</v>
+        <v>2767.214036768366</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000059899e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>82.2923416967986</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 7.389x + -16172.143</t>
-        </is>
+      <c r="W10" t="n">
+        <v>7.388721433240787</v>
       </c>
       <c r="X10" t="n">
         <v>-16172.14336217859</v>
@@ -4824,7 +4682,7 @@
         <v>1.79788051483419e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>218.5500000000002</v>
+        <v>2738.675985261965</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000003111544e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>82.32897058829273</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 7.424x + -16097.178</t>
-        </is>
+      <c r="W11" t="n">
+        <v>7.424430556842815</v>
       </c>
       <c r="X11" t="n">
         <v>-16097.17823252997</v>
@@ -4876,7 +4732,7 @@
         <v>6.925899905588307e-14</v>
       </c>
       <c r="Z11" t="n">
-        <v>212.9499999999998</v>
+        <v>2710.199659339391</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000013651e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>83.32285369878258</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 8.542x + -18538.407</t>
-        </is>
+      <c r="W12" t="n">
+        <v>8.541996977027232</v>
       </c>
       <c r="X12" t="n">
         <v>-18538.40743180953</v>
@@ -4928,7 +4782,7 @@
         <v>8.698792079256109e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>189.8499999999999</v>
+        <v>2682.979306390135</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000019037e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>82.36623349893193</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 7.461x + -15863.743</t>
-        </is>
+      <c r="W13" t="n">
+        <v>7.461107298526787</v>
       </c>
       <c r="X13" t="n">
         <v>-15863.74319316536</v>
@@ -4980,7 +4832,7 @@
         <v>1.294911995502573e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>205.5500000000002</v>
+        <v>2655.560599979192</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000029963e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>83.07434174599595</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 8.233x + -17467.628</t>
-        </is>
+      <c r="W14" t="n">
+        <v>8.232641241472745</v>
       </c>
       <c r="X14" t="n">
         <v>-17467.62813982737</v>
@@ -5032,7 +4882,7 @@
         <v>5.02898540932662e-14</v>
       </c>
       <c r="Z14" t="n">
-        <v>188.5699999999997</v>
+        <v>2628.621820032761</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000496e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>82.72754687888354</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 7.836x + -16404.743</t>
-        </is>
+      <c r="W15" t="n">
+        <v>7.836111738943879</v>
       </c>
       <c r="X15" t="n">
         <v>-16404.74254993359</v>
@@ -5084,7 +4932,7 @@
         <v>2.129029427930446e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>190.8999999999996</v>
+        <v>2602.193960973588</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000008681e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>83.11804821964103</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 8.285x + -17247.905</t>
-        </is>
+      <c r="W16" t="n">
+        <v>8.28543693889398</v>
       </c>
       <c r="X16" t="n">
         <v>-17247.90450462234</v>
@@ -5136,7 +4982,7 @@
         <v>1.467782092261909e-07</v>
       </c>
       <c r="Z16" t="n">
-        <v>183.02</v>
+        <v>2575.984614183384</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000003920471e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>82.54717801170752</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 7.644x + -15655.706</t>
-        </is>
+      <c r="W17" t="n">
+        <v>7.644388848204028</v>
       </c>
       <c r="X17" t="n">
         <v>-15655.70638275604</v>
@@ -5188,7 +5032,7 @@
         <v>1.655215230294291e-07</v>
       </c>
       <c r="Z17" t="n">
-        <v>191.4700000000003</v>
+        <v>2549.524310452643</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000001989374e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>82.53719370838013</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 7.634x + -15475.953</t>
-        </is>
+      <c r="W18" t="n">
+        <v>7.634045252253546</v>
       </c>
       <c r="X18" t="n">
         <v>-15475.9528379699</v>
@@ -5240,7 +5082,7 @@
         <v>1.294975845472857e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>190.0099999999998</v>
+        <v>2522.962256241677</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000003885e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>81.78827322698132</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 6.929x + -13788.508</t>
-        </is>
+      <c r="W19" t="n">
+        <v>6.92947253069374</v>
       </c>
       <c r="X19" t="n">
         <v>-13788.50815160075</v>
@@ -5292,7 +5132,7 @@
         <v>7.333281535670074e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>202.9299999999998</v>
+        <v>2496.178754784095</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000080488e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>82.94100422387126</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 8.076x + -16107.919</t>
-        </is>
+      <c r="W20" t="n">
+        <v>8.075594846681611</v>
       </c>
       <c r="X20" t="n">
         <v>-16107.91924259595</v>
@@ -5344,7 +5182,7 @@
         <v>1.963439150436547e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>175.3799999999999</v>
+        <v>2469.600454719319</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000008409e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>82.68857782797556</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 7.794x + -15340.878</t>
-        </is>
+      <c r="W21" t="n">
+        <v>7.793892956118331</v>
       </c>
       <c r="X21" t="n">
         <v>-15340.87843996631</v>
@@ -5396,7 +5232,7 @@
         <v>7.457985090775765e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>180.6399999999999</v>
+        <v>2442.754711392271</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000080993e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>82.33801949786105</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 7.433x + -14424.350</t>
-        </is>
+      <c r="W22" t="n">
+        <v>7.433304519653019</v>
       </c>
       <c r="X22" t="n">
         <v>-14424.35012449286</v>
@@ -5448,7 +5282,7 @@
         <v>7.38743871202838e-12</v>
       </c>
       <c r="Z22" t="n">
-        <v>182.6900000000003</v>
+        <v>2415.841176766926</v>
       </c>
       <c r="AA22" t="n">
         <v>1.0000000000519e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>85.20881726625123</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.931x + -37181.958</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.93070085217297</v>
       </c>
       <c r="X2" t="n">
         <v>-37181.95774067543</v>
@@ -5646,7 +5478,7 @@
         <v>9.489649772884224e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1809.8</v>
+        <v>3707.894080356654</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000006821e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>87.68078154358194</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 24.691x + -66059.701</t>
-        </is>
+      <c r="W3" t="n">
+        <v>24.6912849006731</v>
       </c>
       <c r="X3" t="n">
         <v>-66059.70141254611</v>
@@ -5698,7 +5528,7 @@
         <v>5.517787105115126e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>796.6599999999999</v>
+        <v>3218.210291151423</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001999e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>88.24301206018693</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 32.600x + -83852.576</t>
-        </is>
+      <c r="W4" t="n">
+        <v>32.60000687122984</v>
       </c>
       <c r="X4" t="n">
         <v>-83852.57578949022</v>
@@ -5750,7 +5578,7 @@
         <v>6.276089341358065e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>441.6199999999999</v>
+        <v>3095.380351498084</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000005625e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>88.06285369564924</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.566x + -74013.201</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.56614394701412</v>
       </c>
       <c r="X5" t="n">
         <v>-74013.20132172584</v>
@@ -5802,7 +5628,7 @@
         <v>6.01561900948159e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>294.9400000000001</v>
+        <v>3033.146864149631</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000004289e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>87.46376315789631</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 22.576x + -55004.404</t>
-        </is>
+      <c r="W6" t="n">
+        <v>22.57610603262578</v>
       </c>
       <c r="X6" t="n">
         <v>-55004.40421502014</v>
@@ -5854,7 +5678,7 @@
         <v>9.5955133763302e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>253.73</v>
+        <v>2983.824621989874</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000004206e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>86.66071576043031</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.139x + -40656.913</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.1386704082084</v>
       </c>
       <c r="X7" t="n">
         <v>-40656.91250923482</v>
@@ -5906,7 +5728,7 @@
         <v>1.415628643110699e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>229.8500000000004</v>
+        <v>2938.874907182456</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000029043e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>84.41402179195856</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.225x + -23038.004</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.22455327739217</v>
       </c>
       <c r="X8" t="n">
         <v>-23038.00394133735</v>
@@ -5958,7 +5778,7 @@
         <v>3.368461865905526e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>229.3199999999997</v>
+        <v>2897.045874698175</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000001490659e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>79.19560156564935</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 5.240x + -10650.117</t>
-        </is>
+      <c r="W9" t="n">
+        <v>5.239998094337719</v>
       </c>
       <c r="X9" t="n">
         <v>-10650.116553725</v>
@@ -6010,7 +5828,7 @@
         <v>1.976068441226693e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>231.6099999999997</v>
+        <v>2857.294100960475</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000002348099e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>-21.92849277603647</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = -0.403x + 3080.166</t>
-        </is>
+      <c r="W10" t="n">
+        <v>-0.4025751942797905</v>
       </c>
       <c r="X10" t="n">
         <v>3080.166053908959</v>
@@ -6062,7 +5878,7 @@
         <v>1.647331413136195e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>216.9900000000002</v>
+        <v>2820.477322753758</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000497801e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>-75.28400969379423</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = -3.807x + 11047.615</t>
-        </is>
+      <c r="W11" t="n">
+        <v>-3.807443826322291</v>
       </c>
       <c r="X11" t="n">
         <v>11047.61525274087</v>
@@ -6114,7 +5928,7 @@
         <v>2.453884835213759e-13</v>
       </c>
       <c r="Z11" t="n">
-        <v>220.3699999999999</v>
+        <v>2785.960762766516</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000097333e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>87.26965780233698</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 20.969x + -54464.963</t>
-        </is>
+      <c r="W2" t="n">
+        <v>20.96894774203287</v>
       </c>
       <c r="X2" t="n">
         <v>-54464.96287665951</v>
@@ -6312,7 +6124,7 @@
         <v>6.826779095373975e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>962.1799999999998</v>
+        <v>3112.206535620435</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000068123e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>88.25526778769634</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 32.829x + -80669.629</t>
-        </is>
+      <c r="W3" t="n">
+        <v>32.82914605098639</v>
       </c>
       <c r="X3" t="n">
         <v>-80669.62904581991</v>
@@ -6364,7 +6174,7 @@
         <v>4.514337441707183e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>370.8200000000002</v>
+        <v>2953.37503172122</v>
       </c>
       <c r="AA3" t="n">
         <v>1.0000000037225e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>87.76978611891255</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 25.678x + -61257.100</t>
-        </is>
+      <c r="W4" t="n">
+        <v>25.6777344837205</v>
       </c>
       <c r="X4" t="n">
         <v>-61257.09970802224</v>
@@ -6416,7 +6224,7 @@
         <v>3.668005610458705e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>238.8199999999997</v>
+        <v>2898.741819339024</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000018462e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>86.51862535185441</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.438x + -37930.709</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.43754459421508</v>
       </c>
       <c r="X5" t="n">
         <v>-37930.7087741549</v>
@@ -6468,7 +6274,7 @@
         <v>3.935896412075662e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>222.1800000000003</v>
+        <v>2862.201244899916</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000016909e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>83.72447086690875</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.093x + -19817.841</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.093492854115269</v>
       </c>
       <c r="X6" t="n">
         <v>-19817.84052044459</v>
@@ -6520,7 +6324,7 @@
         <v>1.94204070804713e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>234.5299999999997</v>
+        <v>2829.966957799847</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000001365048e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>73.19361397958819</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 3.311x + -5842.658</t>
-        </is>
+      <c r="W7" t="n">
+        <v>3.310826101955204</v>
       </c>
       <c r="X7" t="n">
         <v>-5842.658061940697</v>
@@ -6572,7 +6374,7 @@
         <v>2.830260427125439e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>226.0800000000004</v>
+        <v>2800.232420436188</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000016682e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>-40.3947259605872</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = -0.851x + 4033.184</t>
-        </is>
+      <c r="W8" t="n">
+        <v>-0.8509079992515665</v>
       </c>
       <c r="X8" t="n">
         <v>4033.184208893517</v>
@@ -6624,7 +6424,7 @@
         <v>3.189804074923447e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>221.0700000000002</v>
+        <v>2772.05319856209</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000106446e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>-77.34308860832034</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = -4.453x + 12418.750</t>
-        </is>
+      <c r="W9" t="n">
+        <v>-4.452961774792365</v>
       </c>
       <c r="X9" t="n">
         <v>12418.75004068838</v>
@@ -6676,7 +6474,7 @@
         <v>361.9679600828741</v>
       </c>
       <c r="Z9" t="n">
-        <v>216.3099999999999</v>
+        <v>6900.748144565289</v>
       </c>
       <c r="AA9" t="n">
         <v>1.211874841429044e-06</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>-82.75673564432105</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = -7.868x + 20229.592</t>
-        </is>
+      <c r="W10" t="n">
+        <v>-7.868030589990516</v>
       </c>
       <c r="X10" t="n">
         <v>20229.59207957098</v>
@@ -6728,7 +6524,7 @@
         <v>359.2523461034974</v>
       </c>
       <c r="Z10" t="n">
-        <v>211.9500000000003</v>
+        <v>6834.244800307194</v>
       </c>
       <c r="AA10" t="n">
         <v>1.217394013992102e-06</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>-85.45352960590004</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = -12.576x + 30999.364</t>
-        </is>
+      <c r="W11" t="n">
+        <v>-12.57579365416156</v>
       </c>
       <c r="X11" t="n">
         <v>30999.36380989699</v>
@@ -6780,7 +6574,7 @@
         <v>357.2408689988711</v>
       </c>
       <c r="Z11" t="n">
-        <v>200.6599999999999</v>
+        <v>6775.33087665479</v>
       </c>
       <c r="AA11" t="n">
         <v>1.223676434887456e-06</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>-84.77772390229033</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = -10.941x + 26805.845</t>
-        </is>
+      <c r="W12" t="n">
+        <v>-10.94102024882034</v>
       </c>
       <c r="X12" t="n">
         <v>26805.84484575409</v>
@@ -6832,7 +6624,7 @@
         <v>1.022873543275556e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>210.29</v>
+        <v>2673.595039786875</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000125491e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>82.6544099938159</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 7.757x + -16552.665</t>
-        </is>
+      <c r="W13" t="n">
+        <v>7.757242348223084</v>
       </c>
       <c r="X13" t="n">
         <v>-16552.66532110814</v>
@@ -6884,7 +6674,7 @@
         <v>4.55369299566428e-14</v>
       </c>
       <c r="Z13" t="n">
-        <v>206.0599999999999</v>
+        <v>2651.228810142732</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000079327e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>82.44241758664617</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 7.537x + -15918.011</t>
-        </is>
+      <c r="W14" t="n">
+        <v>7.537211873363496</v>
       </c>
       <c r="X14" t="n">
         <v>-15918.01141821042</v>
@@ -6936,7 +6724,7 @@
         <v>8.841104674228749e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>208.9699999999998</v>
+        <v>2629.495411274605</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000677394e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>83.03310516837367</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 8.183x + -17260.476</t>
-        </is>
+      <c r="W15" t="n">
+        <v>8.183433467878601</v>
       </c>
       <c r="X15" t="n">
         <v>-17260.47574685215</v>
@@ -6988,7 +6774,7 @@
         <v>3.299561483160774e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>194.9899999999998</v>
+        <v>2608.163674743105</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000339211e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>82.60768981812728</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 7.708x + -16043.517</t>
-        </is>
+      <c r="W16" t="n">
+        <v>7.707672668899513</v>
       </c>
       <c r="X16" t="n">
         <v>-16043.51675191806</v>
@@ -7040,7 +6824,7 @@
         <v>3.511844908860799e-14</v>
       </c>
       <c r="Z16" t="n">
-        <v>202.0999999999999</v>
+        <v>2586.717452900827</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000001428e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>82.63848551794553</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 7.740x + -15988.568</t>
-        </is>
+      <c r="W17" t="n">
+        <v>7.740276334518517</v>
       </c>
       <c r="X17" t="n">
         <v>-15988.56842160121</v>
@@ -7092,7 +6874,7 @@
         <v>4.959987999328106e-15</v>
       </c>
       <c r="Z17" t="n">
-        <v>198.5599999999999</v>
+        <v>2565.091971097781</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000049384e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>82.26139441669933</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 7.359x + -15020.971</t>
-        </is>
+      <c r="W18" t="n">
+        <v>7.358813126005243</v>
       </c>
       <c r="X18" t="n">
         <v>-15020.97071327513</v>
@@ -7144,7 +6924,7 @@
         <v>6.980759872087457e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>202.6599999999999</v>
+        <v>2543.337884805379</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000470609e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>82.65286823427783</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 7.756x + -15768.304</t>
-        </is>
+      <c r="W19" t="n">
+        <v>7.755596552276817</v>
       </c>
       <c r="X19" t="n">
         <v>-15768.30395494532</v>
@@ -7196,7 +6974,7 @@
         <v>8.488568489960556e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>193.6599999999999</v>
+        <v>2521.96677157164</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000001431337e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>82.6918934023077</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 7.797x + -15725.084</t>
-        </is>
+      <c r="W20" t="n">
+        <v>7.797467595315508</v>
       </c>
       <c r="X20" t="n">
         <v>-15725.08428232545</v>
@@ -7248,7 +7024,7 @@
         <v>9.700793949221654e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>190.1199999999999</v>
+        <v>2499.991973103609</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000115598e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>82.9750707414034</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 8.115x + -16279.860</t>
-        </is>
+      <c r="W21" t="n">
+        <v>8.115154580887042</v>
       </c>
       <c r="X21" t="n">
         <v>-16279.86037098733</v>
@@ -7300,7 +7074,7 @@
         <v>2.322849944898881e-07</v>
       </c>
       <c r="Z21" t="n">
-        <v>183.3100000000002</v>
+        <v>2478.3568299565</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000122447e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>82.74285413621382</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 7.853x + -15583.050</t>
-        </is>
+      <c r="W22" t="n">
+        <v>7.85281886875032</v>
       </c>
       <c r="X22" t="n">
         <v>-15583.04995540379</v>
@@ -7352,7 +7124,7 @@
         <v>1.226996704798019e-06</v>
       </c>
       <c r="Z22" t="n">
-        <v>185.9299999999998</v>
+        <v>2456.830313811909</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000651405e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>85.48188522029676</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.655x + -38450.908</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.65505037353319</v>
       </c>
       <c r="X2" t="n">
         <v>-38450.90750279372</v>
@@ -7550,7 +7320,7 @@
         <v>4.07231523396653e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1673.63</v>
+        <v>3614.404843408442</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000011803e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>87.88601646475465</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 27.091x + -70861.417</t>
-        </is>
+      <c r="W3" t="n">
+        <v>27.0909290628736</v>
       </c>
       <c r="X3" t="n">
         <v>-70861.41668822135</v>
@@ -7602,7 +7370,7 @@
         <v>8.497936375118675e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>679.6599999999999</v>
+        <v>3136.862093895567</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000032086e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>88.11393833010669</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 30.368x + -76005.015</t>
-        </is>
+      <c r="W4" t="n">
+        <v>30.36755574589671</v>
       </c>
       <c r="X4" t="n">
         <v>-76005.01470573906</v>
@@ -7654,7 +7420,7 @@
         <v>5.42339174985863e-15</v>
       </c>
       <c r="Z4" t="n">
-        <v>415.0699999999997</v>
+        <v>3023.552290229102</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000009e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>88.03663367816085</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.171x + -71552.841</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.17099614082921</v>
       </c>
       <c r="X5" t="n">
         <v>-71552.84095192752</v>
@@ -7706,7 +7470,7 @@
         <v>1.143507990293474e-14</v>
       </c>
       <c r="Z5" t="n">
-        <v>280.1599999999999</v>
+        <v>2967.407414415672</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000004e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>87.75455022508199</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 25.503x + -61388.757</t>
-        </is>
+      <c r="W6" t="n">
+        <v>25.50332842970365</v>
       </c>
       <c r="X6" t="n">
         <v>-61388.75708529154</v>
@@ -7758,7 +7520,7 @@
         <v>1.029002508925277e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>237.6100000000001</v>
+        <v>2924.041814009404</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000067729e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>86.82365294782925</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.020x + -42135.531</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.01977871742763</v>
       </c>
       <c r="X7" t="n">
         <v>-42135.53109468762</v>
@@ -7810,7 +7570,7 @@
         <v>9.147892250672547e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>237.1499999999996</v>
+        <v>2884.832626894152</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000131622e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>85.56209972795442</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.885x + -29135.044</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.88473141078554</v>
       </c>
       <c r="X8" t="n">
         <v>-29135.04419632994</v>
@@ -7862,7 +7620,7 @@
         <v>5.542677087333395e-12</v>
       </c>
       <c r="Z8" t="n">
-        <v>244.4900000000002</v>
+        <v>2846.94606088787</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000059907e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>83.4304374773666</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 8.683x + -18746.466</t>
-        </is>
+      <c r="W9" t="n">
+        <v>8.683145826163905</v>
       </c>
       <c r="X9" t="n">
         <v>-18746.46588649466</v>
@@ -7914,7 +7670,7 @@
         <v>9.620224228637031e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>240.3899999999999</v>
+        <v>2810.683657324257</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000002254781e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>76.36115780742992</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 4.121x + -7718.772</t>
-        </is>
+      <c r="W10" t="n">
+        <v>4.121277994429851</v>
       </c>
       <c r="X10" t="n">
         <v>-7718.772412372305</v>
@@ -7966,7 +7720,7 @@
         <v>1.085343435594107e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>227.0500000000002</v>
+        <v>2776.174489074143</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000144727e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>56.86706397072344</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 1.532x + -1625.862</t>
-        </is>
+      <c r="W11" t="n">
+        <v>1.53207107049978</v>
       </c>
       <c r="X11" t="n">
         <v>-1625.861673355688</v>
@@ -8018,7 +7770,7 @@
         <v>1.22764211002573e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>226.8500000000004</v>
+        <v>2742.974615010593</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000042788e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>87.82536700448766</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 26.335x + -68198.247</t>
-        </is>
+      <c r="W2" t="n">
+        <v>26.33468020358896</v>
       </c>
       <c r="X2" t="n">
         <v>-68198.24688085998</v>
@@ -8216,7 +7966,7 @@
         <v>7.829881893687128e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>664.3099999999999</v>
+        <v>3091.679560445009</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000209e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>88.13974500407826</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 30.789x + -74739.214</t>
-        </is>
+      <c r="W3" t="n">
+        <v>30.78913674077157</v>
       </c>
       <c r="X3" t="n">
         <v>-74739.21361180568</v>
@@ -8268,7 +8016,7 @@
         <v>1.233381463419685e-15</v>
       </c>
       <c r="Z3" t="n">
-        <v>306.04</v>
+        <v>2924.594950167621</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000826e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>87.44616200928361</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 22.420x + -52595.860</t>
-        </is>
+      <c r="W4" t="n">
+        <v>22.42030650413371</v>
       </c>
       <c r="X4" t="n">
         <v>-52595.86030621087</v>
@@ -8320,7 +8066,7 @@
         <v>8.081375275611036e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>245.4700000000003</v>
+        <v>2867.690734657103</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000172454e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>86.36506850289545</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.741x + -35860.551</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.74139441019557</v>
       </c>
       <c r="X5" t="n">
         <v>-35860.55058012691</v>
@@ -8372,7 +8116,7 @@
         <v>3.271012226955511e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>220.8400000000001</v>
+        <v>2831.573809693018</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000161538e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>83.45830143272448</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 8.720x + -18705.004</t>
-        </is>
+      <c r="W6" t="n">
+        <v>8.720456612515639</v>
       </c>
       <c r="X6" t="n">
         <v>-18705.0035130191</v>
@@ -8424,7 +8166,7 @@
         <v>9.250746024137434e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>224.52</v>
+        <v>2800.137047970031</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000051283e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>79.02687767896758</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 5.157x + -10140.514</t>
-        </is>
+      <c r="W7" t="n">
+        <v>5.157469801801515</v>
       </c>
       <c r="X7" t="n">
         <v>-10140.51409358245</v>
@@ -8476,7 +8216,7 @@
         <v>1.161438124980658e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>224.5</v>
+        <v>2770.184456181625</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000070569e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>49.39061239768655</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 1.166x + -720.876</t>
-        </is>
+      <c r="W8" t="n">
+        <v>1.166333217617545</v>
       </c>
       <c r="X8" t="n">
         <v>-720.8756938429007</v>
@@ -8528,7 +8266,7 @@
         <v>2.994395494709667e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>218.3800000000001</v>
+        <v>2742.295703597552</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000136758e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>-71.43905883096647</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = -2.978x + 8953.916</t>
-        </is>
+      <c r="W9" t="n">
+        <v>-2.978154267140878</v>
       </c>
       <c r="X9" t="n">
         <v>8953.91573369358</v>
@@ -8580,7 +8316,7 @@
         <v>3.162018812113588e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>208.4899999999998</v>
+        <v>2715.893592132777</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000123253e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>-66.9712138136609</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = -2.353x + 7306.178</t>
-        </is>
+      <c r="W10" t="n">
+        <v>-2.352565425792377</v>
       </c>
       <c r="X10" t="n">
         <v>7306.178078909699</v>
@@ -8632,7 +8366,7 @@
         <v>351.7880185803672</v>
       </c>
       <c r="Z10" t="n">
-        <v>215.9899999999998</v>
+        <v>6799.144643573309</v>
       </c>
       <c r="AA10" t="n">
         <v>1.23751993603162e-06</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>-83.93837649205827</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = -9.417x + 23491.018</t>
-        </is>
+      <c r="W11" t="n">
+        <v>-9.416925354614641</v>
       </c>
       <c r="X11" t="n">
         <v>23491.01751536819</v>
@@ -8684,7 +8416,7 @@
         <v>346.1510907044591</v>
       </c>
       <c r="Z11" t="n">
-        <v>199.0099999999998</v>
+        <v>6714.992890909984</v>
       </c>
       <c r="AA11" t="n">
         <v>1.238171565523057e-06</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>-77.73337620723176</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = -4.599x + 12203.160</t>
-        </is>
+      <c r="W12" t="n">
+        <v>-4.599284565993265</v>
       </c>
       <c r="X12" t="n">
         <v>12203.16032319662</v>
@@ -8736,7 +8466,7 @@
         <v>344.4505887722594</v>
       </c>
       <c r="Z12" t="n">
-        <v>215.02</v>
+        <v>6670.094166821037</v>
       </c>
       <c r="AA12" t="n">
         <v>1.244512812326237e-06</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>-83.56554620747558</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = -8.867x + 21744.659</t>
-        </is>
+      <c r="W13" t="n">
+        <v>-8.867063216188333</v>
       </c>
       <c r="X13" t="n">
         <v>21744.6586949834</v>
@@ -8788,7 +8516,7 @@
         <v>341.094315649004</v>
       </c>
       <c r="Z13" t="n">
-        <v>207.73</v>
+        <v>6610.936832671729</v>
       </c>
       <c r="AA13" t="n">
         <v>1.248090006956523e-06</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>-84.57163450077203</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = -10.523x + 25276.479</t>
-        </is>
+      <c r="W14" t="n">
+        <v>-10.52328622758085</v>
       </c>
       <c r="X14" t="n">
         <v>25276.47871324407</v>
@@ -8840,7 +8566,7 @@
         <v>337.9733616294421</v>
       </c>
       <c r="Z14" t="n">
-        <v>205.6900000000001</v>
+        <v>6553.353565219952</v>
       </c>
       <c r="AA14" t="n">
         <v>1.252345813924323e-06</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>-85.01465463204343</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = -11.464x + 27172.028</t>
-        </is>
+      <c r="W15" t="n">
+        <v>-11.46382235952968</v>
       </c>
       <c r="X15" t="n">
         <v>27172.02773873126</v>
@@ -8892,7 +8616,7 @@
         <v>3.445652138653639e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>200.5799999999999</v>
+        <v>2588.31182980137</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000401e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>83.04760759347671</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 8.201x + -17039.262</t>
-        </is>
+      <c r="W16" t="n">
+        <v>8.200673050021281</v>
       </c>
       <c r="X16" t="n">
         <v>-17039.26185377737</v>
@@ -8944,7 +8666,7 @@
         <v>1.330838232036492e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>190.5900000000001</v>
+        <v>2567.327131939855</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000370885e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>-84.87169996115252</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = -11.143x + 25895.835</t>
-        </is>
+      <c r="W17" t="n">
+        <v>-11.14261904276159</v>
       </c>
       <c r="X17" t="n">
         <v>25895.83522968648</v>
@@ -8996,7 +8716,7 @@
         <v>2.587055930497271e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>205.7600000000002</v>
+        <v>2545.968779739195</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000003167629e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>82.85972290162067</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 7.983x + -16280.100</t>
-        </is>
+      <c r="W18" t="n">
+        <v>7.98272404014578</v>
       </c>
       <c r="X18" t="n">
         <v>-16280.10041114738</v>
@@ -9048,7 +8766,7 @@
         <v>1.133077636823484e-14</v>
       </c>
       <c r="Z18" t="n">
-        <v>192.21</v>
+        <v>2523.784958011967</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000562e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>82.79080654594047</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 7.906x + -15977.312</t>
-        </is>
+      <c r="W19" t="n">
+        <v>7.905613393486639</v>
       </c>
       <c r="X19" t="n">
         <v>-15977.31195387075</v>
@@ -9100,7 +8816,7 @@
         <v>1.380659697293558e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>188.79</v>
+        <v>2501.133789106292</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000001017485e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>82.60370770065516</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 7.703x + -15401.097</t>
-        </is>
+      <c r="W20" t="n">
+        <v>7.703476481506846</v>
       </c>
       <c r="X20" t="n">
         <v>-15401.09675989566</v>
@@ -9152,7 +8866,7 @@
         <v>7.040343705032971e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>191.4300000000001</v>
+        <v>2479.168081807108</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000091103e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>82.94408448505635</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 8.079x + -16066.364</t>
-        </is>
+      <c r="W21" t="n">
+        <v>8.079156170029071</v>
       </c>
       <c r="X21" t="n">
         <v>-16066.36387276008</v>
@@ -9204,7 +8916,7 @@
         <v>6.406043277467845e-11</v>
       </c>
       <c r="Z21" t="n">
-        <v>182</v>
+        <v>2455.792518640102</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000644234e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>82.68646213065504</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 7.792x + -15307.757</t>
-        </is>
+      <c r="W22" t="n">
+        <v>7.791613631966008</v>
       </c>
       <c r="X22" t="n">
         <v>-15307.75665610602</v>
@@ -9256,7 +8966,7 @@
         <v>2.087449055633758e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>186.2800000000002</v>
+        <v>2432.288536473511</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000039001e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>87.03140294551621</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 19.283x + -48579.760</t>
-        </is>
+      <c r="W2" t="n">
+        <v>19.28335164375076</v>
       </c>
       <c r="X2" t="n">
         <v>-48579.76033740994</v>
@@ -9454,7 +9162,7 @@
         <v>392.3858647214501</v>
       </c>
       <c r="Z2" t="n">
-        <v>1059.15</v>
+        <v>8098.63783532979</v>
       </c>
       <c r="AA2" t="n">
         <v>1.239915336039771e-06</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>88.33591378870584</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 34.421x + -74058.001</t>
-        </is>
+      <c r="W3" t="n">
+        <v>34.42109415070531</v>
       </c>
       <c r="X3" t="n">
         <v>-74058.00108082524</v>
@@ -9506,7 +9212,7 @@
         <v>2.236782568648663e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>378.5599999999999</v>
+        <v>2543.975356323464</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000119147e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>88.12244898454843</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 30.505x + -62609.482</t>
-        </is>
+      <c r="W4" t="n">
+        <v>30.50530654230801</v>
       </c>
       <c r="X4" t="n">
         <v>-62609.48196086705</v>
@@ -9558,7 +9262,7 @@
         <v>2.10297097509419e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>228.29</v>
+        <v>2452.546557468798</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000630069e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>87.30883991372554</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 21.275x + -42130.121</t>
-        </is>
+      <c r="W5" t="n">
+        <v>21.27470579155565</v>
       </c>
       <c r="X5" t="n">
         <v>-42130.12097098723</v>
@@ -9610,7 +9312,7 @@
         <v>3.553022794014832e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>210.24</v>
+        <v>2403.962535507002</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000059433e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>85.86794355697477</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.842x + -26346.410</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.84211807723732</v>
       </c>
       <c r="X6" t="n">
         <v>-26346.40992308271</v>
@@ -9662,7 +9362,7 @@
         <v>2.385596207340135e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>193.96</v>
+        <v>2363.838351958109</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000045021e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>83.65473983312367</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 8.993x + -16231.464</t>
-        </is>
+      <c r="W7" t="n">
+        <v>8.99275199847958</v>
       </c>
       <c r="X7" t="n">
         <v>-16231.46414564901</v>
@@ -9714,7 +9412,7 @@
         <v>1074.040966319842</v>
       </c>
       <c r="Z7" t="n">
-        <v>190.4399999999998</v>
+        <v>186810696.507831</v>
       </c>
       <c r="AA7" t="n">
         <v>1.630490183183693e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>74.7550085595128</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 3.669x + -5512.860</t>
-        </is>
+      <c r="W8" t="n">
+        <v>3.669221436867571</v>
       </c>
       <c r="X8" t="n">
         <v>-5512.859662034151</v>
@@ -9766,7 +9462,7 @@
         <v>1068.374948206254</v>
       </c>
       <c r="Z8" t="n">
-        <v>190.55</v>
+        <v>114722952.871877</v>
       </c>
       <c r="AA8" t="n">
         <v>1.562612724679226e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>-4.423922731858651</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = -0.077x + 1903.285</t>
-        </is>
+      <c r="W9" t="n">
+        <v>-0.07736582249354416</v>
       </c>
       <c r="X9" t="n">
         <v>1903.285491749938</v>
@@ -9818,7 +9512,7 @@
         <v>1062.039745893575</v>
       </c>
       <c r="Z9" t="n">
-        <v>179.6200000000001</v>
+        <v>141810577.8011816</v>
       </c>
       <c r="AA9" t="n">
         <v>1.510729130812662e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>22.16267462696134</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 0.407x + 835.052</t>
-        </is>
+      <c r="W10" t="n">
+        <v>0.4073326997882372</v>
       </c>
       <c r="X10" t="n">
         <v>835.0519703303619</v>
@@ -9870,7 +9562,7 @@
         <v>1055.946185732522</v>
       </c>
       <c r="Z10" t="n">
-        <v>188.71</v>
+        <v>111482269.904886</v>
       </c>
       <c r="AA10" t="n">
         <v>1.467170916714975e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>-82.14450195535515</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = -7.248x + 15461.405</t>
-        </is>
+      <c r="W11" t="n">
+        <v>-7.247958175298677</v>
       </c>
       <c r="X11" t="n">
         <v>15461.40481727142</v>
@@ -9922,7 +9612,7 @@
         <v>1049.882941234716</v>
       </c>
       <c r="Z11" t="n">
-        <v>170.3199999999999</v>
+        <v>180933920.122557</v>
       </c>
       <c r="AA11" t="n">
         <v>1.428077054446047e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-567.27</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-326.5899999999997</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-221.3199999999997</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-162.5799999999999</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-118.6799999999998</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-77.92000000000007</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-68.57000000000016</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-40.01999999999998</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-23.42000000000007</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>9.940000000000055</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1973.24</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-965.1299999999997</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-491.8200000000002</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-325.9099999999999</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-218.8099999999999</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-164.5100000000002</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-124.8099999999999</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-83.80999999999995</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-58.71000000000004</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-38.94000000000005</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1809.8</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-796.6599999999999</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-441.6199999999999</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-294.9400000000001</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-217.5900000000001</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-144.8800000000001</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-111.3400000000001</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-88.4699999999998</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-56.40000000000009</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-40.61999999999989</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1673.63</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-679.6599999999999</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-415.0699999999997</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-280.1599999999999</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-204.9200000000001</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-158.3999999999996</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-136.6700000000001</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-109.2099999999996</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-78.17000000000007</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-64.16000000000031</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1059.15</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-378.5599999999999</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-228.29</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-162.3100000000002</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-105.8899999999999</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-83.75999999999999</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-62.77000000000021</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-46.34000000000015</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-49.26999999999998</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-21.18000000000006</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-567.27</v>
+        <v>2132.121</v>
       </c>
       <c r="D2" t="n">
         <v>6.61225e-08</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-326.5899999999997</v>
+        <v>2067.484</v>
       </c>
       <c r="D3" t="n">
         <v>6.50528e-08</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-221.3199999999997</v>
+        <v>2021.42</v>
       </c>
       <c r="D4" t="n">
         <v>6.45043e-08</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-162.5799999999999</v>
+        <v>1972.845</v>
       </c>
       <c r="D5" t="n">
         <v>6.417e-08</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-118.6799999999998</v>
+        <v>1933.767</v>
       </c>
       <c r="D6" t="n">
         <v>6.395500000000001e-08</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-77.92000000000007</v>
+        <v>1906.642</v>
       </c>
       <c r="D7" t="n">
         <v>6.38219e-08</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-68.57000000000016</v>
+        <v>1859.01</v>
       </c>
       <c r="D8" t="n">
         <v>6.372e-08</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-40.01999999999998</v>
+        <v>1833.137</v>
       </c>
       <c r="D9" t="n">
         <v>6.364490000000001e-08</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-23.42000000000007</v>
+        <v>1797.168</v>
       </c>
       <c r="D10" t="n">
         <v>6.357000000000001e-08</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>9.940000000000055</v>
+        <v>1780.3</v>
       </c>
       <c r="D11" t="n">
         <v>6.35288e-08</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-54.4699999999998</v>
+        <v>2058.602</v>
       </c>
       <c r="D2" t="n">
         <v>6.74794e-08</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-77.71000000000004</v>
+        <v>1919.579</v>
       </c>
       <c r="D3" t="n">
         <v>6.77274e-08</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-55.57000000000016</v>
+        <v>1887.444</v>
       </c>
       <c r="D4" t="n">
         <v>6.78196e-08</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-46.97000000000025</v>
+        <v>1857.86</v>
       </c>
       <c r="D5" t="n">
         <v>6.78706e-08</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-227.0300000000002</v>
+        <v>1834.953</v>
       </c>
       <c r="D6" t="n">
         <v>6.92236e-08</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-187.1900000000001</v>
+        <v>1813.986</v>
       </c>
       <c r="D7" t="n">
         <v>6.90902e-08</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-192.27</v>
+        <v>1773.481</v>
       </c>
       <c r="D8" t="n">
         <v>6.90448e-08</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-171.2199999999998</v>
+        <v>1765.362</v>
       </c>
       <c r="D9" t="n">
         <v>6.89808e-08</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-161.4899999999998</v>
+        <v>1750.148</v>
       </c>
       <c r="D10" t="n">
         <v>6.896299999999999e-08</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-159.2599999999998</v>
+        <v>1733.737</v>
       </c>
       <c r="D11" t="n">
         <v>6.89257e-08</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-165.9400000000001</v>
+        <v>1708.16</v>
       </c>
       <c r="D12" t="n">
         <v>6.88937e-08</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-160.2200000000003</v>
+        <v>1704.881</v>
       </c>
       <c r="D13" t="n">
         <v>6.88594e-08</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-167.8699999999999</v>
+        <v>1677.718</v>
       </c>
       <c r="D14" t="n">
         <v>6.88173e-08</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-57.24000000000024</v>
+        <v>1676.577</v>
       </c>
       <c r="D15" t="n">
         <v>6.84767e-08</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-50.32999999999993</v>
+        <v>1654.581</v>
       </c>
       <c r="D16" t="n">
         <v>6.84863e-08</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-96.28999999999996</v>
+        <v>1640.194</v>
       </c>
       <c r="D17" t="n">
         <v>6.854860000000001e-08</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-22.11999999999989</v>
+        <v>1629.852</v>
       </c>
       <c r="D18" t="n">
         <v>6.841669999999999e-08</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-22.56999999999994</v>
+        <v>1603.71</v>
       </c>
       <c r="D19" t="n">
         <v>6.840150000000001e-08</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-29.53999999999996</v>
+        <v>1584.776</v>
       </c>
       <c r="D20" t="n">
         <v>6.8376e-08</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-44.36000000000013</v>
+        <v>1565.679</v>
       </c>
       <c r="D21" t="n">
         <v>6.84333e-08</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-41.73000000000002</v>
+        <v>1548.366</v>
       </c>
       <c r="D22" t="n">
         <v>6.84467e-08</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-961.6500000000001</v>
+        <v>2130</v>
       </c>
       <c r="D2" t="n">
         <v>6.740070000000001e-08</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-372.3099999999999</v>
+        <v>1990.322</v>
       </c>
       <c r="D3" t="n">
         <v>6.55186e-08</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-167.6900000000001</v>
+        <v>1963.209</v>
       </c>
       <c r="D4" t="n">
         <v>6.47311e-08</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-96.36999999999989</v>
+        <v>1928.942</v>
       </c>
       <c r="D5" t="n">
         <v>6.434270000000001e-08</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-62.8100000000004</v>
+        <v>1890.948</v>
       </c>
       <c r="D6" t="n">
         <v>6.414810000000001e-08</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-27.75</v>
+        <v>1865.042</v>
       </c>
       <c r="D7" t="n">
         <v>6.399980000000001e-08</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>4.869999999999891</v>
+        <v>1854.873</v>
       </c>
       <c r="D8" t="n">
         <v>6.39136e-08</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>34.38999999999987</v>
+        <v>1837.504</v>
       </c>
       <c r="D9" t="n">
         <v>6.385170000000001e-08</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>34.97000000000025</v>
+        <v>1811.805</v>
       </c>
       <c r="D10" t="n">
         <v>6.38007e-08</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>48.30999999999995</v>
+        <v>1783.946</v>
       </c>
       <c r="D11" t="n">
         <v>6.37627e-08</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>45.83000000000038</v>
+        <v>1757.436</v>
       </c>
       <c r="D12" t="n">
         <v>6.373989999999999e-08</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>68.75999999999976</v>
+        <v>1746.766</v>
       </c>
       <c r="D13" t="n">
         <v>6.3729e-08</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>83.41999999999962</v>
+        <v>1731.362</v>
       </c>
       <c r="D14" t="n">
         <v>6.3716e-08</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>84.80000000000018</v>
+        <v>1710.801</v>
       </c>
       <c r="D15" t="n">
         <v>6.36922e-08</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>88.12000000000012</v>
+        <v>1685.238</v>
       </c>
       <c r="D16" t="n">
         <v>6.36945e-08</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>103.4399999999998</v>
+        <v>1666.843</v>
       </c>
       <c r="D17" t="n">
         <v>6.36918e-08</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>99.11999999999989</v>
+        <v>1640.389</v>
       </c>
       <c r="D18" t="n">
         <v>6.36817e-08</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>106.8999999999999</v>
+        <v>1624.023</v>
       </c>
       <c r="D19" t="n">
         <v>6.36817e-08</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>112.1200000000001</v>
+        <v>1605.438</v>
       </c>
       <c r="D20" t="n">
         <v>6.36643e-08</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>130.9200000000001</v>
+        <v>1600.409</v>
       </c>
       <c r="D21" t="n">
         <v>6.36642e-08</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>128.25</v>
+        <v>1576.464</v>
       </c>
       <c r="D22" t="n">
         <v>6.366399999999999e-08</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1973.24</v>
+        <v>2635.925</v>
       </c>
       <c r="D2" t="n">
         <v>6.807770000000001e-08</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-965.1299999999997</v>
+        <v>2242.776</v>
       </c>
       <c r="D3" t="n">
         <v>6.74003e-08</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-491.8200000000002</v>
+        <v>2148.145</v>
       </c>
       <c r="D4" t="n">
         <v>6.617129999999999e-08</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-325.9099999999999</v>
+        <v>2077.364</v>
       </c>
       <c r="D5" t="n">
         <v>6.55808e-08</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-218.8099999999999</v>
+        <v>2042.015</v>
       </c>
       <c r="D6" t="n">
         <v>6.53113e-08</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-164.5100000000002</v>
+        <v>1988.128</v>
       </c>
       <c r="D7" t="n">
         <v>6.51838e-08</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-124.8099999999999</v>
+        <v>1951.536</v>
       </c>
       <c r="D8" t="n">
         <v>6.51042e-08</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-83.80999999999995</v>
+        <v>1924.12</v>
       </c>
       <c r="D9" t="n">
         <v>6.50668e-08</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-58.71000000000004</v>
+        <v>1894.526</v>
       </c>
       <c r="D10" t="n">
         <v>6.50538e-08</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-38.94000000000005</v>
+        <v>1865.824</v>
       </c>
       <c r="D11" t="n">
         <v>6.50517e-08</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-635.7600000000002</v>
+        <v>2115.868</v>
       </c>
       <c r="D2" t="n">
         <v>6.68646e-08</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-255.6599999999999</v>
+        <v>1994.89</v>
       </c>
       <c r="D3" t="n">
         <v>6.56379e-08</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-144.7199999999998</v>
+        <v>1947.371</v>
       </c>
       <c r="D4" t="n">
         <v>6.53195e-08</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-83.1899999999996</v>
+        <v>1922.022</v>
       </c>
       <c r="D5" t="n">
         <v>6.51826e-08</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-46.30999999999995</v>
+        <v>1896.409</v>
       </c>
       <c r="D6" t="n">
         <v>6.51337e-08</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-18.26999999999998</v>
+        <v>1877.361</v>
       </c>
       <c r="D7" t="n">
         <v>6.51319e-08</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-15.23999999999978</v>
+        <v>1847.789</v>
       </c>
       <c r="D8" t="n">
         <v>6.512e-08</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>4.259999999999764</v>
+        <v>1826.097</v>
       </c>
       <c r="D9" t="n">
         <v>6.512470000000001e-08</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>13.22000000000025</v>
+        <v>1793.836</v>
       </c>
       <c r="D10" t="n">
         <v>6.51447e-08</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>28.91000000000031</v>
+        <v>1772.736</v>
       </c>
       <c r="D11" t="n">
         <v>6.5148e-08</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>48.98000000000002</v>
+        <v>1772.46</v>
       </c>
       <c r="D12" t="n">
         <v>6.514770000000001e-08</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>44.5300000000002</v>
+        <v>1732.818</v>
       </c>
       <c r="D13" t="n">
         <v>6.51546e-08</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>68.44000000000005</v>
+        <v>1725.676</v>
       </c>
       <c r="D14" t="n">
         <v>6.515700000000001e-08</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>67.47000000000025</v>
+        <v>1699.515</v>
       </c>
       <c r="D15" t="n">
         <v>6.51468e-08</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>83.53999999999996</v>
+        <v>1685.338</v>
       </c>
       <c r="D16" t="n">
         <v>6.51408e-08</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>77.29999999999995</v>
+        <v>1653.387</v>
       </c>
       <c r="D17" t="n">
         <v>6.516190000000001e-08</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>84.45000000000027</v>
+        <v>1631.66</v>
       </c>
       <c r="D18" t="n">
         <v>6.514720000000001e-08</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>82.81999999999994</v>
+        <v>1598.629</v>
       </c>
       <c r="D19" t="n">
         <v>6.516729999999999e-08</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>113.4400000000001</v>
+        <v>1601.069</v>
       </c>
       <c r="D20" t="n">
         <v>6.51763e-08</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>110.6099999999999</v>
+        <v>1573.746</v>
       </c>
       <c r="D21" t="n">
         <v>6.517709999999999e-08</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>110.1399999999999</v>
+        <v>1549.245</v>
       </c>
       <c r="D22" t="n">
         <v>6.51972e-08</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1809.8</v>
+        <v>2657.887</v>
       </c>
       <c r="D2" t="n">
         <v>6.869109999999999e-08</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-796.6599999999999</v>
+        <v>2193.718</v>
       </c>
       <c r="D3" t="n">
         <v>6.773579999999999e-08</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-441.6199999999999</v>
+        <v>2092.929</v>
       </c>
       <c r="D4" t="n">
         <v>6.68213e-08</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-294.9400000000001</v>
+        <v>2036.818</v>
       </c>
       <c r="D5" t="n">
         <v>6.6444e-08</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-217.5900000000001</v>
+        <v>1992.979</v>
       </c>
       <c r="D6" t="n">
         <v>6.62592e-08</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-144.8800000000001</v>
+        <v>1973.083</v>
       </c>
       <c r="D7" t="n">
         <v>6.61719e-08</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-111.3400000000001</v>
+        <v>1933.396</v>
       </c>
       <c r="D8" t="n">
         <v>6.61369e-08</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-88.4699999999998</v>
+        <v>1894.82</v>
       </c>
       <c r="D9" t="n">
         <v>6.6136e-08</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-56.40000000000009</v>
+        <v>1874.924</v>
       </c>
       <c r="D10" t="n">
         <v>6.61349e-08</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-40.61999999999989</v>
+        <v>1840.192</v>
       </c>
       <c r="D11" t="n">
         <v>6.61646e-08</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-962.1799999999998</v>
+        <v>2112.708</v>
       </c>
       <c r="D2" t="n">
         <v>6.923909999999999e-08</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-370.8200000000002</v>
+        <v>1977.818</v>
       </c>
       <c r="D3" t="n">
         <v>6.73327e-08</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-214.6599999999999</v>
+        <v>1933.114</v>
       </c>
       <c r="D4" t="n">
         <v>6.688940000000001e-08</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-134.8800000000001</v>
+        <v>1911.507</v>
       </c>
       <c r="D5" t="n">
         <v>6.67038e-08</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-109.0799999999999</v>
+        <v>1870.091</v>
       </c>
       <c r="D6" t="n">
         <v>6.66288e-08</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-75.75</v>
+        <v>1848.106</v>
       </c>
       <c r="D7" t="n">
         <v>6.66054e-08</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-55.01000000000022</v>
+        <v>1826.383</v>
       </c>
       <c r="D8" t="n">
         <v>6.65822e-08</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-38.23000000000002</v>
+        <v>1806.192</v>
       </c>
       <c r="D9" t="n">
         <v>6.65943e-08</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-21.71000000000004</v>
+        <v>1789.047</v>
       </c>
       <c r="D10" t="n">
         <v>6.66098e-08</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-4.159999999999854</v>
+        <v>1777.308</v>
       </c>
       <c r="D11" t="n">
         <v>6.66092e-08</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-2.279999999999745</v>
+        <v>1747.524</v>
       </c>
       <c r="D12" t="n">
         <v>6.66359e-08</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>6.839999999999691</v>
+        <v>1729.993</v>
       </c>
       <c r="D13" t="n">
         <v>6.66293e-08</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>3.450000000000273</v>
+        <v>1706.314</v>
       </c>
       <c r="D14" t="n">
         <v>6.66455e-08</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>27.71000000000004</v>
+        <v>1703.838</v>
       </c>
       <c r="D15" t="n">
         <v>6.66379e-08</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>22.32999999999993</v>
+        <v>1674.799</v>
       </c>
       <c r="D16" t="n">
         <v>6.665789999999999e-08</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>33.84000000000015</v>
+        <v>1660.743</v>
       </c>
       <c r="D17" t="n">
         <v>6.66758e-08</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>29.68999999999983</v>
+        <v>1636.787</v>
       </c>
       <c r="D18" t="n">
         <v>6.66753e-08</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>47.94000000000005</v>
+        <v>1627.471</v>
       </c>
       <c r="D19" t="n">
         <v>6.66815e-08</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>56.62000000000012</v>
+        <v>1610.084</v>
       </c>
       <c r="D20" t="n">
         <v>6.669580000000001e-08</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>63.18000000000006</v>
+        <v>1599.406</v>
       </c>
       <c r="D21" t="n">
         <v>6.66883e-08</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>62.73000000000002</v>
+        <v>1579.482</v>
       </c>
       <c r="D22" t="n">
         <v>6.670460000000001e-08</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1673.63</v>
+        <v>2567.581</v>
       </c>
       <c r="D2" t="n">
         <v>6.91829e-08</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-679.6599999999999</v>
+        <v>2137.53</v>
       </c>
       <c r="D3" t="n">
         <v>6.82448e-08</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-415.0699999999997</v>
+        <v>2026.95</v>
       </c>
       <c r="D4" t="n">
         <v>6.7658e-08</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-280.1599999999999</v>
+        <v>1991.235</v>
       </c>
       <c r="D5" t="n">
         <v>6.74376e-08</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-204.9200000000001</v>
+        <v>1963.62</v>
       </c>
       <c r="D6" t="n">
         <v>6.73161e-08</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-158.3999999999996</v>
+        <v>1925.438</v>
       </c>
       <c r="D7" t="n">
         <v>6.72919e-08</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-136.6700000000001</v>
+        <v>1883.437</v>
       </c>
       <c r="D8" t="n">
         <v>6.72747e-08</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-109.2099999999996</v>
+        <v>1853.945</v>
       </c>
       <c r="D9" t="n">
         <v>6.73049e-08</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-78.17000000000007</v>
+        <v>1835.76</v>
       </c>
       <c r="D10" t="n">
         <v>6.735029999999999e-08</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-64.16000000000031</v>
+        <v>1804.907</v>
       </c>
       <c r="D11" t="n">
         <v>6.73891e-08</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-664.3099999999999</v>
+        <v>2113.974</v>
       </c>
       <c r="D2" t="n">
         <v>6.92013e-08</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-306.04</v>
+        <v>1970.511</v>
       </c>
       <c r="D3" t="n">
         <v>6.80859e-08</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-202.2400000000002</v>
+        <v>1914.942</v>
       </c>
       <c r="D4" t="n">
         <v>6.778620000000001e-08</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-131.3400000000001</v>
+        <v>1902.173</v>
       </c>
       <c r="D5" t="n">
         <v>6.76946e-08</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-101.1299999999997</v>
+        <v>1868.581</v>
       </c>
       <c r="D6" t="n">
         <v>6.76566e-08</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-84.78999999999996</v>
+        <v>1838.446</v>
       </c>
       <c r="D7" t="n">
         <v>6.76498e-08</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-63.07999999999993</v>
+        <v>1817.64</v>
       </c>
       <c r="D8" t="n">
         <v>6.7673e-08</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-45.96000000000004</v>
+        <v>1803.327</v>
       </c>
       <c r="D9" t="n">
         <v>6.76783e-08</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-45.44999999999982</v>
+        <v>1772.581</v>
       </c>
       <c r="D10" t="n">
         <v>6.77146e-08</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-19.65999999999985</v>
+        <v>1767.578</v>
       </c>
       <c r="D11" t="n">
         <v>6.77324e-08</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-33.17000000000007</v>
+        <v>1732.769</v>
       </c>
       <c r="D12" t="n">
         <v>6.77558e-08</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-14.65000000000009</v>
+        <v>1724.228</v>
       </c>
       <c r="D13" t="n">
         <v>6.77394e-08</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-8.739999999999782</v>
+        <v>1709.091</v>
       </c>
       <c r="D14" t="n">
         <v>6.77677e-08</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-3.599999999999909</v>
+        <v>1695.075</v>
       </c>
       <c r="D15" t="n">
         <v>6.77724e-08</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>14.53999999999996</v>
+        <v>1687.281</v>
       </c>
       <c r="D16" t="n">
         <v>6.779280000000001e-08</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.8099999999999454</v>
+        <v>1650.533</v>
       </c>
       <c r="D17" t="n">
         <v>6.77997e-08</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>20.34000000000015</v>
+        <v>1647.34</v>
       </c>
       <c r="D18" t="n">
         <v>6.78108e-08</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>31.18000000000029</v>
+        <v>1630.251</v>
       </c>
       <c r="D19" t="n">
         <v>6.782240000000001e-08</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>24.10000000000014</v>
+        <v>1608.278</v>
       </c>
       <c r="D20" t="n">
         <v>6.7829e-08</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>45.01999999999998</v>
+        <v>1597.924</v>
       </c>
       <c r="D21" t="n">
         <v>6.78533e-08</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>39.91000000000008</v>
+        <v>1572.524</v>
       </c>
       <c r="D22" t="n">
         <v>6.78604e-08</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1059.15</v>
+        <v>2010.119</v>
       </c>
       <c r="D2" t="n">
         <v>7.01467e-08</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-378.5599999999999</v>
+        <v>1650.378</v>
       </c>
       <c r="D3" t="n">
         <v>6.901170000000001e-08</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-228.29</v>
+        <v>1566.011</v>
       </c>
       <c r="D4" t="n">
         <v>6.871849999999999e-08</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-162.3100000000002</v>
+        <v>1517.161</v>
       </c>
       <c r="D5" t="n">
         <v>6.859489999999999e-08</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-105.8899999999999</v>
+        <v>1495.033</v>
       </c>
       <c r="D6" t="n">
         <v>6.85015e-08</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-83.75999999999999</v>
+        <v>1462.876</v>
       </c>
       <c r="D7" t="n">
         <v>6.84917e-08</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-62.77000000000021</v>
+        <v>1428.973</v>
       </c>
       <c r="D8" t="n">
         <v>6.84907e-08</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-46.34000000000015</v>
+        <v>1406.718</v>
       </c>
       <c r="D9" t="n">
         <v>6.850089999999999e-08</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-49.26999999999998</v>
+        <v>1368.721</v>
       </c>
       <c r="D10" t="n">
         <v>6.853689999999999e-08</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-21.18000000000006</v>
+        <v>1358.596</v>
       </c>
       <c r="D11" t="n">
         <v>6.85614e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>2132.121</v>
       </c>
+      <c r="C2" t="n">
+        <v>2807.523377950308</v>
+      </c>
       <c r="D2" t="n">
         <v>6.61225e-08</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>2067.484</v>
       </c>
+      <c r="C3" t="n">
+        <v>2738.183857971791</v>
+      </c>
       <c r="D3" t="n">
         <v>6.50528e-08</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>2021.42</v>
       </c>
+      <c r="C4" t="n">
+        <v>2692.53906638855</v>
+      </c>
       <c r="D4" t="n">
         <v>6.45043e-08</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>1972.845</v>
       </c>
+      <c r="C5" t="n">
+        <v>2644.353898922284</v>
+      </c>
       <c r="D5" t="n">
         <v>6.417e-08</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1933.767</v>
       </c>
+      <c r="C6" t="n">
+        <v>2608.047586539176</v>
+      </c>
       <c r="D6" t="n">
         <v>6.395500000000001e-08</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1906.642</v>
       </c>
+      <c r="C7" t="n">
+        <v>2580.492000061952</v>
+      </c>
       <c r="D7" t="n">
         <v>6.38219e-08</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1859.01</v>
       </c>
+      <c r="C8" t="n">
+        <v>2533.804992946663</v>
+      </c>
       <c r="D8" t="n">
         <v>6.372e-08</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1833.137</v>
       </c>
+      <c r="C9" t="n">
+        <v>2506.105417190169</v>
+      </c>
       <c r="D9" t="n">
         <v>6.364490000000001e-08</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1797.168</v>
       </c>
+      <c r="C10" t="n">
+        <v>2471.639214550307</v>
+      </c>
       <c r="D10" t="n">
         <v>6.357000000000001e-08</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1780.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2455.43954741523</v>
       </c>
       <c r="D11" t="n">
         <v>6.35288e-08</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>2058.602</v>
       </c>
+      <c r="C2" t="n">
+        <v>2753.21303495648</v>
+      </c>
       <c r="D2" t="n">
         <v>6.74794e-08</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1919.579</v>
       </c>
+      <c r="C3" t="n">
+        <v>2575.289607357818</v>
+      </c>
       <c r="D3" t="n">
         <v>6.77274e-08</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1887.444</v>
       </c>
+      <c r="C4" t="n">
+        <v>2533.687506464527</v>
+      </c>
       <c r="D4" t="n">
         <v>6.78196e-08</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1857.86</v>
       </c>
+      <c r="C5" t="n">
+        <v>2506.384696205068</v>
+      </c>
       <c r="D5" t="n">
         <v>6.78706e-08</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1834.953</v>
       </c>
+      <c r="C6" t="n">
+        <v>2483.790095774002</v>
+      </c>
       <c r="D6" t="n">
         <v>6.92236e-08</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1813.986</v>
       </c>
+      <c r="C7" t="n">
+        <v>2462.761100593423</v>
+      </c>
       <c r="D7" t="n">
         <v>6.90902e-08</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1773.481</v>
       </c>
+      <c r="C8" t="n">
+        <v>2422.163542668291</v>
+      </c>
       <c r="D8" t="n">
         <v>6.90448e-08</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1765.362</v>
       </c>
+      <c r="C9" t="n">
+        <v>2416.007993416801</v>
+      </c>
       <c r="D9" t="n">
         <v>6.89808e-08</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1750.148</v>
       </c>
+      <c r="C10" t="n">
+        <v>2401.869613511418</v>
+      </c>
       <c r="D10" t="n">
         <v>6.896299999999999e-08</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1733.737</v>
       </c>
+      <c r="C11" t="n">
+        <v>2385.651729433416</v>
+      </c>
       <c r="D11" t="n">
         <v>6.89257e-08</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1708.16</v>
       </c>
+      <c r="C12" t="n">
+        <v>2357.434366434806</v>
+      </c>
       <c r="D12" t="n">
         <v>6.88937e-08</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1704.881</v>
       </c>
+      <c r="C13" t="n">
+        <v>2355.130291103077</v>
+      </c>
       <c r="D13" t="n">
         <v>6.88594e-08</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1677.718</v>
       </c>
+      <c r="C14" t="n">
+        <v>2329.188217425468</v>
+      </c>
       <c r="D14" t="n">
         <v>6.88173e-08</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1676.577</v>
       </c>
+      <c r="C15" t="n">
+        <v>2327.744829474304</v>
+      </c>
       <c r="D15" t="n">
         <v>6.84767e-08</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1654.581</v>
       </c>
+      <c r="C16" t="n">
+        <v>2305.552802678888</v>
+      </c>
       <c r="D16" t="n">
         <v>6.84863e-08</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1640.194</v>
       </c>
+      <c r="C17" t="n">
+        <v>2291.357626869064</v>
+      </c>
       <c r="D17" t="n">
         <v>6.854860000000001e-08</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1629.852</v>
       </c>
+      <c r="C18" t="n">
+        <v>2282.487186856989</v>
+      </c>
       <c r="D18" t="n">
         <v>6.841669999999999e-08</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1603.71</v>
       </c>
+      <c r="C19" t="n">
+        <v>2251.031063695554</v>
+      </c>
       <c r="D19" t="n">
         <v>6.840150000000001e-08</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1584.776</v>
       </c>
+      <c r="C20" t="n">
+        <v>2242.953220579035</v>
+      </c>
       <c r="D20" t="n">
         <v>6.8376e-08</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1565.679</v>
       </c>
+      <c r="C21" t="n">
+        <v>2215.682847355326</v>
+      </c>
       <c r="D21" t="n">
         <v>6.84333e-08</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1548.366</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2197.425012083357</v>
       </c>
       <c r="D22" t="n">
         <v>6.84467e-08</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>2130</v>
       </c>
+      <c r="C2" t="n">
+        <v>2837.081579207963</v>
+      </c>
       <c r="D2" t="n">
         <v>6.740070000000001e-08</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>1990.322</v>
       </c>
+      <c r="C3" t="n">
+        <v>2660.542058751909</v>
+      </c>
       <c r="D3" t="n">
         <v>6.55186e-08</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>1963.209</v>
       </c>
+      <c r="C4" t="n">
+        <v>2628.628209015238</v>
+      </c>
       <c r="D4" t="n">
         <v>6.47311e-08</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>1928.942</v>
       </c>
+      <c r="C5" t="n">
+        <v>2593.96370535419</v>
+      </c>
       <c r="D5" t="n">
         <v>6.434270000000001e-08</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1890.948</v>
       </c>
+      <c r="C6" t="n">
+        <v>2556.357443551944</v>
+      </c>
       <c r="D6" t="n">
         <v>6.414810000000001e-08</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1865.042</v>
       </c>
+      <c r="C7" t="n">
+        <v>2533.408284946267</v>
+      </c>
       <c r="D7" t="n">
         <v>6.399980000000001e-08</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1854.873</v>
       </c>
+      <c r="C8" t="n">
+        <v>2520.213525785581</v>
+      </c>
       <c r="D8" t="n">
         <v>6.39136e-08</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1837.504</v>
       </c>
+      <c r="C9" t="n">
+        <v>2505.401128092849</v>
+      </c>
       <c r="D9" t="n">
         <v>6.385170000000001e-08</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1811.805</v>
       </c>
+      <c r="C10" t="n">
+        <v>2480.714576479284</v>
+      </c>
       <c r="D10" t="n">
         <v>6.38007e-08</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1783.946</v>
       </c>
+      <c r="C11" t="n">
+        <v>2453.30077945554</v>
+      </c>
       <c r="D11" t="n">
         <v>6.37627e-08</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1757.436</v>
       </c>
+      <c r="C12" t="n">
+        <v>2425.30405863119</v>
+      </c>
       <c r="D12" t="n">
         <v>6.373989999999999e-08</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1746.766</v>
       </c>
+      <c r="C13" t="n">
+        <v>2414.989826761834</v>
+      </c>
       <c r="D13" t="n">
         <v>6.3729e-08</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1731.362</v>
       </c>
+      <c r="C14" t="n">
+        <v>2403.336425167863</v>
+      </c>
       <c r="D14" t="n">
         <v>6.3716e-08</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1710.801</v>
       </c>
+      <c r="C15" t="n">
+        <v>2377.499701099121</v>
+      </c>
       <c r="D15" t="n">
         <v>6.36922e-08</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1685.238</v>
       </c>
+      <c r="C16" t="n">
+        <v>2352.135844487777</v>
+      </c>
       <c r="D16" t="n">
         <v>6.36945e-08</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1666.843</v>
       </c>
+      <c r="C17" t="n">
+        <v>2333.468595805137</v>
+      </c>
       <c r="D17" t="n">
         <v>6.36918e-08</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1640.389</v>
       </c>
+      <c r="C18" t="n">
+        <v>2310.622323149625</v>
+      </c>
       <c r="D18" t="n">
         <v>6.36817e-08</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1624.023</v>
       </c>
+      <c r="C19" t="n">
+        <v>2293.091393631353</v>
+      </c>
       <c r="D19" t="n">
         <v>6.36817e-08</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1605.438</v>
       </c>
+      <c r="C20" t="n">
+        <v>2272.696968379146</v>
+      </c>
       <c r="D20" t="n">
         <v>6.36643e-08</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1600.409</v>
       </c>
+      <c r="C21" t="n">
+        <v>2270.382478737803</v>
+      </c>
       <c r="D21" t="n">
         <v>6.36642e-08</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1576.464</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2244.064574672223</v>
       </c>
       <c r="D22" t="n">
         <v>6.366399999999999e-08</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2635.925</v>
       </c>
+      <c r="C2" t="n">
+        <v>3471.14822011803</v>
+      </c>
       <c r="D2" t="n">
         <v>6.807770000000001e-08</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>2242.776</v>
       </c>
+      <c r="C3" t="n">
+        <v>2921.449685203173</v>
+      </c>
       <c r="D3" t="n">
         <v>6.74003e-08</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>2148.145</v>
       </c>
+      <c r="C4" t="n">
+        <v>2805.558937405991</v>
+      </c>
       <c r="D4" t="n">
         <v>6.617129999999999e-08</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>2077.364</v>
       </c>
+      <c r="C5" t="n">
+        <v>2734.987733623732</v>
+      </c>
       <c r="D5" t="n">
         <v>6.55808e-08</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>2042.015</v>
       </c>
+      <c r="C6" t="n">
+        <v>2702.751928700992</v>
+      </c>
       <c r="D6" t="n">
         <v>6.53113e-08</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1988.128</v>
       </c>
+      <c r="C7" t="n">
+        <v>2650.159432436502</v>
+      </c>
       <c r="D7" t="n">
         <v>6.51838e-08</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1951.536</v>
       </c>
+      <c r="C8" t="n">
+        <v>2613.731456161337</v>
+      </c>
       <c r="D8" t="n">
         <v>6.51042e-08</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1924.12</v>
       </c>
+      <c r="C9" t="n">
+        <v>2588.363673151795</v>
+      </c>
       <c r="D9" t="n">
         <v>6.50668e-08</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1894.526</v>
       </c>
+      <c r="C10" t="n">
+        <v>2558.731785864685</v>
+      </c>
       <c r="D10" t="n">
         <v>6.50538e-08</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1865.824</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2529.166337481671</v>
       </c>
       <c r="D11" t="n">
         <v>6.50517e-08</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>2115.868</v>
       </c>
+      <c r="C2" t="n">
+        <v>2815.513147352037</v>
+      </c>
       <c r="D2" t="n">
         <v>6.68646e-08</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1994.89</v>
       </c>
+      <c r="C3" t="n">
+        <v>2663.467851756233</v>
+      </c>
       <c r="D3" t="n">
         <v>6.56379e-08</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1947.371</v>
       </c>
+      <c r="C4" t="n">
+        <v>2610.721192668414</v>
+      </c>
       <c r="D4" t="n">
         <v>6.53195e-08</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1922.022</v>
       </c>
+      <c r="C5" t="n">
+        <v>2580.895498089755</v>
+      </c>
       <c r="D5" t="n">
         <v>6.51826e-08</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1896.409</v>
       </c>
+      <c r="C6" t="n">
+        <v>2557.248856581547</v>
+      </c>
       <c r="D6" t="n">
         <v>6.51337e-08</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1877.361</v>
       </c>
+      <c r="C7" t="n">
+        <v>2541.164413550274</v>
+      </c>
       <c r="D7" t="n">
         <v>6.51319e-08</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1847.789</v>
       </c>
+      <c r="C8" t="n">
+        <v>2514.520347358833</v>
+      </c>
       <c r="D8" t="n">
         <v>6.512e-08</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1826.097</v>
       </c>
+      <c r="C9" t="n">
+        <v>2489.604911537104</v>
+      </c>
       <c r="D9" t="n">
         <v>6.512470000000001e-08</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1793.836</v>
       </c>
+      <c r="C10" t="n">
+        <v>2456.954739134393</v>
+      </c>
       <c r="D10" t="n">
         <v>6.51447e-08</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1772.736</v>
       </c>
+      <c r="C11" t="n">
+        <v>2433.992230275316</v>
+      </c>
       <c r="D11" t="n">
         <v>6.5148e-08</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1772.46</v>
       </c>
+      <c r="C12" t="n">
+        <v>2435.822615962971</v>
+      </c>
       <c r="D12" t="n">
         <v>6.514770000000001e-08</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1732.818</v>
       </c>
+      <c r="C13" t="n">
+        <v>2393.782916319463</v>
+      </c>
       <c r="D13" t="n">
         <v>6.51546e-08</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1725.676</v>
       </c>
+      <c r="C14" t="n">
+        <v>2385.75425149155</v>
+      </c>
       <c r="D14" t="n">
         <v>6.515700000000001e-08</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1699.515</v>
       </c>
+      <c r="C15" t="n">
+        <v>2360.319402818955</v>
+      </c>
       <c r="D15" t="n">
         <v>6.51468e-08</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1685.338</v>
       </c>
+      <c r="C16" t="n">
+        <v>2346.499620473312</v>
+      </c>
       <c r="D16" t="n">
         <v>6.51408e-08</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1653.387</v>
       </c>
+      <c r="C17" t="n">
+        <v>2314.130302448684</v>
+      </c>
       <c r="D17" t="n">
         <v>6.516190000000001e-08</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1631.66</v>
       </c>
+      <c r="C18" t="n">
+        <v>2293.186935178948</v>
+      </c>
       <c r="D18" t="n">
         <v>6.514720000000001e-08</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1598.629</v>
       </c>
+      <c r="C19" t="n">
+        <v>2256.150335860247</v>
+      </c>
       <c r="D19" t="n">
         <v>6.516729999999999e-08</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1601.069</v>
       </c>
+      <c r="C20" t="n">
+        <v>2258.580869010679</v>
+      </c>
       <c r="D20" t="n">
         <v>6.51763e-08</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1573.746</v>
       </c>
+      <c r="C21" t="n">
+        <v>2235.021492492712</v>
+      </c>
       <c r="D21" t="n">
         <v>6.517709999999999e-08</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1549.245</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2208.988965637895</v>
       </c>
       <c r="D22" t="n">
         <v>6.51972e-08</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2657.887</v>
       </c>
+      <c r="C2" t="n">
+        <v>3522.297670316287</v>
+      </c>
       <c r="D2" t="n">
         <v>6.869109999999999e-08</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>2193.718</v>
       </c>
+      <c r="C3" t="n">
+        <v>2879.954427507051</v>
+      </c>
       <c r="D3" t="n">
         <v>6.773579999999999e-08</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>2092.929</v>
       </c>
+      <c r="C4" t="n">
+        <v>2755.64681098763</v>
+      </c>
       <c r="D4" t="n">
         <v>6.68213e-08</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>2036.818</v>
       </c>
+      <c r="C5" t="n">
+        <v>2696.511508296964</v>
+      </c>
       <c r="D5" t="n">
         <v>6.6444e-08</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1992.979</v>
       </c>
+      <c r="C6" t="n">
+        <v>2652.845730590333</v>
+      </c>
       <c r="D6" t="n">
         <v>6.62592e-08</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1973.083</v>
       </c>
+      <c r="C7" t="n">
+        <v>2633.665290694923</v>
+      </c>
       <c r="D7" t="n">
         <v>6.61719e-08</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1933.396</v>
       </c>
+      <c r="C8" t="n">
+        <v>2595.160792369262</v>
+      </c>
       <c r="D8" t="n">
         <v>6.61369e-08</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1894.82</v>
       </c>
+      <c r="C9" t="n">
+        <v>2556.211274581343</v>
+      </c>
       <c r="D9" t="n">
         <v>6.6136e-08</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1874.924</v>
       </c>
+      <c r="C10" t="n">
+        <v>2538.253877598401</v>
+      </c>
       <c r="D10" t="n">
         <v>6.61349e-08</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1840.192</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2502.711960838546</v>
       </c>
       <c r="D11" t="n">
         <v>6.61646e-08</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>2112.708</v>
       </c>
+      <c r="C2" t="n">
+        <v>2831.053949149834</v>
+      </c>
       <c r="D2" t="n">
         <v>6.923909999999999e-08</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1977.818</v>
       </c>
+      <c r="C3" t="n">
+        <v>2644.739001090484</v>
+      </c>
       <c r="D3" t="n">
         <v>6.73327e-08</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>1933.114</v>
       </c>
+      <c r="C4" t="n">
+        <v>2594.513529813527</v>
+      </c>
       <c r="D4" t="n">
         <v>6.688940000000001e-08</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1911.507</v>
       </c>
+      <c r="C5" t="n">
+        <v>2572.304740291317</v>
+      </c>
       <c r="D5" t="n">
         <v>6.67038e-08</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1870.091</v>
       </c>
+      <c r="C6" t="n">
+        <v>2533.814546424893</v>
+      </c>
       <c r="D6" t="n">
         <v>6.66288e-08</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1848.106</v>
       </c>
+      <c r="C7" t="n">
+        <v>2514.572413307002</v>
+      </c>
       <c r="D7" t="n">
         <v>6.66054e-08</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1826.383</v>
       </c>
+      <c r="C8" t="n">
+        <v>2491.441528080324</v>
+      </c>
       <c r="D8" t="n">
         <v>6.65822e-08</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1806.192</v>
       </c>
+      <c r="C9" t="n">
+        <v>2470.419335263338</v>
+      </c>
       <c r="D9" t="n">
         <v>6.65943e-08</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1789.047</v>
       </c>
+      <c r="C10" t="n">
+        <v>2453.450072040972</v>
+      </c>
       <c r="D10" t="n">
         <v>6.66098e-08</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1777.308</v>
       </c>
+      <c r="C11" t="n">
+        <v>2442.816256341011</v>
+      </c>
       <c r="D11" t="n">
         <v>6.66092e-08</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1747.524</v>
       </c>
+      <c r="C12" t="n">
+        <v>2410.630155746916</v>
+      </c>
       <c r="D12" t="n">
         <v>6.66359e-08</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1729.993</v>
       </c>
+      <c r="C13" t="n">
+        <v>2393.255189098942</v>
+      </c>
       <c r="D13" t="n">
         <v>6.66293e-08</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1706.314</v>
       </c>
+      <c r="C14" t="n">
+        <v>2369.860434719639</v>
+      </c>
       <c r="D14" t="n">
         <v>6.66455e-08</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1703.838</v>
       </c>
+      <c r="C15" t="n">
+        <v>2367.815451115851</v>
+      </c>
       <c r="D15" t="n">
         <v>6.66379e-08</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1674.799</v>
       </c>
+      <c r="C16" t="n">
+        <v>2339.745079576756</v>
+      </c>
       <c r="D16" t="n">
         <v>6.665789999999999e-08</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1660.743</v>
       </c>
+      <c r="C17" t="n">
+        <v>2322.514503458473</v>
+      </c>
       <c r="D17" t="n">
         <v>6.66758e-08</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1636.787</v>
       </c>
+      <c r="C18" t="n">
+        <v>2300.18362337423</v>
+      </c>
       <c r="D18" t="n">
         <v>6.66753e-08</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1627.471</v>
       </c>
+      <c r="C19" t="n">
+        <v>2292.151915926079</v>
+      </c>
       <c r="D19" t="n">
         <v>6.66815e-08</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1610.084</v>
       </c>
+      <c r="C20" t="n">
+        <v>2273.130597475883</v>
+      </c>
       <c r="D20" t="n">
         <v>6.669580000000001e-08</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1599.406</v>
       </c>
+      <c r="C21" t="n">
+        <v>2264.104358102199</v>
+      </c>
       <c r="D21" t="n">
         <v>6.66883e-08</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1579.482</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2240.883488112794</v>
       </c>
       <c r="D22" t="n">
         <v>6.670460000000001e-08</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>2567.581</v>
       </c>
+      <c r="C2" t="n">
+        <v>3439.737213157986</v>
+      </c>
       <c r="D2" t="n">
         <v>6.91829e-08</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>2137.53</v>
       </c>
+      <c r="C3" t="n">
+        <v>2815.891814583839</v>
+      </c>
       <c r="D3" t="n">
         <v>6.82448e-08</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>2026.95</v>
       </c>
+      <c r="C4" t="n">
+        <v>2682.747453652637</v>
+      </c>
       <c r="D4" t="n">
         <v>6.7658e-08</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1991.235</v>
       </c>
+      <c r="C5" t="n">
+        <v>2643.499696491502</v>
+      </c>
       <c r="D5" t="n">
         <v>6.74376e-08</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1963.62</v>
       </c>
+      <c r="C6" t="n">
+        <v>2620.238635989926</v>
+      </c>
       <c r="D6" t="n">
         <v>6.73161e-08</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1925.438</v>
       </c>
+      <c r="C7" t="n">
+        <v>2579.667852362258</v>
+      </c>
       <c r="D7" t="n">
         <v>6.72919e-08</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1883.437</v>
       </c>
+      <c r="C8" t="n">
+        <v>2539.761112147605</v>
+      </c>
       <c r="D8" t="n">
         <v>6.72747e-08</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1853.945</v>
       </c>
+      <c r="C9" t="n">
+        <v>2513.259520944326</v>
+      </c>
       <c r="D9" t="n">
         <v>6.73049e-08</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1835.76</v>
       </c>
+      <c r="C10" t="n">
+        <v>2493.107445635282</v>
+      </c>
       <c r="D10" t="n">
         <v>6.735029999999999e-08</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1804.907</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2460.811598120684</v>
       </c>
       <c r="D11" t="n">
         <v>6.73891e-08</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>2113.974</v>
       </c>
+      <c r="C2" t="n">
+        <v>2815.871994705783</v>
+      </c>
       <c r="D2" t="n">
         <v>6.92013e-08</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1970.511</v>
       </c>
+      <c r="C3" t="n">
+        <v>2619.602129415383</v>
+      </c>
       <c r="D3" t="n">
         <v>6.80859e-08</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1914.942</v>
       </c>
+      <c r="C4" t="n">
+        <v>2557.777422792895</v>
+      </c>
       <c r="D4" t="n">
         <v>6.778620000000001e-08</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1902.173</v>
       </c>
+      <c r="C5" t="n">
+        <v>2544.321716035151</v>
+      </c>
       <c r="D5" t="n">
         <v>6.76946e-08</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1868.581</v>
       </c>
+      <c r="C6" t="n">
+        <v>2512.505592456963</v>
+      </c>
       <c r="D6" t="n">
         <v>6.76566e-08</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1838.446</v>
       </c>
+      <c r="C7" t="n">
+        <v>2483.769710022842</v>
+      </c>
       <c r="D7" t="n">
         <v>6.76498e-08</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1817.64</v>
       </c>
+      <c r="C8" t="n">
+        <v>2461.68416914409</v>
+      </c>
       <c r="D8" t="n">
         <v>6.7673e-08</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1803.327</v>
       </c>
+      <c r="C9" t="n">
+        <v>2448.912450163897</v>
+      </c>
       <c r="D9" t="n">
         <v>6.76783e-08</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1772.581</v>
       </c>
+      <c r="C10" t="n">
+        <v>2417.497347878381</v>
+      </c>
       <c r="D10" t="n">
         <v>6.77146e-08</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1767.578</v>
       </c>
+      <c r="C11" t="n">
+        <v>2412.623564087847</v>
+      </c>
       <c r="D11" t="n">
         <v>6.77324e-08</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1732.769</v>
       </c>
+      <c r="C12" t="n">
+        <v>2378.42937405697</v>
+      </c>
       <c r="D12" t="n">
         <v>6.77558e-08</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1724.228</v>
       </c>
+      <c r="C13" t="n">
+        <v>2368.409692563174</v>
+      </c>
       <c r="D13" t="n">
         <v>6.77394e-08</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1709.091</v>
       </c>
+      <c r="C14" t="n">
+        <v>2354.280927838032</v>
+      </c>
       <c r="D14" t="n">
         <v>6.77677e-08</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1695.075</v>
       </c>
+      <c r="C15" t="n">
+        <v>2339.313108393941</v>
+      </c>
       <c r="D15" t="n">
         <v>6.77724e-08</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1687.281</v>
       </c>
+      <c r="C16" t="n">
+        <v>2331.678353283453</v>
+      </c>
       <c r="D16" t="n">
         <v>6.779280000000001e-08</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1650.533</v>
       </c>
+      <c r="C17" t="n">
+        <v>2294.025256394212</v>
+      </c>
       <c r="D17" t="n">
         <v>6.77997e-08</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1647.34</v>
       </c>
+      <c r="C18" t="n">
+        <v>2292.713696429185</v>
+      </c>
       <c r="D18" t="n">
         <v>6.78108e-08</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1630.251</v>
       </c>
+      <c r="C19" t="n">
+        <v>2273.131949050485</v>
+      </c>
       <c r="D19" t="n">
         <v>6.782240000000001e-08</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1608.278</v>
       </c>
+      <c r="C20" t="n">
+        <v>2251.047291126069</v>
+      </c>
       <c r="D20" t="n">
         <v>6.7829e-08</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1597.924</v>
       </c>
+      <c r="C21" t="n">
+        <v>2240.593252081722</v>
+      </c>
       <c r="D21" t="n">
         <v>6.78533e-08</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1572.524</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2217.493115999557</v>
       </c>
       <c r="D22" t="n">
         <v>6.78604e-08</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>2010.119</v>
       </c>
+      <c r="C2" t="n">
+        <v>2917.68223969468</v>
+      </c>
       <c r="D2" t="n">
         <v>7.01467e-08</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1650.378</v>
       </c>
+      <c r="C3" t="n">
+        <v>2363.617240453161</v>
+      </c>
       <c r="D3" t="n">
         <v>6.901170000000001e-08</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1566.011</v>
       </c>
+      <c r="C4" t="n">
+        <v>2250.56214544429</v>
+      </c>
       <c r="D4" t="n">
         <v>6.871849999999999e-08</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1517.161</v>
       </c>
+      <c r="C5" t="n">
+        <v>2197.75155972025</v>
+      </c>
       <c r="D5" t="n">
         <v>6.859489999999999e-08</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1495.033</v>
       </c>
+      <c r="C6" t="n">
+        <v>2179.473497512298</v>
+      </c>
       <c r="D6" t="n">
         <v>6.85015e-08</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1462.876</v>
       </c>
+      <c r="C7" t="n">
+        <v>2146.041185403216</v>
+      </c>
       <c r="D7" t="n">
         <v>6.84917e-08</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1428.973</v>
       </c>
+      <c r="C8" t="n">
+        <v>2112.5130624722</v>
+      </c>
       <c r="D8" t="n">
         <v>6.84907e-08</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>1406.718</v>
       </c>
+      <c r="C9" t="n">
+        <v>2095.23243794881</v>
+      </c>
       <c r="D9" t="n">
         <v>6.850089999999999e-08</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>1368.721</v>
       </c>
+      <c r="C10" t="n">
+        <v>2052.789079685184</v>
+      </c>
       <c r="D10" t="n">
         <v>6.853689999999999e-08</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>1358.596</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2047.111465543965</v>
       </c>
       <c r="D11" t="n">
         <v>6.85614e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
@@ -565,7 +565,7 @@
         <v>2132.121</v>
       </c>
       <c r="C2" t="n">
-        <v>2807.523377950308</v>
+        <v>1094.870530776381</v>
       </c>
       <c r="D2" t="n">
         <v>6.61225e-08</v>
@@ -598,16 +598,13 @@
         <v>-76840.01227654665</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.685909701608607e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3154.322157603146</v>
+        <v>474.345578480541</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000024562e-08</v>
+        <v>7.570426503820087e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8126238409191623</v>
+        <v>0.9983479465596755</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>2067.484</v>
       </c>
       <c r="C3" t="n">
-        <v>2738.183857971791</v>
+        <v>989.0292728292011</v>
       </c>
       <c r="D3" t="n">
         <v>6.50528e-08</v>
@@ -651,16 +648,13 @@
         <v>-76671.13656891391</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.70066461649694e-13</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3073.389084395707</v>
+        <v>604.4250256161832</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000112659e-08</v>
+        <v>1.004604697402223e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8127361061187315</v>
+        <v>0.9843343895703431</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>2021.42</v>
       </c>
       <c r="C4" t="n">
-        <v>2692.53906638855</v>
+        <v>947.436939820391</v>
       </c>
       <c r="D4" t="n">
         <v>6.45043e-08</v>
@@ -704,16 +698,13 @@
         <v>-61176.13245778675</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.23662972393889e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3011.901859888208</v>
+        <v>731.2727410041964</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000001930405e-08</v>
+        <v>3.677216066051029e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8128312407084796</v>
+        <v>0.9210136086091268</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>1972.845</v>
       </c>
       <c r="C5" t="n">
-        <v>2644.353898922284</v>
+        <v>1643.567073579305</v>
       </c>
       <c r="D5" t="n">
         <v>6.417e-08</v>
@@ -757,16 +748,13 @@
         <v>-40546.82309079404</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.709181305967928e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2958.173639205987</v>
+        <v>0.8368644407497948</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000127682e-08</v>
+        <v>2.16433728313556e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8129965467384119</v>
+        <v>0.8804309197724549</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>1933.767</v>
       </c>
       <c r="C6" t="n">
-        <v>2608.047586539176</v>
+        <v>1494.152164821343</v>
       </c>
       <c r="D6" t="n">
         <v>6.395500000000001e-08</v>
@@ -810,16 +798,13 @@
         <v>-23748.45357520839</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.277472911906481e-13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2908.799405817799</v>
+        <v>154.817395392637</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000001034e-08</v>
+        <v>2.505208759659949e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8132103789963276</v>
+        <v>0.8851052089346079</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>1906.642</v>
       </c>
       <c r="C7" t="n">
-        <v>2580.492000061952</v>
+        <v>1430.417189542661</v>
       </c>
       <c r="D7" t="n">
         <v>6.38219e-08</v>
@@ -863,16 +848,13 @@
         <v>-6398.589481440563</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.201259017102285e-14</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2863.506652860962</v>
+        <v>71.30471142302578</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000026023e-08</v>
+        <v>7.376858273517803e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8134185748916484</v>
+        <v>0.9687613752498452</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>1859.01</v>
       </c>
       <c r="C8" t="n">
-        <v>2533.804992946663</v>
+        <v>1596.348108806094</v>
       </c>
       <c r="D8" t="n">
         <v>6.372e-08</v>
@@ -916,16 +898,13 @@
         <v>-420.6473918224783</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.141136021500345e-14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2821.656266362052</v>
+        <v>0.8332330503071811</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000016933e-08</v>
+        <v>2.00892282003739e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8136481426912326</v>
+        <v>0.8914396821464737</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +915,7 @@
         <v>1833.137</v>
       </c>
       <c r="C9" t="n">
-        <v>2506.105417190169</v>
+        <v>1601.582830034657</v>
       </c>
       <c r="D9" t="n">
         <v>6.364490000000001e-08</v>
@@ -969,16 +948,13 @@
         <v>12090.36223906311</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.55905770065459e-14</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2784.444589544122</v>
+        <v>1.606604638643767</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000025275e-08</v>
+        <v>2.199649655667432e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.813854540302587</v>
+        <v>0.8794902196354502</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +965,7 @@
         <v>1797.168</v>
       </c>
       <c r="C10" t="n">
-        <v>2471.639214550307</v>
+        <v>1587.459711153481</v>
       </c>
       <c r="D10" t="n">
         <v>6.357000000000001e-08</v>
@@ -1022,16 +998,13 @@
         <v>19482.54587506013</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.941494330057665e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2749.097279000534</v>
+        <v>2.463519219137631</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000116808e-08</v>
+        <v>2.163382340632012e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8140451335626275</v>
+        <v>0.8813501698174314</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1015,7 @@
         <v>1780.3</v>
       </c>
       <c r="C11" t="n">
-        <v>2455.43954741523</v>
+        <v>2125.675328271122</v>
       </c>
       <c r="D11" t="n">
         <v>6.35288e-08</v>
@@ -1075,16 +1048,13 @@
         <v>-16897.91057253166</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.869407702567255e-14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2717.97926798109</v>
+        <v>6.111260075216586</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000467e-08</v>
+        <v>2.702351529767329e-07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.814230204809796</v>
+        <v>0.5489858209826964</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1211,7 @@
         <v>2058.602</v>
       </c>
       <c r="C2" t="n">
-        <v>2753.21303495648</v>
+        <v>948.9042746567166</v>
       </c>
       <c r="D2" t="n">
         <v>6.74794e-08</v>
@@ -1274,16 +1244,13 @@
         <v>7974.760763267007</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.640397004616299e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3001.585328281391</v>
+        <v>613.6738852179915</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000001899757e-08</v>
+        <v>1.452787541046652e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8140293700987243</v>
+        <v>0.9717235318329388</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>1919.579</v>
       </c>
       <c r="C3" t="n">
-        <v>2575.289607357818</v>
+        <v>901.0472308856123</v>
       </c>
       <c r="D3" t="n">
         <v>6.77274e-08</v>
@@ -1327,16 +1294,13 @@
         <v>-4105.444491448474</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.406035629773169e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2874.875828182493</v>
+        <v>665.4582474800226</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000067825e-08</v>
+        <v>2.770325007440454e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.814521829023492</v>
+        <v>0.9345633615000851</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1311,7 @@
         <v>1887.444</v>
       </c>
       <c r="C4" t="n">
-        <v>2533.687506464527</v>
+        <v>1430.643585200401</v>
       </c>
       <c r="D4" t="n">
         <v>6.78196e-08</v>
@@ -1380,16 +1344,13 @@
         <v>3667.350732222937</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.713748635193583e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2824.137356664117</v>
+        <v>25.20991690288491</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.00000000001881e-08</v>
+        <v>4.428647833699843e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8146754569102467</v>
+        <v>0.9939493342118414</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1361,7 @@
         <v>1857.86</v>
       </c>
       <c r="C5" t="n">
-        <v>2506.384696205068</v>
+        <v>1398.808379079512</v>
       </c>
       <c r="D5" t="n">
         <v>6.78706e-08</v>
@@ -1433,16 +1394,13 @@
         <v>7557.655430969498</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.798274215678066e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2788.772242124763</v>
+        <v>49.68852575912396</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000615846e-08</v>
+        <v>4.949576860026817e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8147582496974379</v>
+        <v>0.9974046943043232</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1411,7 @@
         <v>1834.953</v>
       </c>
       <c r="C6" t="n">
-        <v>2483.790095774002</v>
+        <v>1555.644751320387</v>
       </c>
       <c r="D6" t="n">
         <v>6.92236e-08</v>
@@ -1486,16 +1444,13 @@
         <v>-65630.98061932939</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.545114213889972e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2761.7199542041</v>
+        <v>0.1463460272504871</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000001421993e-08</v>
+        <v>1.829899976090441e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8148045760751251</v>
+        <v>0.8971748884137132</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1461,7 @@
         <v>1813.986</v>
       </c>
       <c r="C7" t="n">
-        <v>2462.761100593423</v>
+        <v>1386.249904876068</v>
       </c>
       <c r="D7" t="n">
         <v>6.90902e-08</v>
@@ -1539,16 +1494,13 @@
         <v>-56895.36174195277</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.847866497245891e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2733.489103789219</v>
+        <v>207.898987563096</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000706327e-08</v>
+        <v>3.036418238334654e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8148714646566978</v>
+        <v>0.8777393941534261</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1511,7 @@
         <v>1773.481</v>
       </c>
       <c r="C8" t="n">
-        <v>2422.163542668291</v>
+        <v>1390.204644799358</v>
       </c>
       <c r="D8" t="n">
         <v>6.90448e-08</v>
@@ -1592,16 +1544,13 @@
         <v>-47327.05424900413</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.735499326061547e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2707.103229311077</v>
+        <v>166.9306021627456</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000070395e-08</v>
+        <v>2.284090647313374e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8149580221425988</v>
+        <v>0.8937325689438212</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1561,7 @@
         <v>1765.362</v>
       </c>
       <c r="C9" t="n">
-        <v>2416.007993416801</v>
+        <v>1506.614330470899</v>
       </c>
       <c r="D9" t="n">
         <v>6.89808e-08</v>
@@ -1645,16 +1594,13 @@
         <v>-48963.4742857961</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.43947090069047e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2683.432122226611</v>
+        <v>3.421346485615709</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000034529e-08</v>
+        <v>1.53605963287363e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8150450636151971</v>
+        <v>0.9115693629838368</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1611,7 @@
         <v>1750.148</v>
       </c>
       <c r="C10" t="n">
-        <v>2401.869613511418</v>
+        <v>1537.021456882584</v>
       </c>
       <c r="D10" t="n">
         <v>6.896299999999999e-08</v>
@@ -1698,16 +1644,13 @@
         <v>-47516.06608020557</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.328699988977746e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2662.023493568865</v>
+        <v>0.9921835544130141</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000004330382e-08</v>
+        <v>1.991092180368192e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8151516295079959</v>
+        <v>0.8915094781055738</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1661,7 @@
         <v>1733.737</v>
       </c>
       <c r="C11" t="n">
-        <v>2385.651729433416</v>
+        <v>1542.314273456329</v>
       </c>
       <c r="D11" t="n">
         <v>6.89257e-08</v>
@@ -1751,16 +1694,13 @@
         <v>-47657.55043392426</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.709030642352584e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2641.899796822844</v>
+        <v>2.101943125121017</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000022788e-08</v>
+        <v>2.506662824169382e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8152982860708917</v>
+        <v>0.8766791046957985</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1711,7 @@
         <v>1708.16</v>
       </c>
       <c r="C12" t="n">
-        <v>2357.434366434806</v>
+        <v>1530.051935264054</v>
       </c>
       <c r="D12" t="n">
         <v>6.88937e-08</v>
@@ -1804,16 +1744,13 @@
         <v>-43038.86747210872</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.241992900452892e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2623.157901990913</v>
+        <v>2.082407193222901</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000379033e-08</v>
+        <v>2.154573405077518e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8154835925613381</v>
+        <v>0.8833510505348977</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1761,7 @@
         <v>1704.881</v>
       </c>
       <c r="C13" t="n">
-        <v>2355.130291103077</v>
+        <v>2021.778507518427</v>
       </c>
       <c r="D13" t="n">
         <v>6.88594e-08</v>
@@ -1857,16 +1794,13 @@
         <v>-49505.18196301869</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.842324758274235e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2604.469220382614</v>
+        <v>0.9194178828246626</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000140426e-08</v>
+        <v>2.350101034047378e-07</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8156713198400521</v>
+        <v>0.558678910018939</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1811,7 @@
         <v>1677.718</v>
       </c>
       <c r="C14" t="n">
-        <v>2329.188217425468</v>
+        <v>2016.628268304938</v>
       </c>
       <c r="D14" t="n">
         <v>6.88173e-08</v>
@@ -1910,16 +1844,13 @@
         <v>-44963.83211327767</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.030577065505473e-07</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2584.732100695554</v>
+        <v>1.311130160637717</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000003581505e-08</v>
+        <v>2.431281072517196e-07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8159098350356051</v>
+        <v>0.5567674176865393</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1861,7 @@
         <v>1676.577</v>
       </c>
       <c r="C15" t="n">
-        <v>2327.744829474304</v>
+        <v>2015.117696856358</v>
       </c>
       <c r="D15" t="n">
         <v>6.84767e-08</v>
@@ -1963,16 +1894,13 @@
         <v>243.5865482251355</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.126298726775029e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2563.776064966605</v>
+        <v>3.934519649732227</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000002325532e-08</v>
+        <v>2.571001604513065e-07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8161456690907986</v>
+        <v>0.5536591172169349</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1911,7 @@
         <v>1654.581</v>
       </c>
       <c r="C16" t="n">
-        <v>2305.552802678888</v>
+        <v>2009.387634319245</v>
       </c>
       <c r="D16" t="n">
         <v>6.84863e-08</v>
@@ -2016,16 +1944,13 @@
         <v>4049.962157504391</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.236013066885747e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2542.982383236801</v>
+        <v>3.739612657736624</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000321449e-08</v>
+        <v>2.662225682665991e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8163903954638848</v>
+        <v>0.5517059771891365</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1961,7 @@
         <v>1640.194</v>
       </c>
       <c r="C17" t="n">
-        <v>2291.357626869064</v>
+        <v>1999.63370931346</v>
       </c>
       <c r="D17" t="n">
         <v>6.854860000000001e-08</v>
@@ -2069,16 +1994,13 @@
         <v>-19840.82956715482</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.1592652297334e-10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2522.901797562265</v>
+        <v>3.534600584496292</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000049537e-08</v>
+        <v>2.696871347850258e-07</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8166355055745373</v>
+        <v>0.5510985514119024</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2011,7 @@
         <v>1629.852</v>
       </c>
       <c r="C18" t="n">
-        <v>2282.487186856989</v>
+        <v>2002.593445703546</v>
       </c>
       <c r="D18" t="n">
         <v>6.841669999999999e-08</v>
@@ -2122,16 +2044,13 @@
         <v>19519.92006611818</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.126577163053326e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2500.26313363378</v>
+        <v>4.654263288721291</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.00000000036226e-08</v>
+        <v>2.964135419467869e-07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8168914354971314</v>
+        <v>0.5455488203248282</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2061,7 @@
         <v>1603.71</v>
       </c>
       <c r="C19" t="n">
-        <v>2251.031063695554</v>
+        <v>1999.232963309181</v>
       </c>
       <c r="D19" t="n">
         <v>6.840150000000001e-08</v>
@@ -2175,16 +2094,13 @@
         <v>16628.51016872962</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.262996572198026e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2478.894211949943</v>
+        <v>4.474669835934685</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000344816e-08</v>
+        <v>3.13653367135986e-07</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8171500330217488</v>
+        <v>0.5422610764203687</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2111,7 @@
         <v>1584.776</v>
       </c>
       <c r="C20" t="n">
-        <v>2242.953220579035</v>
+        <v>1993.385982234633</v>
       </c>
       <c r="D20" t="n">
         <v>6.8376e-08</v>
@@ -2228,16 +2144,13 @@
         <v>14239.27019081562</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.226941585207567e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2457.371874773199</v>
+        <v>4.19727690996783</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000338555e-08</v>
+        <v>3.269681055491526e-07</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8174073760261732</v>
+        <v>0.539904520418545</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2161,7 @@
         <v>1565.679</v>
       </c>
       <c r="C21" t="n">
-        <v>2215.682847355326</v>
+        <v>1983.239800582101</v>
       </c>
       <c r="D21" t="n">
         <v>6.84333e-08</v>
@@ -2281,16 +2194,13 @@
         <v>5873.204082927272</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.197617281222268e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2435.480744332806</v>
+        <v>4.031163853067191</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000135527e-08</v>
+        <v>3.330417379036776e-07</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8176774955586625</v>
+        <v>0.5390073137604646</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2211,7 @@
         <v>1548.366</v>
       </c>
       <c r="C22" t="n">
-        <v>2197.425012083357</v>
+        <v>1390.569904662807</v>
       </c>
       <c r="D22" t="n">
         <v>6.84467e-08</v>
@@ -2334,16 +2244,13 @@
         <v>7324.253338262391</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.988510286001275e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2413.714908084446</v>
+        <v>13.62686927283053</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000435508e-08</v>
+        <v>1.368099589224512e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8179412466224817</v>
+        <v>0.9245403426882955</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2407,7 @@
         <v>2130</v>
       </c>
       <c r="C2" t="n">
-        <v>2837.081579207963</v>
+        <v>1249.644433303666</v>
       </c>
       <c r="D2" t="n">
         <v>6.740070000000001e-08</v>
@@ -2533,16 +2440,13 @@
         <v>-57612.37529112391</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.935639218335637e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3124.097576951988</v>
+        <v>295.2042240367358</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000353349e-08</v>
+        <v>1.016208367952012e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8130108639113784</v>
+        <v>0.9588815371466547</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2457,7 @@
         <v>1990.322</v>
       </c>
       <c r="C3" t="n">
-        <v>2660.542058751909</v>
+        <v>967.3972752933248</v>
       </c>
       <c r="D3" t="n">
         <v>6.55186e-08</v>
@@ -2586,16 +2490,13 @@
         <v>-80256.39060911685</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.997280937048963e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2980.686290916395</v>
+        <v>569.296932134357</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000160544e-08</v>
+        <v>9.382446038492038e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8133994860999627</v>
+        <v>0.9930639579693026</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2507,7 @@
         <v>1963.209</v>
       </c>
       <c r="C4" t="n">
-        <v>2628.628209015238</v>
+        <v>1461.972866140632</v>
       </c>
       <c r="D4" t="n">
         <v>6.47311e-08</v>
@@ -2639,16 +2540,13 @@
         <v>-51535.25844373357</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.577927479512069e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2926.924640818975</v>
+        <v>39.73777922089883</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000092494e-08</v>
+        <v>5.232598308505217e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8135096614813595</v>
+        <v>0.9856229562324577</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2557,7 @@
         <v>1928.942</v>
       </c>
       <c r="C5" t="n">
-        <v>2593.96370535419</v>
+        <v>1446.554236026771</v>
       </c>
       <c r="D5" t="n">
         <v>6.434270000000001e-08</v>
@@ -2692,16 +2590,13 @@
         <v>-15732.08497911205</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.068582775005646e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2889.730856509508</v>
+        <v>83.02458803676932</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000130792e-08</v>
+        <v>8.475402074509384e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8135940824648769</v>
+        <v>0.9583397522470644</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2607,7 @@
         <v>1890.948</v>
       </c>
       <c r="C6" t="n">
-        <v>2556.357443551944</v>
+        <v>1576.392212809065</v>
       </c>
       <c r="D6" t="n">
         <v>6.414810000000001e-08</v>
@@ -2745,16 +2640,13 @@
         <v>1610.646372966079</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.294856708039462e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2857.708439011398</v>
+        <v>34.53166005498817</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000141992e-08</v>
+        <v>2.038043929988759e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8137013118070346</v>
+        <v>0.8932134060636459</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2657,7 @@
         <v>1865.042</v>
       </c>
       <c r="C7" t="n">
-        <v>2533.408284946267</v>
+        <v>1597.429261181542</v>
       </c>
       <c r="D7" t="n">
         <v>6.399980000000001e-08</v>
@@ -2798,16 +2690,13 @@
         <v>19151.64821697749</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.790135062023177e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2827.965888007551</v>
+        <v>0.008972922196078141</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000168204e-08</v>
+        <v>2.040274602368985e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.813818146844563</v>
+        <v>0.8861970518618226</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2707,7 @@
         <v>1854.873</v>
       </c>
       <c r="C8" t="n">
-        <v>2520.213525785581</v>
+        <v>1595.663785999598</v>
       </c>
       <c r="D8" t="n">
         <v>6.39136e-08</v>
@@ -2851,16 +2740,13 @@
         <v>-17379.51475196866</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.024899505934977e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2799.830358196889</v>
+        <v>0.07140134897650866</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000858937e-08</v>
+        <v>2.194866181486246e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8139686487906279</v>
+        <v>0.8814834554863403</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2757,7 @@
         <v>1837.504</v>
       </c>
       <c r="C9" t="n">
-        <v>2505.401128092849</v>
+        <v>1585.066064659405</v>
       </c>
       <c r="D9" t="n">
         <v>6.385170000000001e-08</v>
@@ -2904,16 +2790,13 @@
         <v>-18265.96631159286</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.898674031924192e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2772.536949719294</v>
+        <v>0.2028158999926046</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000152786e-08</v>
+        <v>2.18012391543485e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8141281714136135</v>
+        <v>0.8860475813439096</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2807,7 @@
         <v>1811.805</v>
       </c>
       <c r="C10" t="n">
-        <v>2480.714576479284</v>
+        <v>1584.23398079579</v>
       </c>
       <c r="D10" t="n">
         <v>6.38007e-08</v>
@@ -2957,16 +2840,13 @@
         <v>-17429.16732465491</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.021404550313151e-12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2746.10559054189</v>
+        <v>0.4550877187333136</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000450889e-08</v>
+        <v>2.309423102113633e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8143032206753101</v>
+        <v>0.8823566229855631</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2857,7 @@
         <v>1783.946</v>
       </c>
       <c r="C11" t="n">
-        <v>2453.30077945554</v>
+        <v>16430.97030124517</v>
       </c>
       <c r="D11" t="n">
         <v>6.37627e-08</v>
@@ -3010,10 +2890,7 @@
         <v>-16688.27394000787</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.680692204652808e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2720.32384039339</v>
+        <v>-13930.27014697986</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000717e-08</v>
@@ -3030,7 +2907,7 @@
         <v>1757.436</v>
       </c>
       <c r="C12" t="n">
-        <v>2425.30405863119</v>
+        <v>16155.57063786163</v>
       </c>
       <c r="D12" t="n">
         <v>6.373989999999999e-08</v>
@@ -3063,10 +2940,7 @@
         <v>-15769.0620547541</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.944154481043606e-12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2694.545242986159</v>
+        <v>-13675.71055373312</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000052814e-08</v>
@@ -3083,7 +2957,7 @@
         <v>1746.766</v>
       </c>
       <c r="C13" t="n">
-        <v>2414.989826761834</v>
+        <v>15235.61036253842</v>
       </c>
       <c r="D13" t="n">
         <v>6.3729e-08</v>
@@ -3116,10 +2990,7 @@
         <v>-16253.52181116075</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.449466072159275e-14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2669.333430884795</v>
+        <v>-12771.35602464439</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000209167e-08</v>
@@ -3136,7 +3007,7 @@
         <v>1731.362</v>
       </c>
       <c r="C14" t="n">
-        <v>2403.336425167863</v>
+        <v>15037.25529938782</v>
       </c>
       <c r="D14" t="n">
         <v>6.3716e-08</v>
@@ -3169,10 +3040,7 @@
         <v>-16715.06673198813</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.609665042640764e-07</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2644.386817820363</v>
+        <v>-12594.42668581968</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000003700823e-08</v>
@@ -3189,7 +3057,7 @@
         <v>1710.801</v>
       </c>
       <c r="C15" t="n">
-        <v>2377.499701099121</v>
+        <v>1539.84484541638</v>
       </c>
       <c r="D15" t="n">
         <v>6.36922e-08</v>
@@ -3222,16 +3090,13 @@
         <v>-16117.76919812736</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.756212343463959e-12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2619.210287062468</v>
+        <v>0.01039461133772433</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000114633e-08</v>
+        <v>2.338531671599793e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8153244681154601</v>
+        <v>0.8821216909132196</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3107,7 @@
         <v>1685.238</v>
       </c>
       <c r="C16" t="n">
-        <v>2352.135844487777</v>
+        <v>14559.77045751831</v>
       </c>
       <c r="D16" t="n">
         <v>6.36945e-08</v>
@@ -3275,10 +3140,7 @@
         <v>-15374.21500809582</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.496960890675319e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2594.29855900179</v>
+        <v>-12155.59684593163</v>
       </c>
       <c r="AA16" t="n">
         <v>1.00000000642978e-08</v>
@@ -3295,7 +3157,7 @@
         <v>1666.843</v>
       </c>
       <c r="C17" t="n">
-        <v>2333.468595805137</v>
+        <v>14071.25295494495</v>
       </c>
       <c r="D17" t="n">
         <v>6.36918e-08</v>
@@ -3328,10 +3190,7 @@
         <v>-15401.70994721583</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.389098823756533e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2569.430394762981</v>
+        <v>-11684.93366641788</v>
       </c>
       <c r="AA17" t="n">
         <v>1.00000000006778e-08</v>
@@ -3348,7 +3207,7 @@
         <v>1640.389</v>
       </c>
       <c r="C18" t="n">
-        <v>2310.622323149625</v>
+        <v>14023.48158143559</v>
       </c>
       <c r="D18" t="n">
         <v>6.36817e-08</v>
@@ -3381,10 +3240,7 @@
         <v>-14606.28364334215</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.446120653530682e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2545.384582301588</v>
+        <v>-11657.81343539314</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000001617385e-08</v>
@@ -3401,7 +3257,7 @@
         <v>1624.023</v>
       </c>
       <c r="C19" t="n">
-        <v>2293.091393631353</v>
+        <v>13878.88818929873</v>
       </c>
       <c r="D19" t="n">
         <v>6.36817e-08</v>
@@ -3434,10 +3290,7 @@
         <v>-14335.54501288281</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.198463456871953e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2521.233104624443</v>
+        <v>-11533.24893510504</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000075597e-08</v>
@@ -3454,7 +3307,7 @@
         <v>1605.438</v>
       </c>
       <c r="C20" t="n">
-        <v>2272.696968379146</v>
+        <v>13659.65699642102</v>
       </c>
       <c r="D20" t="n">
         <v>6.36643e-08</v>
@@ -3487,10 +3340,7 @@
         <v>-14260.04878831147</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.231359391734711e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2497.263868741764</v>
+        <v>-11333.01531261729</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000010916e-08</v>
@@ -3507,7 +3357,7 @@
         <v>1600.409</v>
       </c>
       <c r="C21" t="n">
-        <v>2270.382478737803</v>
+        <v>13644.34346773503</v>
       </c>
       <c r="D21" t="n">
         <v>6.36642e-08</v>
@@ -3540,10 +3390,7 @@
         <v>-15288.69473552221</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.990481872477043e-11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2474.079850377143</v>
+        <v>-11337.9240774746</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000005916e-08</v>
@@ -3560,7 +3407,7 @@
         <v>1576.464</v>
       </c>
       <c r="C22" t="n">
-        <v>2244.064574672223</v>
+        <v>13613.8078729531</v>
       </c>
       <c r="D22" t="n">
         <v>6.366399999999999e-08</v>
@@ -3593,10 +3440,7 @@
         <v>-14503.35821236979</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.640809110827982e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2450.656159830546</v>
+        <v>-11327.40247662773</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000089927e-08</v>
@@ -3759,7 +3603,7 @@
         <v>2635.925</v>
       </c>
       <c r="C2" t="n">
-        <v>3471.14822011803</v>
+        <v>1285.368918660668</v>
       </c>
       <c r="D2" t="n">
         <v>6.807770000000001e-08</v>
@@ -3792,16 +3636,13 @@
         <v>-33913.17346430986</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.335479054312013e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3724.855063932422</v>
+        <v>403.3163840084686</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000185512e-08</v>
+        <v>6.086280747818061e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.811194722778607</v>
+        <v>0.9937463566227474</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3653,7 @@
         <v>2242.776</v>
       </c>
       <c r="C3" t="n">
-        <v>2921.449685203173</v>
+        <v>1304.725419494483</v>
       </c>
       <c r="D3" t="n">
         <v>6.74003e-08</v>
@@ -3845,16 +3686,13 @@
         <v>-59676.98683048016</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.15787692821595e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3272.142500169624</v>
+        <v>290.3222131962752</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000007171e-08</v>
+        <v>9.821300772384196e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8123093237459992</v>
+        <v>0.9594754929830314</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3703,7 @@
         <v>2148.145</v>
       </c>
       <c r="C4" t="n">
-        <v>2805.558937405991</v>
+        <v>1076.929121958463</v>
       </c>
       <c r="D4" t="n">
         <v>6.617129999999999e-08</v>
@@ -3898,16 +3736,13 @@
         <v>-88793.05783803968</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.535052391839412e-13</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3149.705858993187</v>
+        <v>503.8231645183567</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000011272e-08</v>
+        <v>7.730438484554312e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8125806612880909</v>
+        <v>0.9984943691159311</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3753,7 @@
         <v>2077.364</v>
       </c>
       <c r="C5" t="n">
-        <v>2734.987733623732</v>
+        <v>994.0645622486779</v>
       </c>
       <c r="D5" t="n">
         <v>6.55808e-08</v>
@@ -3951,16 +3786,13 @@
         <v>-78445.74332960373</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.007370219226665e-13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3082.660736637521</v>
+        <v>586.7065135634822</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.00000000001852e-08</v>
+        <v>1.250627507150612e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8127328977220692</v>
+        <v>0.974065879456241</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3803,7 @@
         <v>2042.015</v>
       </c>
       <c r="C6" t="n">
-        <v>2702.751928700992</v>
+        <v>952.5989853563259</v>
       </c>
       <c r="D6" t="n">
         <v>6.53113e-08</v>
@@ -4004,16 +3836,13 @@
         <v>-66733.2851430825</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.136330487606972e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3026.970313126165</v>
+        <v>623.7578553820227</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000149396e-08</v>
+        <v>1.002792660474804e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8128842293572777</v>
+        <v>0.9943590559131756</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3853,7 @@
         <v>1988.128</v>
       </c>
       <c r="C7" t="n">
-        <v>2650.159432436502</v>
+        <v>933.5347359648356</v>
       </c>
       <c r="D7" t="n">
         <v>6.51838e-08</v>
@@ -4057,16 +3886,13 @@
         <v>-40833.41244077377</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.773676998252171e-12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2975.443512917976</v>
+        <v>631.5895831461838</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000152931e-08</v>
+        <v>1.072904757210729e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8130514773053217</v>
+        <v>0.9932468597790959</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3903,7 @@
         <v>1951.536</v>
       </c>
       <c r="C8" t="n">
-        <v>2613.731456161337</v>
+        <v>1482.068651347464</v>
       </c>
       <c r="D8" t="n">
         <v>6.51042e-08</v>
@@ -4110,16 +3936,13 @@
         <v>-26478.52027116762</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.706624408938204e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2928.207222118213</v>
+        <v>206.6245117952468</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000125036e-08</v>
+        <v>3.348585361524752e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8132137327329829</v>
+        <v>0.8692696256940108</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3953,7 @@
         <v>1924.12</v>
       </c>
       <c r="C9" t="n">
-        <v>2588.363673151795</v>
+        <v>1440.404844614966</v>
       </c>
       <c r="D9" t="n">
         <v>6.50668e-08</v>
@@ -4163,16 +3986,13 @@
         <v>-9327.408867039567</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.010949242543768e-14</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2884.750338449863</v>
+        <v>71.56259572307452</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.00000000026676e-08</v>
+        <v>7.744247500814606e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8133796058844598</v>
+        <v>0.9648624547374625</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4003,7 @@
         <v>1894.526</v>
       </c>
       <c r="C10" t="n">
-        <v>2558.731785864685</v>
+        <v>1425.220046031538</v>
       </c>
       <c r="D10" t="n">
         <v>6.50538e-08</v>
@@ -4216,16 +4036,13 @@
         <v>3264.069165949725</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.975261471801174e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2844.982276807901</v>
+        <v>58.69671749588909</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000002224216e-08</v>
+        <v>4.949966265424026e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8135550389336141</v>
+        <v>0.99058822141208</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4053,7 @@
         <v>1865.824</v>
       </c>
       <c r="C11" t="n">
-        <v>2529.166337481671</v>
+        <v>1600.575976500058</v>
       </c>
       <c r="D11" t="n">
         <v>6.50517e-08</v>
@@ -4269,16 +4086,13 @@
         <v>13687.38722258985</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.682352462606695e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2807.938141447114</v>
+        <v>4.926748593112048</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000023074e-08</v>
+        <v>2.371467395055344e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8137422252644344</v>
+        <v>0.8774244780408922</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4249,7 @@
         <v>2115.868</v>
       </c>
       <c r="C2" t="n">
-        <v>2815.513147352037</v>
+        <v>1101.92924499987</v>
       </c>
       <c r="D2" t="n">
         <v>6.68646e-08</v>
@@ -4468,16 +4282,13 @@
         <v>-78594.54834015714</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.503713272876611e-14</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3100.80941084509</v>
+        <v>488.6123626930802</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000923e-08</v>
+        <v>1.204013575545291e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8127349193393201</v>
+        <v>0.9643429947565811</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4299,7 @@
         <v>1994.89</v>
       </c>
       <c r="C3" t="n">
-        <v>2663.467851756233</v>
+        <v>936.7111557835136</v>
       </c>
       <c r="D3" t="n">
         <v>6.56379e-08</v>
@@ -4521,16 +4332,13 @@
         <v>-70461.33876678524</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.232455212980571e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2978.445253380965</v>
+        <v>611.380428973177</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000002362421e-08</v>
+        <v>1.172106535573098e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8130220748634609</v>
+        <v>0.9888130273360498</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4349,7 @@
         <v>1947.371</v>
       </c>
       <c r="C4" t="n">
-        <v>2610.721192668414</v>
+        <v>1476.760732969943</v>
       </c>
       <c r="D4" t="n">
         <v>6.53195e-08</v>
@@ -4574,16 +4382,13 @@
         <v>-34260.85119992684</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.334338909097358e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2926.702183851483</v>
+        <v>152.5912328151074</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000626478e-08</v>
+        <v>2.096314585803567e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8131284198321581</v>
+        <v>0.8958306841434913</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4399,7 @@
         <v>1922.022</v>
       </c>
       <c r="C5" t="n">
-        <v>2580.895498089755</v>
+        <v>1441.510742790406</v>
       </c>
       <c r="D5" t="n">
         <v>6.51826e-08</v>
@@ -4627,16 +4432,13 @@
         <v>-9528.855288247358</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.341261710476093e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2889.113656267828</v>
+        <v>55.42938277868943</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000459937e-08</v>
+        <v>4.883436832863725e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8132293587807676</v>
+        <v>0.9897458213052938</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4449,7 @@
         <v>1896.409</v>
       </c>
       <c r="C6" t="n">
-        <v>2557.248856581547</v>
+        <v>1444.764331134187</v>
       </c>
       <c r="D6" t="n">
         <v>6.51337e-08</v>
@@ -4680,16 +4482,13 @@
         <v>8611.958834524094</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.121758090205614e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2856.524373585025</v>
+        <v>196.4496459584322</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000139599e-08</v>
+        <v>2.742552174035271e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8133959097042963</v>
+        <v>0.8828964643655494</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4499,7 @@
         <v>1877.361</v>
       </c>
       <c r="C7" t="n">
-        <v>2541.164413550274</v>
+        <v>1606.064820224521</v>
       </c>
       <c r="D7" t="n">
         <v>6.51319e-08</v>
@@ -4733,16 +4532,13 @@
         <v>25634.43472015978</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.727928214626339e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2825.827724083491</v>
+        <v>1.352155556014293</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000130665e-08</v>
+        <v>2.386480673788805e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.813588395598457</v>
+        <v>0.8768318537824479</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4549,7 @@
         <v>1847.789</v>
       </c>
       <c r="C8" t="n">
-        <v>2514.520347358833</v>
+        <v>1600.186474147271</v>
       </c>
       <c r="D8" t="n">
         <v>6.512e-08</v>
@@ -4786,16 +4582,13 @@
         <v>25320.98282286995</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.024607990855834e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2796.404053660201</v>
+        <v>0.3669716737029417</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000002077736e-08</v>
+        <v>2.164962858511641e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8138108417260976</v>
+        <v>0.8801891677002054</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4599,7 @@
         <v>1826.097</v>
       </c>
       <c r="C9" t="n">
-        <v>2489.604911537104</v>
+        <v>1582.368734009963</v>
       </c>
       <c r="D9" t="n">
         <v>6.512470000000001e-08</v>
@@ -4839,16 +4632,13 @@
         <v>-17405.60786540977</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.457729395873112e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2767.214036768366</v>
+        <v>0.2369759193458393</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000059899e-08</v>
+        <v>2.152675013622073e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8140396719454193</v>
+        <v>0.8843020605597346</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4649,7 @@
         <v>1793.836</v>
       </c>
       <c r="C10" t="n">
-        <v>2456.954739134393</v>
+        <v>1573.801513044664</v>
       </c>
       <c r="D10" t="n">
         <v>6.51447e-08</v>
@@ -4892,16 +4682,13 @@
         <v>-16172.14336217859</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.79788051483419e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2738.675985261965</v>
+        <v>1.795542404253598</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000003111544e-08</v>
+        <v>2.065634449768168e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8142978253090731</v>
+        <v>0.8857928396334545</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4699,7 @@
         <v>1772.736</v>
       </c>
       <c r="C11" t="n">
-        <v>2433.992230275316</v>
+        <v>16878.85616346177</v>
       </c>
       <c r="D11" t="n">
         <v>6.5148e-08</v>
@@ -4945,10 +4732,7 @@
         <v>-16097.17823252997</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.925899905588307e-14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2710.199659339391</v>
+        <v>-14386.37423403168</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000013651e-08</v>
@@ -4965,7 +4749,7 @@
         <v>1772.46</v>
       </c>
       <c r="C12" t="n">
-        <v>2435.822615962971</v>
+        <v>16995.17316715741</v>
       </c>
       <c r="D12" t="n">
         <v>6.514770000000001e-08</v>
@@ -4998,10 +4782,7 @@
         <v>-18538.40743180953</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.698792079256109e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2682.979306390135</v>
+        <v>-14526.96883670357</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000019037e-08</v>
@@ -5018,7 +4799,7 @@
         <v>1732.818</v>
       </c>
       <c r="C13" t="n">
-        <v>2393.782916319463</v>
+        <v>15859.26360732646</v>
       </c>
       <c r="D13" t="n">
         <v>6.51546e-08</v>
@@ -5051,10 +4832,7 @@
         <v>-15863.74319316536</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.294911995502573e-07</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2655.560599979192</v>
+        <v>-13408.18538899332</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000029963e-08</v>
@@ -5071,7 +4849,7 @@
         <v>1725.676</v>
       </c>
       <c r="C14" t="n">
-        <v>2385.75425149155</v>
+        <v>15275.99646808144</v>
       </c>
       <c r="D14" t="n">
         <v>6.515700000000001e-08</v>
@@ -5104,10 +4882,7 @@
         <v>-17467.62813982737</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.02898540932662e-14</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2628.621820032761</v>
+        <v>-12844.21939379487</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000496e-08</v>
@@ -5124,7 +4899,7 @@
         <v>1699.515</v>
       </c>
       <c r="C15" t="n">
-        <v>2360.319402818955</v>
+        <v>2092.020932872202</v>
       </c>
       <c r="D15" t="n">
         <v>6.51468e-08</v>
@@ -5157,16 +4932,13 @@
         <v>-16404.74254993359</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.129029427930446e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2602.193960973588</v>
+        <v>3.572767101546439</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.00000000008681e-08</v>
+        <v>3.371088601136403e-07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8157111145780713</v>
+        <v>0.5364265246559035</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4949,7 @@
         <v>1685.338</v>
       </c>
       <c r="C16" t="n">
-        <v>2346.499620473312</v>
+        <v>14697.2626642176</v>
       </c>
       <c r="D16" t="n">
         <v>6.51408e-08</v>
@@ -5210,10 +4982,7 @@
         <v>-17247.90450462234</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.467782092261909e-07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2575.984614183384</v>
+        <v>-12306.6826096448</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000003920471e-08</v>
@@ -5230,7 +4999,7 @@
         <v>1653.387</v>
       </c>
       <c r="C17" t="n">
-        <v>2314.130302448684</v>
+        <v>14591.03580869045</v>
       </c>
       <c r="D17" t="n">
         <v>6.516190000000001e-08</v>
@@ -5263,10 +5032,7 @@
         <v>-15655.70638275604</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.655215230294291e-07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2549.524310452643</v>
+        <v>-12222.75305446677</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000001989374e-08</v>
@@ -5283,7 +5049,7 @@
         <v>1631.66</v>
       </c>
       <c r="C18" t="n">
-        <v>2293.186935178948</v>
+        <v>14203.24232972208</v>
       </c>
       <c r="D18" t="n">
         <v>6.514720000000001e-08</v>
@@ -5316,10 +5082,7 @@
         <v>-15475.9528379699</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.294975845472857e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2522.962256241677</v>
+        <v>-11854.69682355493</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000003885e-08</v>
@@ -5336,7 +5099,7 @@
         <v>1598.629</v>
       </c>
       <c r="C19" t="n">
-        <v>2256.150335860247</v>
+        <v>13706.26072187081</v>
       </c>
       <c r="D19" t="n">
         <v>6.516729999999999e-08</v>
@@ -5369,10 +5132,7 @@
         <v>-13788.50815160075</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.333281535670074e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2496.178754784095</v>
+        <v>-11376.56967328241</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000080488e-08</v>
@@ -5389,7 +5149,7 @@
         <v>1601.069</v>
       </c>
       <c r="C20" t="n">
-        <v>2258.580869010679</v>
+        <v>13626.54458191063</v>
       </c>
       <c r="D20" t="n">
         <v>6.51763e-08</v>
@@ -5422,10 +5182,7 @@
         <v>-16107.91924259595</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.963439150436547e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2469.600454719319</v>
+        <v>-11318.64767449236</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000008409e-08</v>
@@ -5442,7 +5199,7 @@
         <v>1573.746</v>
       </c>
       <c r="C21" t="n">
-        <v>2235.021492492712</v>
+        <v>13647.45496919078</v>
       </c>
       <c r="D21" t="n">
         <v>6.517709999999999e-08</v>
@@ -5475,10 +5232,7 @@
         <v>-15340.87843996631</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.457985090775765e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2442.754711392271</v>
+        <v>-11362.78381311068</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000080993e-08</v>
@@ -5495,7 +5249,7 @@
         <v>1549.245</v>
       </c>
       <c r="C22" t="n">
-        <v>2208.988965637895</v>
+        <v>13551.31373688888</v>
       </c>
       <c r="D22" t="n">
         <v>6.51972e-08</v>
@@ -5528,10 +5282,7 @@
         <v>-14424.35012449286</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.38743871202838e-12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2415.841176766926</v>
+        <v>-11289.82537849018</v>
       </c>
       <c r="AA22" t="n">
         <v>1.0000000000519e-08</v>
@@ -5694,7 +5445,7 @@
         <v>2657.887</v>
       </c>
       <c r="C2" t="n">
-        <v>3522.297670316287</v>
+        <v>1324.990721902253</v>
       </c>
       <c r="D2" t="n">
         <v>6.869109999999999e-08</v>
@@ -5727,16 +5478,13 @@
         <v>-37181.95774067543</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.489649772884224e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3707.894080356654</v>
+        <v>518.8974172148202</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000006821e-08</v>
+        <v>2.98842396127692e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8109729998283166</v>
+        <v>0.8927214815847572</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5495,7 @@
         <v>2193.718</v>
       </c>
       <c r="C3" t="n">
-        <v>2879.954427507051</v>
+        <v>1191.803466182526</v>
       </c>
       <c r="D3" t="n">
         <v>6.773579999999999e-08</v>
@@ -5780,16 +5528,13 @@
         <v>-66059.70141254611</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.517787105115126e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3218.210291151423</v>
+        <v>385.0959983916417</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000001999e-08</v>
+        <v>6.459453654965825e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8122060551240007</v>
+        <v>0.9928816730124472</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5545,7 @@
         <v>2092.929</v>
       </c>
       <c r="C4" t="n">
-        <v>2755.64681098763</v>
+        <v>1035.158030981445</v>
       </c>
       <c r="D4" t="n">
         <v>6.68213e-08</v>
@@ -5833,16 +5578,13 @@
         <v>-83852.57578949022</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.276089341358065e-13</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3095.380351498084</v>
+        <v>554.341487124387</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000005625e-08</v>
+        <v>1.161573565791477e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8124861103466645</v>
+        <v>0.9743975239164142</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5595,7 @@
         <v>2036.818</v>
       </c>
       <c r="C5" t="n">
-        <v>2696.511508296964</v>
+        <v>966.7867171348859</v>
       </c>
       <c r="D5" t="n">
         <v>6.6444e-08</v>
@@ -5886,16 +5628,13 @@
         <v>-74013.20132172584</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.01561900948159e-13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3033.146864149631</v>
+        <v>596.91526630684</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000004289e-08</v>
+        <v>1.082144108083992e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8126131828785502</v>
+        <v>0.9881007824465123</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5645,7 @@
         <v>1992.979</v>
       </c>
       <c r="C6" t="n">
-        <v>2652.845730590333</v>
+        <v>938.1967130027448</v>
       </c>
       <c r="D6" t="n">
         <v>6.62592e-08</v>
@@ -5939,16 +5678,13 @@
         <v>-55004.40421502014</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.5955133763302e-13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2983.824621989874</v>
+        <v>607.4692865960764</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000004206e-08</v>
+        <v>1.024776117664404e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8127358872415184</v>
+        <v>0.9940105672526913</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5695,7 @@
         <v>1973.083</v>
       </c>
       <c r="C7" t="n">
-        <v>2633.665290694923</v>
+        <v>1658.184064201064</v>
       </c>
       <c r="D7" t="n">
         <v>6.61719e-08</v>
@@ -5992,16 +5728,13 @@
         <v>-40656.91250923482</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.415628643110699e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2938.874907182456</v>
+        <v>13.77530894079012</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000029043e-08</v>
+        <v>2.941544905136809e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8128738039469225</v>
+        <v>0.8633225275358437</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5745,7 @@
         <v>1933.396</v>
       </c>
       <c r="C8" t="n">
-        <v>2595.160792369262</v>
+        <v>1518.328841863984</v>
       </c>
       <c r="D8" t="n">
         <v>6.61369e-08</v>
@@ -6045,16 +5778,13 @@
         <v>-23038.00394133735</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.368461865905526e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2897.045874698175</v>
+        <v>135.3929680624141</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000001490659e-08</v>
+        <v>2.709941949664662e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8130346229438706</v>
+        <v>0.8751758713755903</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5795,7 @@
         <v>1894.82</v>
       </c>
       <c r="C9" t="n">
-        <v>2556.211274581343</v>
+        <v>1442.663990802382</v>
       </c>
       <c r="D9" t="n">
         <v>6.6136e-08</v>
@@ -6098,16 +5828,13 @@
         <v>-10650.116553725</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.976068441226693e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2857.294100960475</v>
+        <v>205.4965286439594</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000002348099e-08</v>
+        <v>2.979088809615402e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8132137836730984</v>
+        <v>0.876809493751184</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5845,7 @@
         <v>1874.924</v>
       </c>
       <c r="C10" t="n">
-        <v>2538.253877598401</v>
+        <v>1434.022635981974</v>
       </c>
       <c r="D10" t="n">
         <v>6.61349e-08</v>
@@ -6151,16 +5878,13 @@
         <v>3080.166053908959</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.647331413136195e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2820.477322753758</v>
+        <v>190.214995267318</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000497801e-08</v>
+        <v>2.615511879498473e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8134093161771635</v>
+        <v>0.8860007173082401</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5895,7 @@
         <v>1840.192</v>
       </c>
       <c r="C11" t="n">
-        <v>2502.711960838546</v>
+        <v>1597.606816982584</v>
       </c>
       <c r="D11" t="n">
         <v>6.61646e-08</v>
@@ -6204,16 +5928,13 @@
         <v>11047.61525274087</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.453884835213759e-13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2785.960762766516</v>
+        <v>3.955991101082074</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000097333e-08</v>
+        <v>2.318472207015763e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8136157439402472</v>
+        <v>0.8809813094555364</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6091,7 @@
         <v>2112.708</v>
       </c>
       <c r="C2" t="n">
-        <v>2831.053949149834</v>
+        <v>1244.829310367887</v>
       </c>
       <c r="D2" t="n">
         <v>6.923909999999999e-08</v>
@@ -6403,16 +6124,13 @@
         <v>-54464.96287665951</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.826779095373975e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3112.206535620435</v>
+        <v>289.472549153031</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000068123e-08</v>
+        <v>7.744272901233875e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8126956674502752</v>
+        <v>0.9860714166735516</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6141,7 @@
         <v>1977.818</v>
       </c>
       <c r="C3" t="n">
-        <v>2644.739001090484</v>
+        <v>960.5792006229372</v>
       </c>
       <c r="D3" t="n">
         <v>6.73327e-08</v>
@@ -6456,16 +6174,13 @@
         <v>-80669.62904581991</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.514337441707183e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2953.37503172122</v>
+        <v>567.3376301562294</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.0000000037225e-08</v>
+        <v>9.109224708568955e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8130326148565623</v>
+        <v>0.9948627007162076</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6191,7 @@
         <v>1933.114</v>
       </c>
       <c r="C4" t="n">
-        <v>2594.513529813527</v>
+        <v>1455.274186802169</v>
       </c>
       <c r="D4" t="n">
         <v>6.688940000000001e-08</v>
@@ -6509,16 +6224,13 @@
         <v>-61257.09970802224</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.668005610458705e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2898.741819339024</v>
+        <v>40.79972616567354</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000018462e-08</v>
+        <v>4.764231503265817e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8131080792903281</v>
+        <v>0.9905095576910056</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6241,7 @@
         <v>1911.507</v>
       </c>
       <c r="C5" t="n">
-        <v>2572.304740291317</v>
+        <v>1438.778071147071</v>
       </c>
       <c r="D5" t="n">
         <v>6.67038e-08</v>
@@ -6562,16 +6274,13 @@
         <v>-37930.7087741549</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.935896412075662e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2862.201244899916</v>
+        <v>42.56618091299594</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000016909e-08</v>
+        <v>4.897302508635402e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8131771093337712</v>
+        <v>0.9962803871835901</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6291,7 @@
         <v>1870.091</v>
       </c>
       <c r="C6" t="n">
-        <v>2533.814546424893</v>
+        <v>1413.577098539263</v>
       </c>
       <c r="D6" t="n">
         <v>6.66288e-08</v>
@@ -6615,16 +6324,13 @@
         <v>-19817.84052044459</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.94204070804713e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2829.966957799847</v>
+        <v>59.35228585706362</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000001365048e-08</v>
+        <v>4.993850138631509e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.813283468521506</v>
+        <v>0.9966244774533067</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6341,7 @@
         <v>1848.106</v>
       </c>
       <c r="C7" t="n">
-        <v>2514.572413307002</v>
+        <v>1564.775759210079</v>
       </c>
       <c r="D7" t="n">
         <v>6.66054e-08</v>
@@ -6668,16 +6374,13 @@
         <v>-5842.658061940697</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.830260427125439e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2800.232420436188</v>
+        <v>47.08534582918101</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000016682e-08</v>
+        <v>2.387396347991174e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.813419236779981</v>
+        <v>0.878450697232331</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6391,7 @@
         <v>1826.383</v>
       </c>
       <c r="C8" t="n">
-        <v>2491.441528080324</v>
+        <v>1583.931789147935</v>
       </c>
       <c r="D8" t="n">
         <v>6.65822e-08</v>
@@ -6721,16 +6424,13 @@
         <v>4033.184208893517</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.189804074923447e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2772.05319856209</v>
+        <v>0.06324685729173321</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000106446e-08</v>
+        <v>2.064283405341022e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8135655042494276</v>
+        <v>0.884367516603605</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6441,7 @@
         <v>1806.192</v>
       </c>
       <c r="C9" t="n">
-        <v>2470.419335263338</v>
+        <v>1581.465916382355</v>
       </c>
       <c r="D9" t="n">
         <v>6.65943e-08</v>
@@ -6774,16 +6474,13 @@
         <v>12418.75004068838</v>
       </c>
       <c r="Y9" t="n">
-        <v>361.9679600828741</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6900.748144565289</v>
+        <v>1.324599921172499</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.211874841429044e-06</v>
+        <v>2.099516203520727e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5000563328564563</v>
+        <v>0.8831092324874151</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6491,7 @@
         <v>1789.047</v>
       </c>
       <c r="C10" t="n">
-        <v>2453.450072040972</v>
+        <v>1577.334509324906</v>
       </c>
       <c r="D10" t="n">
         <v>6.66098e-08</v>
@@ -6827,16 +6524,13 @@
         <v>20229.59207957098</v>
       </c>
       <c r="Y10" t="n">
-        <v>359.2523461034974</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6834.244800307194</v>
+        <v>1.902084712536368</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.217394013992102e-06</v>
+        <v>2.381391674014868e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.5001064745672358</v>
+        <v>0.8757383897973159</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6541,7 @@
         <v>1777.308</v>
       </c>
       <c r="C11" t="n">
-        <v>2442.816256341011</v>
+        <v>2092.12358803342</v>
       </c>
       <c r="D11" t="n">
         <v>6.66092e-08</v>
@@ -6880,16 +6574,13 @@
         <v>30999.36380989699</v>
       </c>
       <c r="Y11" t="n">
-        <v>357.2408689988711</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6775.33087665479</v>
+        <v>5.45344580370575</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.223676434887456e-06</v>
+        <v>2.446362724705318e-07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.50017299514923</v>
+        <v>0.554967115063107</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6591,7 @@
         <v>1747.524</v>
       </c>
       <c r="C12" t="n">
-        <v>2410.630155746916</v>
+        <v>2096.71521842547</v>
       </c>
       <c r="D12" t="n">
         <v>6.66359e-08</v>
@@ -6933,16 +6624,13 @@
         <v>26805.84484575409</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.022873543275556e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2673.595039786875</v>
+        <v>5.80133528097073</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000125491e-08</v>
+        <v>2.694755493020713e-07</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.814220548455625</v>
+        <v>0.5489859483259311</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6641,7 @@
         <v>1729.993</v>
       </c>
       <c r="C13" t="n">
-        <v>2393.255189098942</v>
+        <v>2102.640189110336</v>
       </c>
       <c r="D13" t="n">
         <v>6.66293e-08</v>
@@ -6986,16 +6674,13 @@
         <v>-16552.66532110814</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.55369299566428e-14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2651.228810142732</v>
+        <v>5.237545762641504</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000079327e-08</v>
+        <v>2.978660672382116e-07</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.814409419532958</v>
+        <v>0.5428670244814701</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6691,7 @@
         <v>1706.314</v>
       </c>
       <c r="C14" t="n">
-        <v>2369.860434719639</v>
+        <v>2102.816413925981</v>
       </c>
       <c r="D14" t="n">
         <v>6.66455e-08</v>
@@ -7039,16 +6724,13 @@
         <v>-15918.01141821042</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.841104674228749e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2629.495411274605</v>
+        <v>4.558346277724517</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000677394e-08</v>
+        <v>3.19659158012155e-07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8145926991059536</v>
+        <v>0.5385875993391063</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6741,7 @@
         <v>1703.838</v>
       </c>
       <c r="C15" t="n">
-        <v>2367.815451115851</v>
+        <v>2099.841779555479</v>
       </c>
       <c r="D15" t="n">
         <v>6.66379e-08</v>
@@ -7092,16 +6774,13 @@
         <v>-17260.47574685215</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.299561483160774e-12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2608.163674743105</v>
+        <v>3.944956853443386</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000339211e-08</v>
+        <v>3.359284456306818e-07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8147965180180896</v>
+        <v>0.5356577791669616</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6791,7 @@
         <v>1674.799</v>
       </c>
       <c r="C16" t="n">
-        <v>2339.745079576756</v>
+        <v>2099.109159520962</v>
       </c>
       <c r="D16" t="n">
         <v>6.665789999999999e-08</v>
@@ -7145,16 +6824,13 @@
         <v>-16043.51675191806</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.511844908860799e-14</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2586.717452900827</v>
+        <v>2.980175978958956</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000001428e-08</v>
+        <v>3.598145226893829e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8149999008664018</v>
+        <v>0.5314679867138414</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6841,7 @@
         <v>1660.743</v>
       </c>
       <c r="C17" t="n">
-        <v>2322.514503458473</v>
+        <v>16669.94671879774</v>
       </c>
       <c r="D17" t="n">
         <v>6.66758e-08</v>
@@ -7198,10 +6874,7 @@
         <v>-15988.56842160121</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.959987999328106e-15</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2565.091971097781</v>
+        <v>-14299.36932468944</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000049384e-08</v>
@@ -7218,7 +6891,7 @@
         <v>1636.787</v>
       </c>
       <c r="C18" t="n">
-        <v>2300.18362337423</v>
+        <v>16277.35463861063</v>
       </c>
       <c r="D18" t="n">
         <v>6.66753e-08</v>
@@ -7251,10 +6924,7 @@
         <v>-15020.97071327513</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.980759872087457e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2543.337884805379</v>
+        <v>-13922.79240016094</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000470609e-08</v>
@@ -7271,7 +6941,7 @@
         <v>1627.471</v>
       </c>
       <c r="C19" t="n">
-        <v>2292.151915926079</v>
+        <v>15686.78434643888</v>
       </c>
       <c r="D19" t="n">
         <v>6.66815e-08</v>
@@ -7304,10 +6974,7 @@
         <v>-15768.30395494532</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.488568489960556e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2521.96677157164</v>
+        <v>-13346.93973955665</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000001431337e-08</v>
@@ -7324,7 +6991,7 @@
         <v>1610.084</v>
       </c>
       <c r="C20" t="n">
-        <v>2273.130597475883</v>
+        <v>15220.62027025426</v>
       </c>
       <c r="D20" t="n">
         <v>6.669580000000001e-08</v>
@@ -7357,10 +7024,7 @@
         <v>-15725.08428232545</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.700793949221654e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2499.991973103609</v>
+        <v>-12897.19728367328</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000115598e-08</v>
@@ -7377,7 +7041,7 @@
         <v>1599.406</v>
       </c>
       <c r="C21" t="n">
-        <v>2264.104358102199</v>
+        <v>15330.3079638319</v>
       </c>
       <c r="D21" t="n">
         <v>6.66883e-08</v>
@@ -7410,10 +7074,7 @@
         <v>-16279.86037098733</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.322849944898881e-07</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2478.3568299565</v>
+        <v>-13025.67101549964</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000122447e-08</v>
@@ -7430,7 +7091,7 @@
         <v>1579.482</v>
       </c>
       <c r="C22" t="n">
-        <v>2240.883488112794</v>
+        <v>15140.7649600813</v>
       </c>
       <c r="D22" t="n">
         <v>6.670460000000001e-08</v>
@@ -7463,10 +7124,7 @@
         <v>-15583.04995540379</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.226996704798019e-06</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2456.830313811909</v>
+        <v>-12853.2737454831</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000651405e-08</v>
@@ -7629,7 +7287,7 @@
         <v>2567.581</v>
       </c>
       <c r="C2" t="n">
-        <v>3439.737213157986</v>
+        <v>1333.736961727727</v>
       </c>
       <c r="D2" t="n">
         <v>6.91829e-08</v>
@@ -7662,16 +7320,13 @@
         <v>-38450.90750279372</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.07231523396653e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3614.404843408442</v>
+        <v>434.4981029876619</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.00000000011803e-08</v>
+        <v>3.080214018652025e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8117315975817562</v>
+        <v>0.8856698662552838</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7337,7 @@
         <v>2137.53</v>
       </c>
       <c r="C3" t="n">
-        <v>2815.891814583839</v>
+        <v>1129.411519666248</v>
       </c>
       <c r="D3" t="n">
         <v>6.82448e-08</v>
@@ -7715,16 +7370,13 @@
         <v>-70861.41668822135</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.497936375118675e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3136.862093895567</v>
+        <v>471.6170221735709</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.00000000032086e-08</v>
+        <v>1.516026604139034e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.81292692789788</v>
+        <v>0.9471016032463125</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7387,7 @@
         <v>2026.95</v>
       </c>
       <c r="C4" t="n">
-        <v>2682.747453652637</v>
+        <v>996.8834808989483</v>
       </c>
       <c r="D4" t="n">
         <v>6.7658e-08</v>
@@ -7768,16 +7420,13 @@
         <v>-76005.01470573906</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.42339174985863e-15</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3023.552290229102</v>
+        <v>542.6753495644757</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>1.364491068912251e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8131766875636037</v>
+        <v>0.9782557436306818</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7437,7 @@
         <v>1991.235</v>
       </c>
       <c r="C5" t="n">
-        <v>2643.499696491502</v>
+        <v>942.4964817292699</v>
       </c>
       <c r="D5" t="n">
         <v>6.74376e-08</v>
@@ -7821,16 +7470,13 @@
         <v>-71552.84095192752</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.143507990293474e-14</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2967.407414415672</v>
+        <v>613.6891253891271</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000004e-08</v>
+        <v>9.630366775644559e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8132854401415903</v>
+        <v>0.9896117123986951</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7487,7 @@
         <v>1963.62</v>
       </c>
       <c r="C6" t="n">
-        <v>2620.238635989926</v>
+        <v>918.2639536760885</v>
       </c>
       <c r="D6" t="n">
         <v>6.73161e-08</v>
@@ -7874,16 +7520,13 @@
         <v>-61388.75708529154</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.029002508925277e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2924.041814009404</v>
+        <v>577.1309320029544</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000067729e-08</v>
+        <v>1.076022318965921e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8133819292230474</v>
+        <v>0.990418771064605</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7537,7 @@
         <v>1925.438</v>
       </c>
       <c r="C7" t="n">
-        <v>2579.667852362258</v>
+        <v>1454.861965950211</v>
       </c>
       <c r="D7" t="n">
         <v>6.72919e-08</v>
@@ -7927,16 +7570,13 @@
         <v>-42135.53109468762</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.147892250672547e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2884.832626894152</v>
+        <v>124.7280082934389</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000131622e-08</v>
+        <v>1.619852568431515e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8134824101818988</v>
+        <v>0.9135898821687497</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7587,7 @@
         <v>1883.437</v>
       </c>
       <c r="C8" t="n">
-        <v>2539.761112147605</v>
+        <v>1500.674153661702</v>
       </c>
       <c r="D8" t="n">
         <v>6.72747e-08</v>
@@ -7980,16 +7620,13 @@
         <v>-29135.04419632994</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.542677087333395e-12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2846.94606088787</v>
+        <v>135.9804522372594</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000059907e-08</v>
+        <v>3.016109994449842e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.813631498832315</v>
+        <v>0.8732075268582689</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7637,7 @@
         <v>1853.945</v>
       </c>
       <c r="C9" t="n">
-        <v>2513.259520944326</v>
+        <v>1471.832377808759</v>
       </c>
       <c r="D9" t="n">
         <v>6.73049e-08</v>
@@ -8033,16 +7670,13 @@
         <v>-18746.46588649466</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.620224228637031e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2810.683657324257</v>
+        <v>0.06867606560865916</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000002254781e-08</v>
+        <v>5.122665508845769e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8137990104894609</v>
+        <v>0.9874698757467385</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7687,7 @@
         <v>1835.76</v>
       </c>
       <c r="C10" t="n">
-        <v>2493.107445635282</v>
+        <v>1390.554790495664</v>
       </c>
       <c r="D10" t="n">
         <v>6.735029999999999e-08</v>
@@ -8086,16 +7720,13 @@
         <v>-7718.772412372305</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.085343435594107e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2776.174489074143</v>
+        <v>62.37619030976084</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000144727e-08</v>
+        <v>5.009146725884421e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8139823526587866</v>
+        <v>0.997003736669932</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7737,7 @@
         <v>1804.907</v>
       </c>
       <c r="C11" t="n">
-        <v>2460.811598120684</v>
+        <v>1563.066996595393</v>
       </c>
       <c r="D11" t="n">
         <v>6.73891e-08</v>
@@ -8139,16 +7770,13 @@
         <v>-1625.861673355688</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22764211002573e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2742.974615010593</v>
+        <v>10.37984213408352</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000042788e-08</v>
+        <v>2.024853865935816e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8141579711116839</v>
+        <v>0.8903930282549488</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7933,7 @@
         <v>2113.974</v>
       </c>
       <c r="C2" t="n">
-        <v>2815.871994705783</v>
+        <v>1106.051605933254</v>
       </c>
       <c r="D2" t="n">
         <v>6.92013e-08</v>
@@ -8338,16 +7966,13 @@
         <v>-68198.24688085998</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.829881893687128e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3091.679560445009</v>
+        <v>722.8349744507127</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.00000000000209e-08</v>
+        <v>1.398281832782502e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8142497834061933</v>
+        <v>0.8262125182397186</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +7983,7 @@
         <v>1970.511</v>
       </c>
       <c r="C3" t="n">
-        <v>2619.602129415383</v>
+        <v>935.5714202814125</v>
       </c>
       <c r="D3" t="n">
         <v>6.80859e-08</v>
@@ -8391,16 +8016,13 @@
         <v>-74739.21361180568</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.233381463419685e-15</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2924.594950167621</v>
+        <v>580.0971147781763</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.00000000000826e-08</v>
+        <v>1.391638034448331e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8148335769186714</v>
+        <v>0.9685791381570024</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8033,7 @@
         <v>1914.942</v>
       </c>
       <c r="C4" t="n">
-        <v>2557.777422792895</v>
+        <v>899.4756148163884</v>
       </c>
       <c r="D4" t="n">
         <v>6.778620000000001e-08</v>
@@ -8444,16 +8066,13 @@
         <v>-52595.86030621087</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.081375275611036e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2867.690734657103</v>
+        <v>617.974945445894</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000172454e-08</v>
+        <v>1.016555446845432e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8149709646965708</v>
+        <v>0.9971264103847122</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8083,7 @@
         <v>1902.173</v>
       </c>
       <c r="C5" t="n">
-        <v>2544.321716035151</v>
+        <v>1434.652175759658</v>
       </c>
       <c r="D5" t="n">
         <v>6.76946e-08</v>
@@ -8497,16 +8116,13 @@
         <v>-35860.55058012691</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.271012226955511e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2831.573809693018</v>
+        <v>23.81511249892918</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000161538e-08</v>
+        <v>4.657625833261913e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8150196790466799</v>
+        <v>0.9907667276005443</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8133,7 @@
         <v>1868.581</v>
       </c>
       <c r="C6" t="n">
-        <v>2512.505592456963</v>
+        <v>1481.384483413822</v>
       </c>
       <c r="D6" t="n">
         <v>6.76566e-08</v>
@@ -8550,16 +8166,13 @@
         <v>-18705.0035130191</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.250746024137434e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2800.137047970031</v>
+        <v>4.353914267629923</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000051283e-08</v>
+        <v>8.068323208048428e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8150958478252835</v>
+        <v>0.9578190795286169</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8183,7 @@
         <v>1838.446</v>
       </c>
       <c r="C7" t="n">
-        <v>2483.769710022842</v>
+        <v>1400.261424838306</v>
       </c>
       <c r="D7" t="n">
         <v>6.76498e-08</v>
@@ -8603,16 +8216,13 @@
         <v>-10140.51409358245</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.161438124980658e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2770.184456181625</v>
+        <v>202.8848311858748</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000070569e-08</v>
+        <v>3.024136617815062e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8151890374926833</v>
+        <v>0.878119761961509</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8233,7 @@
         <v>1817.64</v>
       </c>
       <c r="C8" t="n">
-        <v>2461.68416914409</v>
+        <v>1374.806428097808</v>
       </c>
       <c r="D8" t="n">
         <v>6.7673e-08</v>
@@ -8656,16 +8266,13 @@
         <v>-720.8756938429007</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.994395494709667e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2742.295703597552</v>
+        <v>74.30239047918528</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000136758e-08</v>
+        <v>7.677012253297711e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8153074815972636</v>
+        <v>0.9681163737523306</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8283,7 @@
         <v>1803.327</v>
       </c>
       <c r="C9" t="n">
-        <v>2448.912450163897</v>
+        <v>1539.333418767253</v>
       </c>
       <c r="D9" t="n">
         <v>6.76783e-08</v>
@@ -8709,16 +8316,13 @@
         <v>8953.91573369358</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.162018812113588e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2715.893592132777</v>
+        <v>9.290148129531422</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000123253e-08</v>
+        <v>2.015016231080671e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8154335627502167</v>
+        <v>0.8871853653272325</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8333,7 @@
         <v>1772.581</v>
       </c>
       <c r="C10" t="n">
-        <v>2417.497347878381</v>
+        <v>1545.817374531889</v>
       </c>
       <c r="D10" t="n">
         <v>6.77146e-08</v>
@@ -8762,16 +8366,13 @@
         <v>7306.178078909699</v>
       </c>
       <c r="Y10" t="n">
-        <v>351.7880185803672</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6799.144643573309</v>
+        <v>0.03082293714841948</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.23751993603162e-06</v>
+        <v>2.255829643500255e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.5000346600109846</v>
+        <v>0.8844751836974587</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8383,7 @@
         <v>1767.578</v>
       </c>
       <c r="C11" t="n">
-        <v>2412.623564087847</v>
+        <v>1536.973739650973</v>
       </c>
       <c r="D11" t="n">
         <v>6.77324e-08</v>
@@ -8815,16 +8416,13 @@
         <v>23491.01751536819</v>
       </c>
       <c r="Y11" t="n">
-        <v>346.1510907044591</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6714.992890909984</v>
+        <v>0.9973109641484175</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.238171565523057e-06</v>
+        <v>2.055408036298191e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.5000167426251596</v>
+        <v>0.8874900186009949</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8433,7 @@
         <v>1732.769</v>
       </c>
       <c r="C12" t="n">
-        <v>2378.42937405697</v>
+        <v>1534.909489561341</v>
       </c>
       <c r="D12" t="n">
         <v>6.77558e-08</v>
@@ -8868,16 +8466,13 @@
         <v>12203.16032319662</v>
       </c>
       <c r="Y12" t="n">
-        <v>344.4505887722594</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6670.094166821037</v>
+        <v>1.125668424338472</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.244512812326237e-06</v>
+        <v>2.339766060814693e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.5000455978319578</v>
+        <v>0.8789076104782236</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8483,7 @@
         <v>1724.228</v>
       </c>
       <c r="C13" t="n">
-        <v>2368.409692563174</v>
+        <v>1530.313097873509</v>
       </c>
       <c r="D13" t="n">
         <v>6.77394e-08</v>
@@ -8921,16 +8516,13 @@
         <v>21744.6586949834</v>
       </c>
       <c r="Y13" t="n">
-        <v>341.094315649004</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6610.936832671729</v>
+        <v>1.767410501929465</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.248090006956523e-06</v>
+        <v>2.200288873084977e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5000900777831849</v>
+        <v>0.8821082271541798</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8533,7 @@
         <v>1709.091</v>
       </c>
       <c r="C14" t="n">
-        <v>2354.280927838032</v>
+        <v>1508.627318828398</v>
       </c>
       <c r="D14" t="n">
         <v>6.77677e-08</v>
@@ -8974,16 +8566,13 @@
         <v>25276.47871324407</v>
       </c>
       <c r="Y14" t="n">
-        <v>337.9733616294421</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6553.353565219952</v>
+        <v>0.8177797828912843</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.252345813924323e-06</v>
+        <v>1.901253127879379e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5001469922418816</v>
+        <v>0.8967022028423102</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8583,7 @@
         <v>1695.075</v>
       </c>
       <c r="C15" t="n">
-        <v>2339.313108393941</v>
+        <v>2017.583165554883</v>
       </c>
       <c r="D15" t="n">
         <v>6.77724e-08</v>
@@ -9027,16 +8616,13 @@
         <v>27172.02773873126</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.445652138653639e-12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2588.31182980137</v>
+        <v>5.143866882298155</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000401e-08</v>
+        <v>2.481018836361167e-07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8164955951202296</v>
+        <v>0.5564384037384518</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8633,7 @@
         <v>1687.281</v>
       </c>
       <c r="C16" t="n">
-        <v>2331.678353283453</v>
+        <v>2011.668012139097</v>
       </c>
       <c r="D16" t="n">
         <v>6.779280000000001e-08</v>
@@ -9080,16 +8666,13 @@
         <v>-17039.26185377737</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.330838232036492e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2567.327131939855</v>
+        <v>5.342817684761952</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000370885e-08</v>
+        <v>2.576209343123898e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8167523881424483</v>
+        <v>0.5542775432878041</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8683,7 @@
         <v>1650.533</v>
       </c>
       <c r="C17" t="n">
-        <v>2294.025256394212</v>
+        <v>2010.436468322443</v>
       </c>
       <c r="D17" t="n">
         <v>6.77997e-08</v>
@@ -9133,16 +8716,13 @@
         <v>25895.83522968648</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.587055930497271e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2545.968779739195</v>
+        <v>5.323147158449709</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000003167629e-08</v>
+        <v>2.748947411305256e-07</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8170067791979968</v>
+        <v>0.5504260366788549</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8733,7 @@
         <v>1647.34</v>
       </c>
       <c r="C18" t="n">
-        <v>2292.713696429185</v>
+        <v>2003.827658958392</v>
       </c>
       <c r="D18" t="n">
         <v>6.78108e-08</v>
@@ -9186,16 +8766,13 @@
         <v>-16280.10041114738</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.133077636823484e-14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2523.784958011967</v>
+        <v>5.19338726841634</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000562e-08</v>
+        <v>2.847882562179901e-07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.817265665735262</v>
+        <v>0.548472995302237</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8783,7 @@
         <v>1630.251</v>
       </c>
       <c r="C19" t="n">
-        <v>2273.131949050485</v>
+        <v>16657.16821011688</v>
       </c>
       <c r="D19" t="n">
         <v>6.782240000000001e-08</v>
@@ -9239,10 +8816,7 @@
         <v>-15977.31195387075</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.380659697293558e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2501.133789106292</v>
+        <v>-14344.20794248038</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000001017485e-08</v>
@@ -9259,7 +8833,7 @@
         <v>1608.278</v>
       </c>
       <c r="C20" t="n">
-        <v>2251.047291126069</v>
+        <v>1996.430321037684</v>
       </c>
       <c r="D20" t="n">
         <v>6.7829e-08</v>
@@ -9292,16 +8866,13 @@
         <v>-15401.09675989566</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.040343705032971e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2479.168081807108</v>
+        <v>4.542476343863203</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000091103e-08</v>
+        <v>3.185044643929534e-07</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8178109244701777</v>
+        <v>0.5419888038870317</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8883,7 @@
         <v>1597.924</v>
       </c>
       <c r="C21" t="n">
-        <v>2240.593252081722</v>
+        <v>1992.74168812614</v>
       </c>
       <c r="D21" t="n">
         <v>6.78533e-08</v>
@@ -9345,16 +8916,13 @@
         <v>-16066.36387276008</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.406043277467845e-11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2455.792518640102</v>
+        <v>3.978128855061487</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000644234e-08</v>
+        <v>3.387453507608277e-07</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8180944798607266</v>
+        <v>0.5383835112374686</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8933,7 @@
         <v>1572.524</v>
       </c>
       <c r="C22" t="n">
-        <v>2217.493115999557</v>
+        <v>15987.91029839093</v>
       </c>
       <c r="D22" t="n">
         <v>6.78604e-08</v>
@@ -9398,10 +8966,7 @@
         <v>-15307.75665610602</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.087449055633758e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2432.288536473511</v>
+        <v>-13730.99765350909</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000039001e-08</v>
@@ -9564,7 +9129,7 @@
         <v>2010.119</v>
       </c>
       <c r="C2" t="n">
-        <v>2917.68223969468</v>
+        <v>1512.013650471747</v>
       </c>
       <c r="D2" t="n">
         <v>7.01467e-08</v>
@@ -9597,16 +9162,13 @@
         <v>-48579.76033740994</v>
       </c>
       <c r="Y2" t="n">
-        <v>392.3858647214501</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8098.63783532979</v>
+        <v>112.5004059325427</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.239915336039771e-06</v>
+        <v>2.571373057885018e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000510379219727</v>
+        <v>0.8777989557251499</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9179,7 @@
         <v>1650.378</v>
       </c>
       <c r="C3" t="n">
-        <v>2363.617240453161</v>
+        <v>810.4553972586007</v>
       </c>
       <c r="D3" t="n">
         <v>6.901170000000001e-08</v>
@@ -9650,16 +9212,13 @@
         <v>-74058.00108082524</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.236782568648663e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2543.975356323464</v>
+        <v>627.4964149062539</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000119147e-08</v>
+        <v>1.135052159914612e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8151763217885174</v>
+        <v>0.9971077064036751</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9229,7 @@
         <v>1566.011</v>
       </c>
       <c r="C4" t="n">
-        <v>2250.56214544429</v>
+        <v>1461.801480118405</v>
       </c>
       <c r="D4" t="n">
         <v>6.871849999999999e-08</v>
@@ -9703,16 +9262,13 @@
         <v>-62609.48196086705</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.10297097509419e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2452.546557468798</v>
+        <v>21.64312250951291</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000630069e-08</v>
+        <v>2.126649891917068e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.81544558927731</v>
+        <v>0.8889893290710508</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9279,7 @@
         <v>1517.161</v>
       </c>
       <c r="C5" t="n">
-        <v>2197.75155972025</v>
+        <v>885.6150795076318</v>
       </c>
       <c r="D5" t="n">
         <v>6.859489999999999e-08</v>
@@ -9756,16 +9312,13 @@
         <v>-42130.12097098723</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.553022794014832e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2403.962535507002</v>
+        <v>501.6567592110734</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000059433e-08</v>
+        <v>1.06489951980824e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8156291108516524</v>
+        <v>0.9916302343450906</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9329,7 @@
         <v>1495.033</v>
       </c>
       <c r="C6" t="n">
-        <v>2179.473497512298</v>
+        <v>894.223357739697</v>
       </c>
       <c r="D6" t="n">
         <v>6.85015e-08</v>
@@ -9809,16 +9362,13 @@
         <v>-26346.40992308271</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.385596207340135e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2363.838351958109</v>
+        <v>479.8117574496479</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000045021e-08</v>
+        <v>1.214363030509161e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8158345403340916</v>
+        <v>0.9776551324577181</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9379,7 @@
         <v>1462.876</v>
       </c>
       <c r="C7" t="n">
-        <v>2146.041185403216</v>
+        <v>899.4742385869424</v>
       </c>
       <c r="D7" t="n">
         <v>6.84917e-08</v>
@@ -9862,16 +9412,13 @@
         <v>-16231.46414564901</v>
       </c>
       <c r="Y7" t="n">
-        <v>1074.040966319842</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>186810696.507831</v>
+        <v>486.1830984221611</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.630490183183693e-07</v>
+        <v>1.633164104842381e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8649589617869202</v>
+        <v>0.9605807269260865</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9429,7 @@
         <v>1428.973</v>
       </c>
       <c r="C8" t="n">
-        <v>2112.5130624722</v>
+        <v>906.5324630172746</v>
       </c>
       <c r="D8" t="n">
         <v>6.84907e-08</v>
@@ -9915,16 +9462,13 @@
         <v>-5512.859662034151</v>
       </c>
       <c r="Y8" t="n">
-        <v>1068.374948206254</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>114722952.871877</v>
+        <v>456.51280624559</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.562612724679226e-07</v>
+        <v>1.311898485058176e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8714784495588442</v>
+        <v>0.9724556513299245</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9479,7 @@
         <v>1406.718</v>
       </c>
       <c r="C9" t="n">
-        <v>2095.23243794881</v>
+        <v>914.4334415386005</v>
       </c>
       <c r="D9" t="n">
         <v>6.850089999999999e-08</v>
@@ -9968,16 +9512,13 @@
         <v>1903.285491749938</v>
       </c>
       <c r="Y9" t="n">
-        <v>1062.039745893575</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>141810577.8011816</v>
+        <v>420.0019413470054</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.510729130812662e-07</v>
+        <v>1.09860382943924e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.876697387913545</v>
+        <v>0.9780787448970434</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9529,7 @@
         <v>1368.721</v>
       </c>
       <c r="C10" t="n">
-        <v>2052.789079685184</v>
+        <v>1089.060024334766</v>
       </c>
       <c r="D10" t="n">
         <v>6.853689999999999e-08</v>
@@ -10021,16 +9562,13 @@
         <v>835.0519703303619</v>
       </c>
       <c r="Y10" t="n">
-        <v>1055.946185732522</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>111482269.904886</v>
+        <v>220.6215274772578</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.467170916714975e-07</v>
+        <v>6.161061084783897e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8812835313565098</v>
+        <v>0.998728492785568</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9579,7 @@
         <v>1358.596</v>
       </c>
       <c r="C11" t="n">
-        <v>2047.111465543965</v>
+        <v>1064.20404133465</v>
       </c>
       <c r="D11" t="n">
         <v>6.85614e-08</v>
@@ -10074,16 +9612,13 @@
         <v>15461.40481727142</v>
       </c>
       <c r="Y11" t="n">
-        <v>1049.882941234716</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>180933920.122557</v>
+        <v>238.7221098681305</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.428077054446047e-07</v>
+        <v>6.500383120401123e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8855000882939355</v>
+        <v>0.9959496022465535</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1.000000000000467e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.814230204809796</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2132.121</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3189.619437900127</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.61225e-08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-82.506</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2343743442742951</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9244809474002373</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.000964525761355</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.51104332856812</v>
+      </c>
+      <c r="L12" t="n">
+        <v>70.38157436576104</v>
+      </c>
+      <c r="M12" t="n">
+        <v>88.05130521994244</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>29.3907932384448</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-76840.01227654665</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-215.2625026570679</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000024562e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8126238409191623</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2067.484</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9696841783369705</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3119.328700403459</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9779626570300362</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.50528e-08</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.354</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2208548089908971</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.928123848445807</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.471708876600364</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.691970342702316</v>
+      </c>
+      <c r="L13" t="n">
+        <v>223.0329343442915</v>
+      </c>
+      <c r="M13" t="n">
+        <v>88.104591265172</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>30.21769193406556</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-76671.13656891391</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-215.9079065880567</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000112659e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8127361061187315</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2021.42</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9480794007469557</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3075.982502601671</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9643728860101037</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.45043e-08</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.764</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3485611616468593</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.032955248312594</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.327046050758152</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.148091272999795</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.69000005984699</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>24.78992790574833</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-61176.13245778675</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-221.4207763972358</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000001930405e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8128312407084796</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1972.845</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9252969226418201</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2867.093629970189</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8988826679140532</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.417e-08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-84.044</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.07252787191573158</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8703976778886107</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.110336336973675</v>
+      </c>
+      <c r="K15" t="n">
+        <v>412.004742687768</v>
+      </c>
+      <c r="L15" t="n">
+        <v>26.16149309536137</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.63989011974138</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>17.03220488645321</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-40546.82309079404</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-154.9100226451631</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000127682e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8129965467384119</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1933.767</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9069686945534517</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2771.46466314225</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8689013586419677</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.395500000000001e-08</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-84.253</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1826653508224224</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8847209752962711</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.275462215865676</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.23593455563406</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.55807236546769</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10.49690275613332</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-23748.45357520839</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-132.5218987392977</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000001034e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8132103789963276</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1906.642</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.89424662108764</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2657.43964217258</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8331525731866289</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.38219e-08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-84.42</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3410522827334818</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.213144910882809</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.657552267463065</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21.52771544897151</v>
+      </c>
+      <c r="M17" t="n">
+        <v>74.19145667576016</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.531914860784846</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-6398.589481440563</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-99.12457857067284</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000026023e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8134185748916484</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1859.01</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8719064255734078</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2583.316103360994</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8099135817474544</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.372e-08</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.559</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1960542176726415</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7785697247593172</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.004897586342347</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.06744247813327</v>
+      </c>
+      <c r="M18" t="n">
+        <v>45.98535052200963</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.035000599110234</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-420.6473918224783</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-82.02092224711146</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000016933e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8136481426912326</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1833.137</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.85977156080729</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2455.727009386663</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7699122284642774</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.364490000000001e-08</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.68899999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.264161670762313</v>
+      </c>
+      <c r="I19" t="n">
+        <v>987.7210559440875</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.383235449790547</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.342407330990516</v>
+      </c>
+      <c r="L19" t="n">
+        <v>18.8528027549354</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-76.78609877128874</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-4.258873648679776</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>12090.36223906311</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-37.72094734345342</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000025275e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.813854540302587</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1797.168</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.842901505120957</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2424.146309226416</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7600111412734376</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.357000000000001e-08</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.812</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.05923809152265091</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.488137063290126</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.12536331376819</v>
+      </c>
+      <c r="L20" t="n">
+        <v>16.27770217327346</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-82.43159977400823</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-7.526312565517713</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>19482.54587506013</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-37.05022364773436</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000116808e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8140451335626275</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1780.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.834990134237222</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2393.806126478762</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7504989774124008</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.35288e-08</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.929</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3421487716741068</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6703626165829071</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.093152184851112</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.937072895074832</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5.471852087896089</v>
+      </c>
+      <c r="M21" t="n">
+        <v>82.65589182473957</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.758824819299897</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-16897.91057253166</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-35.02774451035589</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000467e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.814230204809796</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>1.000000000435508e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8179412466224817</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2058.602</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2812.991613620723</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.74794e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-83.813</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4543801584321411</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9215050861285461</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.820639936678351</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17.66907044972603</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-65.70931508433515</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-2.215714894342073</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7974.760763267007</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-106.2286164155344</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000001899757e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8140293700987243</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1919.579</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9324672763360764</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2638.972722285769</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.938137429741226</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.77274e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-84.069</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1037725819299271</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9180530997660872</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.662100870717262</v>
+      </c>
+      <c r="L24" t="n">
+        <v>22.8034049699186</v>
+      </c>
+      <c r="M24" t="n">
+        <v>68.25430857777698</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.507067546178828</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-4105.444491448474</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-82.60946672708087</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000067825e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.814521829023492</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1887.444</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9168571681170035</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2552.1143787942</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9072598604406301</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.78196e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.193</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2950387924040814</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.152452908789304</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.227845063926751</v>
+      </c>
+      <c r="L25" t="n">
+        <v>29.61479762259942</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-33.53220000703727</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-0.6626940644601449</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3667.350732222937</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-64.36713091428282</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.00000000001881e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8146754569102467</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1857.86</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9024862503776833</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2463.050490149349</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8755982343577093</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.78706e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.27500000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.397687786448148</v>
+      </c>
+      <c r="I26" t="n">
+        <v>730.2180776780416</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.242644028281791</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.393072511955302</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28.82280802736893</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-66.6106641159671</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-2.312044204314832</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>7557.655430969498</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-38.18907165460018</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000615846e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8147582496974379</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1834.953</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8913587959207266</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2872.315879623764</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.021089386017288</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.92236e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.755</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4752620989306149</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.145349964446096</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.513414921905881</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.239048494630296</v>
+      </c>
+      <c r="L27" t="n">
+        <v>245.8475369518642</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.00077382004689</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>28.64734623184315</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-65630.98061932939</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-231.2580607331029</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000001421993e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8148045760751251</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1813.986</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8811737285789092</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2900.245835091564</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.031018301316061</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.90902e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.917</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3492574154833302</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.288621630941714</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.438124475179138</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.115440013575289</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.72752814586424</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>25.19975443342456</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-56895.36174195277</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-256.1375206803079</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000706327e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8148714646566978</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1773.481</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8614977543012198</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2781.327358355878</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9887435657072265</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.90448e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.009</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.06576810302047548</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6311631942841991</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.336571488270056</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.958910848646772</v>
+      </c>
+      <c r="L29" t="n">
+        <v>14.29256977800766</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.3188431259309</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>21.35419690208468</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-47327.05424900413</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-214.3819748332485</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000070395e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8149580221425988</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1765.362</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8575538156477065</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2351.693597957975</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8360115922745353</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.89808e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.083</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4057434292168398</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.201337701024349</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.11348226407737</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.502531234474674</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.42226254303172</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>22.21215999573946</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-48963.4742857961</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-29.11721698637666</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000034529e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8150450636151971</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1750.148</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8501633632921759</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2617.314151392094</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9304379503724277</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.896299999999999e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.14700000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4170430816817713</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.104176681605816</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.184520022376841</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.475583762612138</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.36773313344881</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>21.75139013265514</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-47516.06608020557</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-159.7788356266835</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000004330382e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8151516295079959</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1733.737</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8421914483712732</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2602.985893314182</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9253443489523122</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.89257e-08</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.194</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3267231200034272</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.167394342512154</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.087083520332675</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.461072396555181</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.39339591616216</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>21.96583911005257</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-47657.55043392426</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-161.3941392715255</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000022788e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8152982860708917</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1708.16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8297669972146144</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2648.731150209597</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9416064866259237</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6.88937e-08</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.246</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.07923899417197085</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.768895196648223</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.867679425326893</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.376577545247151</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.14813825231388</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20.07406396717945</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-43038.86747210872</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-189.1163911258977</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000379033e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8154835925613381</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1704.881</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8281741686834073</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2582.379064388451</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9180187569292323</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6.88594e-08</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.271</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3396301654230586</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.311910016073335</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.490980897022942</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.529336409683285</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.51984458494603</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>23.08725841649229</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-49505.18196301869</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-166.1730487695222</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000140426e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8156713198400521</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1677.718</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8149792917717945</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2577.266044999988</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9162011121969459</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.88173e-08</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.32299999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1615815026312842</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8175045119208715</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.901732320712659</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.24644200621972</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.30288265207135</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>21.2276459961044</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-44963.83211327767</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-171.8575956792299</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000003581505e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8159098350356051</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1676.577</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8144250321334574</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2254.603912895018</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8014968484008455</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.84767e-08</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.633</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3950762642919339</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.06886658176147</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.911590063092414</v>
+      </c>
+      <c r="L36" t="n">
+        <v>19.36734462883731</v>
+      </c>
+      <c r="M36" t="n">
+        <v>38.01064789776142</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.7815849494580217</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>243.5865482251355</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-29.0033442609415</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000002325532e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8161456690907986</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1654.581</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.8037401110073729</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2236.724581631821</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7951408638409826</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.84863e-08</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.70399999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.340441269891429</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.868853761696838</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.396633520415679</v>
+      </c>
+      <c r="L37" t="n">
+        <v>17.88554306623543</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-44.80258112615174</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-0.9931324171214956</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4049.962157504391</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-28.39849443273829</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000321449e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8163903954638848</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1640.194</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.796751387592162</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2377.78503759817</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8452869273000142</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.854860000000001e-08</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.622</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3350962199162855</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.011986509205258</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.14446529658988</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>18.04726569633489</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.32949883650566</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.07117145654693</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-19840.82956715482</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-102.7828112546911</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000049537e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8166355055745373</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1629.852</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7917275898886719</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2197.547898975689</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7812138110668343</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6.841669999999999e-08</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.845</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5057244567015815</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.533178215643016</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.171655739701199</v>
+      </c>
+      <c r="L39" t="n">
+        <v>14.46562109079477</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-83.05180615951504</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-8.205677411610846</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>19519.92006611818</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-26.42696082643965</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.00000000036226e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8168914354971314</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1603.71</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7790286806288927</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2177.327402683619</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7740255577516943</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.840150000000001e-08</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.911</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.03489195936144598</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.769939064847059</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.977302990787715</v>
+      </c>
+      <c r="L40" t="n">
+        <v>16.7810493556606</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-81.85952438131247</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-6.990959076751902</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>16628.51016872962</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-24.9668642739332</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000344816e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8171500330217488</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1584.776</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7698311766917547</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2164.617626444844</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7695073159705127</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.8376e-08</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.94199999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2196242105599186</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.949549549663012</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.295906355342668</v>
+      </c>
+      <c r="L41" t="n">
+        <v>16.65922768774281</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-80.39838400769001</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-5.911341075263284</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>14239.27019081562</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-27.2396491170889</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000338555e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8174073760261732</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1565.679</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.760554492806283</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2145.602215795323</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7627474626679124</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6.84333e-08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.949</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1186803508687396</v>
+      </c>
+      <c r="I42" t="n">
+        <v>465.0771447642225</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.216270597819965</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.576697513857683</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-63.09955057614199</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-1.971069359565729</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>5873.204082927272</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-27.02742287050432</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000135527e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8176774955586625</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1548.366</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7521444164534959</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2123.889530930061</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7550287461384609</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.84467e-08</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.998</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1275635332353491</v>
+      </c>
+      <c r="I43" t="n">
+        <v>345.3732642513999</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.273493165225116</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.824408559035502</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-69.62958949863966</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-2.693175278695681</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>7324.253338262391</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-24.69454050274294</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000435508e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8179412466224817</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1.000000000089927e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8170488691685506</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2130</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2828.102594364345</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.740070000000001e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.35899999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1580295787236385</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.069636761434954</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.316777065036722</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.359598161451792</v>
+      </c>
+      <c r="L23" t="n">
+        <v>30.40500353390687</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.40808114583562</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>22.09046401895205</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-57612.37529112391</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-75.23480821967223</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000353349e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8130108639113784</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1990.322</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9344234741784037</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3048.529502085019</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.077941623532302</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.55186e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.377</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.15597662669536</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.804448181899402</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.964976895865203</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.839260274199415</v>
+      </c>
+      <c r="L24" t="n">
+        <v>136.0127590362873</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.23777067129679</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>32.5029839488345</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-80256.39060911685</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-221.0534672194676</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000160544e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8133994860999627</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1963.209</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9216943661971831</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2832.983499810754</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.001725858692727</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.47311e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.00700000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4214937090948205</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.532845405562863</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.303454962172879</v>
+      </c>
+      <c r="K25" t="n">
+        <v>322.4729132133072</v>
+      </c>
+      <c r="L25" t="n">
+        <v>34.29149545690387</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.34884385921778</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21.5961941619497</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-51535.25844373357</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-151.8131924648724</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000092494e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8135096614813595</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1928.942</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9056065727699532</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2722.708978417177</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.962733453815576</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.434270000000001e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.289</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3990947454883627</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.04718887486033</v>
+      </c>
+      <c r="J26" t="n">
+        <v>562.4458520221332</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.348477644807508</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.25388086006874</v>
+      </c>
+      <c r="M26" t="n">
+        <v>82.20491213081031</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7.304835606516962</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-15732.08497911205</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-118.3792067745319</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000130792e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8135940824648769</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1890.948</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8877690140845069</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2598.516533908582</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9188197553676916</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.414810000000001e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.47</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1958259552771341</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7575991155664278</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.197567526764884</v>
+      </c>
+      <c r="L27" t="n">
+        <v>19.87413801614347</v>
+      </c>
+      <c r="M27" t="n">
+        <v>10.14312710119752</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.1789038273068075</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1610.646372966079</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-75.03147763158881</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000141992e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8137013118070346</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1865.042</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.875606572769953</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2505.249223996454</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8858409977731178</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.399980000000001e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.622</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1630152208283609</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.686931970383128</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.216059520728476</v>
+      </c>
+      <c r="L28" t="n">
+        <v>17.3349869625258</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-82.04743849485872</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-7.158369266781004</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>19151.64821697749</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-44.00739275724436</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000168204e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.813818146844563</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1854.873</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8708323943661972</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2471.394457046254</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8738701566099775</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.39136e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.72799999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.293593661308444</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.062945521271499</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.316385048721868</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.562918941348437</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>82.6468918039423</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>7.749223325492801</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-17379.51475196866</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-39.07730208790917</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000858937e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8139686487906279</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1837.504</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8626779342723004</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2434.476526685094</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8608161993614929</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.385170000000001e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.837</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.658982534001837</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.296508888095846</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.53453796222686</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.806789448732688</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>83.03672626642278</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.187731310842549</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-18265.96631159286</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-32.54801634049272</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000152786e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8141281714136135</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1811.805</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8506126760563381</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2412.432404627066</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8530215309141898</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.38007e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.902</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.32984824405361</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.296957869396333</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.423771901983319</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.625267641330924</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>82.79216215529004</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7.907116044594668</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-17429.16732465491</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-32.66794953416752</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000450889e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8143032206753101</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1783.946</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8375333333333334</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2386.288366547039</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8437771569186621</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.37627e-08</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2729264226267282</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.03906723245154</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.078088519867189</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.024956456466199</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>82.56310257964626</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7.660943623567285</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-16688.27394000787</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-30.25615837425676</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.00000000000717e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8144778646036316</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1757.436</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.825087323943662</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2359.809840461939</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8344145099843303</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6.373989999999999e-08</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-85.056</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.06609625557926974</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.712282329320996</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.821712515724188</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.601343412375206</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6.49972096216698</v>
+      </c>
+      <c r="M33" t="n">
+        <v>82.23306190620703</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7.331639520279781</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-15769.0620547541</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-27.75923357900911</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.00000000052814e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8146771151968254</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1746.766</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8200779342723004</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2336.704532981253</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8262446127794946</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6.3729e-08</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-85.133</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3933404076447223</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.071486841442027</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.472536317713148</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.153526135518121</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>82.50606800820141</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7.601975363329343</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-16253.52181116075</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-26.57544568689036</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000209167e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8148807343212996</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1731.362</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8128460093896713</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2317.571615201233</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8194793285857223</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.3716e-08</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-85.203</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4654544198926757</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.555597913374986</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.521592688617574</v>
+      </c>
+      <c r="K35" t="n">
+        <v>84.86890251743107</v>
+      </c>
+      <c r="L35" t="n">
+        <v>22.42573878765785</v>
+      </c>
+      <c r="M35" t="n">
+        <v>82.75603483147846</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.867261230982351</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-16715.06673198813</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-27.03246557662692</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000003700823e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8151006963176228</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1710.801</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8031929577464788</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2292.273513080904</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8105340724373981</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.36922e-08</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-85.25700000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1584921865606517</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.175420956246815</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.117284836218874</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.387009919038376</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>82.57422742846562</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7.672550623320563</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-16117.76919812736</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-25.0834098484795</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000114633e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8153244681154601</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1685.238</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7911915492957747</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2271.500433271888</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8031888368542155</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.36945e-08</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-85.322</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2133279147626263</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8213329672743404</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.990190307023456</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.950945897487208</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>82.31096173310172</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7.406831651867853</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-15374.21500809582</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-24.78850735269248</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.00000000642978e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8155510463640283</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1666.843</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7825553990610328</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2249.2275997659</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7953132974199774</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.36918e-08</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-85.401</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3419949327900979</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.857407207973485</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.003504997896159</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.842874762838925</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>82.39128011185888</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7.4859605965272</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-15401.70994721583</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-23.66552046277957</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.00000000006778e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8157929667660343</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1640.389</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7701356807511737</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2228.23362902894</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7878899561385134</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6.36817e-08</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-85.45</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1967301522627209</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.6414688705217806</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.813678695379959</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.134069767441859</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>82.07863491517216</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7.186925443500214</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-14606.28364334215</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-23.27805834879996</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000001617385e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.816027122175902</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1624.023</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7624521126760562</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2207.17213402863</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7804427386852713</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.36817e-08</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.50700000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1604204294412884</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.669975273499428</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.757336367665618</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.220499864432375</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>82.01049780865009</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.1248415104164</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-14335.54501288281</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-22.60075835923385</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000075597e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8162853293675241</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1605.438</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7537267605633803</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2184.174878018974</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7723110478281277</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.36643e-08</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.56399999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.04889432344159064</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7731944817870466</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.675676841011736</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.281008539207324</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>82.03847132861051</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.150202160846341</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-14260.04878831147</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-20.80866304859228</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000010916e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8165295367997146</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1600.409</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7513657276995306</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2168.513524727765</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7667732878747167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6.36642e-08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.619</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6540865509207645</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.316073894541076</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.484518542411394</v>
+      </c>
+      <c r="K42" t="n">
+        <v>88.26794817049611</v>
+      </c>
+      <c r="L42" t="n">
+        <v>20.14386897762218</v>
+      </c>
+      <c r="M42" t="n">
+        <v>82.58977545658749</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7.688830565337469</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-15288.69473552221</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-22.31062851937622</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000005916e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8167862150656783</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1576.464</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7401239436619718</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2145.035785114358</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7584717009166648</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.366399999999999e-08</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.66800000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.397888051238116</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9804175531918452</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.135804950262686</v>
+      </c>
+      <c r="K43" t="n">
+        <v>106.2490284567456</v>
+      </c>
+      <c r="L43" t="n">
+        <v>16.91258002358736</v>
+      </c>
+      <c r="M43" t="n">
+        <v>82.28823448463952</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7.384738378755111</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-14503.35821236979</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-20.17255028545333</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000089927e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8170488691685506</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.000000000023074e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8137422252644344</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2635.925</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3459.681233894288</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.807770000000001e-08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-77.313</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.04550344814309736</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5580797666755246</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.418663878511529</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.766487141873533</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.40332360891977</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.79996252394287</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.98807051125864</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-33913.17346430986</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-115.5314203880368</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000185512e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.811194722778607</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2242.776</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8508497017176135</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2913.116084783756</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8420186392446025</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.74003e-08</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.084</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3245242578422265</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8567645075295822</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.780614927576904</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.002013520060604</v>
+      </c>
+      <c r="L13" t="n">
+        <v>28.80511722086773</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.39422175177619</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>21.97281024128023</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-59676.98683048016</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-59.91660437868882</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000007171e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8123093237459992</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2148.145</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8149492113774103</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3148.246781345115</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9099817493305254</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.617129999999999e-08</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.651</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3970203475726921</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9920027205718991</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.88447485836918</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.574334311713713</v>
+      </c>
+      <c r="L14" t="n">
+        <v>70.40106069079212</v>
+      </c>
+      <c r="M14" t="n">
+        <v>88.30846062536317</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>33.86213351235661</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-88793.05783803968</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-198.7200451608683</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000011272e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8125806612880909</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2077.364</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7880967781708509</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3093.770369116862</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8942356708494934</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.55808e-08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.285</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.222679911297436</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8959392974463951</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.153423847076427</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.626900353123343</v>
+      </c>
+      <c r="L15" t="n">
+        <v>216.2076776011839</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.14230204396958</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>30.83154641646207</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-78445.74332960373</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-200.4009151988932</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.00000000001852e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8127328977220692</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2042.015</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7746863055663573</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2695.285028624283</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7790558859061172</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.53113e-08</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.646</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4112659140558896</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.289500538285351</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.050059766324692</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.326048107358549</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.86450806269114</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>26.81782363821599</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-66733.2851430825</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-53.79135226498465</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000149396e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8128842293572777</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1988.128</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7542430076728283</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2830.567301616297</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.818158411210085</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.51838e-08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.913</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.08243634189666081</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7861537736643299</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.134458874961983</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.302076675158259</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.64282388502379</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17.04712313695595</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-40833.41244077377</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-131.8807726640603</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000152931e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8130514773053217</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1951.536</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.740360973851684</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2745.603046220148</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7936000054923097</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.51042e-08</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.09699999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1230264301439157</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9809079507791082</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.129788354064586</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>23.80932746228655</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.03898339160779</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11.52032484958182</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-26478.52027116762</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-112.9339259174455</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000125036e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8132137327329829</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1924.12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.729960070942838</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2693.861410989606</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7786443978127258</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.50668e-08</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.259</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3359268731767412</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.248549101683565</v>
+      </c>
+      <c r="J19" t="n">
+        <v>255.8684253981218</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.390230129602131</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.97194545176075</v>
+      </c>
+      <c r="M19" t="n">
+        <v>77.96061947910844</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.688781213721339</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9327.408867039567</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-106.6940925262718</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.00000000026676e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8133796058844598</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1894.526</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7187328926278252</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2606.977707879221</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7535311873067432</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.50538e-08</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.387</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4156084745312651</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.511120816133291</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.44365165026855</v>
+      </c>
+      <c r="L20" t="n">
+        <v>19.01463507159734</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-24.75953327825828</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.4612080787200517</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3264.069165949725</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-83.07667295031433</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000002224216e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8135550389336141</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1865.824</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7078441154433455</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2518.349302224149</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7279136810501595</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.50517e-08</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.497</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4801716831424558</v>
+      </c>
+      <c r="I21" t="n">
+        <v>233.9765723461011</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.267426904202037</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.625076270868216</v>
+      </c>
+      <c r="L21" t="n">
+        <v>12.35932724304997</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-78.31701812655305</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-4.836050560703918</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>13687.38722258985</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-56.98337200860601</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000023074e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8137422252644344</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>1.0000000000519e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8178419656413997</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2115.868</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2806.796892493367</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.68646e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-82.277</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5224662395404657</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8596903279918767</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.779849853921197</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.451980227520143</v>
+      </c>
+      <c r="L23" t="n">
+        <v>49.58616221477614</v>
+      </c>
+      <c r="M23" t="n">
+        <v>88.10408525269288</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>30.20962105852097</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-78594.54834015714</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-74.27994813402665</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000923e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8127349193393201</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1994.89</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9428234653579525</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3033.165948476659</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.080650315877399</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.56379e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.631</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2299875267411905</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9765537385766515</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.435031411780813</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.15973285987229</v>
+      </c>
+      <c r="L24" t="n">
+        <v>300.4750651305349</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.00266796165695</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>28.67453559113178</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-70461.33876678524</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-215.5865585964525</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000002362421e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8130220748634609</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1947.371</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9203650700327243</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2764.837816330763</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.985050904012748</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.53195e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.038</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2186282747559263</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.006599740111411</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.01788693361006</v>
+      </c>
+      <c r="K25" t="n">
+        <v>454.9545991151126</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24.2013184924612</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.09871374465523</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.66367803259995</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-34260.85119992684</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-122.7968825307535</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000626478e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8131284198321581</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1922.022</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9083846440326147</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2656.926244043025</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9466043842177667</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.51826e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.254</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2132916421850715</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.074112447211002</v>
+      </c>
+      <c r="J26" t="n">
+        <v>701.332437404939</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.768126543859957</v>
+      </c>
+      <c r="L26" t="n">
+        <v>23.27308236530344</v>
+      </c>
+      <c r="M26" t="n">
+        <v>78.10228108292959</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4.746276572635655</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-9528.855288247358</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-89.48785663239119</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000459937e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8132293587807676</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1896.409</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8962794465439243</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2586.090468427834</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9213671553307613</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.51337e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.405</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.150290940774579</v>
+      </c>
+      <c r="I27" t="n">
+        <v>997.7145411517471</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.110722426395651</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.957266499651763</v>
+      </c>
+      <c r="L27" t="n">
+        <v>21.91682704374759</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-69.68331444941018</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-2.700933705203028</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8611.958834524094</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-69.98620983400428</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000139599e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8133959097042963</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1877.361</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.887276994595126</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2491.516362014866</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8876724812822392</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.51319e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.51600000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>963.9600873800287</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.056855734435787</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.375406652913493</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.566344750190809</v>
+      </c>
+      <c r="L28" t="n">
+        <v>15.23016660033596</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-84.17006358102275</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-9.793916039797647</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>25634.43472015978</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-38.55498098183944</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000130665e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.813588395598457</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1847.789</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8733006973970022</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2467.576692162034</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8791433034436656</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.512e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="H29" t="n">
+        <v>859.7398174529048</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9450573178502284</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.691040537328041</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.82080385896931</v>
+      </c>
+      <c r="L29" t="n">
+        <v>18.46936484995584</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-84.17881511505529</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-9.808742199680122</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>25320.98282286995</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-38.81827452781181</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000002077736e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8138108417260976</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1826.097</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8630486400852984</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2435.102746947951</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8675735509970482</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.512470000000001e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.68899999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2159452420063499</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.192938989066114</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.363034497360235</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.954927296358205</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3.604128231278341</v>
+      </c>
+      <c r="M30" t="n">
+        <v>82.72326703628727</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>7.831453004417508</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-17405.60786540977</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-34.82964645475636</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000059899e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8140396719454193</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1793.836</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8478014696568973</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2404.298960198047</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8565988392776904</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.51447e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.785</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1539813821686699</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7247079262969177</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.738583694049607</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.333325695998801</v>
+      </c>
+      <c r="L31" t="n">
+        <v>18.38893480456041</v>
+      </c>
+      <c r="M31" t="n">
+        <v>82.2923416967986</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7.388721433240787</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-16172.14336217859</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-31.29192626394638</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000003111544e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8142978253090731</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1772.736</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8378292029559501</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2378.853283124959</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8475331041897187</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.5148e-08</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.87</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0570491373193269</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.689910969529472</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.677377225359953</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.386536921154347</v>
+      </c>
+      <c r="L32" t="n">
+        <v>17.29287226173624</v>
+      </c>
+      <c r="M32" t="n">
+        <v>82.32897058829273</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7.424430556842815</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-16097.17823252997</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-30.38932168361521</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000013651e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.814566077357348</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1772.46</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8376987600360704</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2353.995971239091</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8386769906774273</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6.514770000000001e-08</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.919</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6926409794846983</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.378933562063089</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.876763641746646</v>
+      </c>
+      <c r="K33" t="n">
+        <v>6.020939149231372</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>83.32285369878258</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8.541996977027232</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-18538.40743180953</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-29.07066766962384</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000019037e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8148507923077259</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1732.818</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8189631867394375</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2329.502979431457</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8299506763961411</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6.51546e-08</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-85.005</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.08430795675470899</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8693581035100446</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.892837839986041</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.346879071618357</v>
+      </c>
+      <c r="L34" t="n">
+        <v>12.68698203670818</v>
+      </c>
+      <c r="M34" t="n">
+        <v>82.36623349893193</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7.461107298526787</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-15863.74319316536</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-27.90069457430218</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000029963e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8151318643277632</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1725.676</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8155877398779131</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2304.348314525935</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8209886225429402</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.515700000000001e-08</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-85.078</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4538014456128008</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.270728528200539</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.588698396316813</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5.264117793118986</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>83.07434174599595</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>8.232641241472745</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-17467.62813982737</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-26.46303235969253</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000496e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.815424033264312</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1699.515</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8032235470265632</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2278.623286803886</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8118233609627923</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.51468e-08</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-85.13800000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2807208115207647</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9320509599010536</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.562637252825413</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.090386287698845</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>82.72754687888354</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7.836111738943879</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-16404.74254993359</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-24.56810908166813</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.00000000008681e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8157111145780713</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1685.338</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7965232235659313</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2255.002148410209</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8034076688773227</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.51408e-08</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-85.209</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4671266925861034</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.507284691641977</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.600534237754687</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5.478308216028103</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>83.11804821964103</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8.28543693889398</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-17247.90450462234</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-23.1865363533484</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000003920471e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8160036355184819</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1653.387</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7814225651127575</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2235.525105579844</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7964684268956689</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.516190000000001e-08</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-85.26900000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1924618333284086</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8569416684325321</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.891929918773218</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.760301571238977</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.464175592813915</v>
+      </c>
+      <c r="M38" t="n">
+        <v>82.54717801170752</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7.644388848204028</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-15655.70638275604</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-24.22198273955769</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000001989374e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8163055244018254</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1631.66</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7711539661264315</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2209.153707003426</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7870728775964138</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6.514720000000001e-08</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-85.339</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2192511755180279</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.069544199669198</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.262563459775259</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.933499878697754</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>82.53719370838013</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7.634045252253546</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-15475.9528379699</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-21.94800508521917</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000003885e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8166031456178153</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1598.629</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.755542878856337</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2187.69409422905</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.779427289548426</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.516729999999999e-08</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.413</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.01077199133467825</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.5623969768540781</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.925911354952493</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.351554236717937</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>81.78827322698132</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>6.92947253069374</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-13788.50815160075</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-22.04325611011723</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000080488e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8169071089293406</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1601.069</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7566960698871574</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2160.776902389359</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.769837286113664</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.51763e-08</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.47799999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3230803326864015</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.11745834705278</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.710850112336614</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.586149634659372</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>82.94100422387126</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>8.075594846681611</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-16107.91924259595</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-19.46475045721036</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000008409e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8172039036849513</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1573.746</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7437826934383431</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2140.440098979822</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7625917303472576</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6.517709999999999e-08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.536</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4063705285693058</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.753871161041425</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.212174743685456</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.686132008045209</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>82.68857782797556</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7.793892956118331</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-15340.87843996631</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-20.31491346235293</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000080993e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.817526089437753</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1549.245</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7322030485833709</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2117.344812237791</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7543633876396685</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.51972e-08</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.59399999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2336070175640058</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.800136050538975</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.651468209523168</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.352616131184802</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>82.33801949786105</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7.433304519653019</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-14424.35012449286</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-19.83166407985686</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.0000000000519e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8178419656413997</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1.000000000097333e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8136157439402472</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2657.887</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3508.690894027779</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.869109999999999e-08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-77.56399999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.368670535899603</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.018778616827501</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.104693583118042</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.079354626743005</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.73429738230535</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.20881726625123</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.93070085217297</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-37181.95774067543</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-137.8472729825344</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000006821e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8109729998283166</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2193.718</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8253616500626249</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2872.281087497064</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8186190161082691</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.773579999999999e-08</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.58</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1428075333806495</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.112463845473705</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.433034428350365</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.253716394962943</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40.92582888887071</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.68078154358194</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>24.6912849006731</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-66059.70141254611</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-60.38762120898787</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000001999e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8122060551240007</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2092.929</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7874409258181405</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3103.428282241298</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8844974880869992</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.68213e-08</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.824</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3060606607977521</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.26235226147249</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.621115819462565</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.907755154428532</v>
+      </c>
+      <c r="L14" t="n">
+        <v>114.5159154914054</v>
+      </c>
+      <c r="M14" t="n">
+        <v>88.24301206018693</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>32.60000687122984</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-83852.57578949022</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-200.9543207064928</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000005625e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8124861103466645</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2036.818</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7663297950590072</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3049.835382911667</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8692231590143378</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.6444e-08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.35599999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1474345053483577</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9258873759680991</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.281035562291068</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.711910285079546</v>
+      </c>
+      <c r="L15" t="n">
+        <v>248.6927140617362</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.06285369564924</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>29.56614394701412</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-74013.20132172584</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-201.8614941675137</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000004289e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8126131828785502</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1992.979</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.749835865858857</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3014.270517406017</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8590869382471604</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.62592e-08</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.666</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1076303433884637</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7515393588475775</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.036844956890463</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.904420255761019</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.46376315789631</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>22.57610603262578</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-55004.40421502014</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-205.7233137859641</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000004206e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8127358872415184</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1973.083</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7423502203065818</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2796.671816160657</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7970698760956498</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.61719e-08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.893</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4700390066022139</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.407290598965406</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.87943595928412</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>37.20917935819942</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.66071576043031</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17.1386704082084</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-40656.91250923482</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-132.0690246431341</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000029043e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8128738039469225</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1933.396</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7274184342675215</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2739.834111177273</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7808707560534347</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.61369e-08</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.071</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.339361609702095</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.291496295870567</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.824557720328762</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>27.60731814421631</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.41402179195856</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10.22455327739217</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-23038.00394133735</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-123.1546713698674</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000001490659e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8130346229438706</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1894.82</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7129046494452173</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2660.34576001564</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7582160527574183</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.6136e-08</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.217</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2804282024296779</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.015041879947511</v>
+      </c>
+      <c r="J19" t="n">
+        <v>775.7964998472776</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.818694001047188</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23.11977899084852</v>
+      </c>
+      <c r="M19" t="n">
+        <v>79.19560156564935</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.239998094337719</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-10650.116553725</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-102.8640501191705</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000002348099e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8132137836730984</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1874.924</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.705419003892942</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2508.283645289495</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7148773491443491</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.61349e-08</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.33799999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4938244097451646</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.385171385396958</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.376952961017122</v>
+      </c>
+      <c r="L20" t="n">
+        <v>22.40035351755466</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-21.92849277603647</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.4025751942797905</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3080.166053908959</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-48.04208357758284</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000497801e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8134093161771635</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1840.192</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6923514807062904</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2452.475242539742</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.698971587013879</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.61646e-08</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.455</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3549174609987874</v>
+      </c>
+      <c r="I21" t="n">
+        <v>569.5643109027702</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.156861594970937</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.68174851275586</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.14222002904654</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-75.28400969379423</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-3.807443826322291</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11047.61525274087</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-35.52836531138291</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000097333e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8136157439402472</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>1.000000000651405e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8163970762775339</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2112.708</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2823.078556257497</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.923909999999999e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.149</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.02004990114195903</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8035893550285281</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.057892972621946</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.016597909889322</v>
+      </c>
+      <c r="L23" t="n">
+        <v>29.87246431620744</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.26965780233698</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>20.96894774203287</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-54464.96287665951</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-76.52156452472195</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000068123e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8126956674502752</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1977.818</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9361530320328223</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3012.414794770176</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.067067293644028</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.73327e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.215</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2966307433737653</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.118247964962843</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.424259341866376</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.820198313833394</v>
+      </c>
+      <c r="L24" t="n">
+        <v>144.6082177062939</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.25526778769634</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>32.82914605098639</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-80669.62904581991</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-217.7725480110171</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.0000000037225e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8130326148565623</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1933.114</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9149934586322388</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2884.376599858653</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.021713190894134</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.688940000000001e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.748</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2816896166728754</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.095836514455185</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.393509347176842</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.351802816360049</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.76978611891255</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>25.6777344837205</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-61257.09970802224</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-184.968175278837</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000018462e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8131080792903281</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1911.507</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9047662999335448</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2768.082903828097</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9805192624528637</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.67038e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.01000000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6222679677783994</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.606568660345036</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.024282822529965</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>38.47842985017402</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.51862535185441</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.43754459421508</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-37930.7087741549</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-149.4808334467918</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000016909e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8131771093337712</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1870.091</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8851630230017588</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2615.707762795005</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9265444480803254</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.66288e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.17700000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1964211091759708</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8676938478135484</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.399829657718957</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>23.04510424740899</v>
+      </c>
+      <c r="M27" t="n">
+        <v>83.72447086690875</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.093492854115269</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-19817.84052044459</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-94.27902473251015</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000001365048e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.813283468521506</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1848.106</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8747569470082944</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2558.684142143844</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9063453570827458</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.66054e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.309</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3621063804832538</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.059122115772579</v>
+      </c>
+      <c r="J28" t="n">
+        <v>308.5689945119358</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.803049152916322</v>
+      </c>
+      <c r="L28" t="n">
+        <v>23.09022103703036</v>
+      </c>
+      <c r="M28" t="n">
+        <v>73.19361397958819</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>3.310826101955204</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-5842.658061940697</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-79.76205344096888</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000016682e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.813419236779981</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1826.383</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8644748824731102</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2438.099999165542</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.863631652672707</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.65822e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.413</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2268032068809779</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.186848658609656</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.813202662031709</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23.36606636500764</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-40.3947259605872</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.8509079992515665</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4033.184208893517</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-35.3686300385782</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000106446e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8135655042494276</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1806.192</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8549179536405409</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2405.916448864974</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8522314915864236</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.65943e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.501</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2826317231400974</v>
+      </c>
+      <c r="I30" t="n">
+        <v>109.2245808686943</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.963253499786657</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.718578786218772</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.01638682371835</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-77.34308860832034</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-4.452961774792365</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>12418.75004068838</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-30.65176389408384</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.211874841429044e-06</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.5000563328564563</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1789.047</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8468027763420216</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2386.444454284232</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8453340588041931</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.66098e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.58</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2315372922585823</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.08247889450443</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.978139712027799</v>
+      </c>
+      <c r="L31" t="n">
+        <v>21.59286806384119</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-82.75673564432105</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-7.868030589990516</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>20229.59207957098</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-31.14592012486673</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.217394013992102e-06</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.5001064745672358</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1777.308</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8412464003544265</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2365.32092582185</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8378516143587275</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.66092e-08</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.649</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.299504293409823</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.436665893629074</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.433580754824138</v>
+      </c>
+      <c r="L32" t="n">
+        <v>11.81036933400633</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-85.45352960590004</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-12.57579365416156</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>30999.36380989699</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-30.4642188812968</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.223676434887456e-06</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.50017299514923</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1747.524</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.827148853509335</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2344.1454603911</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8303507726326574</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6.66359e-08</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.724</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8551203760470256</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.138101622679569</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.392742334305396</v>
+      </c>
+      <c r="L33" t="n">
+        <v>18.61633231269152</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-84.77772390229033</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-10.94102024882034</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>26805.84484575409</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-29.45823111706522</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000125491e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.814220548455625</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1729.993</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.818850972306632</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2281.413081092723</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8081295067173582</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6.66293e-08</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.788</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3556182464170944</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9013461880111284</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.06800882454366</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.006150566351298</v>
+      </c>
+      <c r="L34" t="n">
+        <v>15.56188178462839</v>
+      </c>
+      <c r="M34" t="n">
+        <v>82.6544099938159</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7.757242348223084</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-16552.66532110814</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-9.896565633882574</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000079327e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.814409419532958</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1706.314</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.807643081769937</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2301.402071894668</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8152100715700924</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.66455e-08</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.834</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.09067411212974082</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.7301172327593519</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.834602953475233</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.661961976684862</v>
+      </c>
+      <c r="L35" t="n">
+        <v>16.93992091927861</v>
+      </c>
+      <c r="M35" t="n">
+        <v>82.44241758664617</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.537211873363496</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-15918.01141821042</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-26.51640165076174</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000677394e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8145926991059536</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1703.838</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8064711261565726</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2284.20925519762</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8091199765357411</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.66379e-08</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.90000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6009831210715595</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.29942970736833</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.349827811549894</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5.20014064547841</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>83.03310516837367</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8.183433467878601</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-17260.47574685215</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-26.43644279677369</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000339211e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8147965180180896</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1674.799</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7927262073130787</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2264.639341571865</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8021878585532722</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.665789999999999e-08</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.953</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.06389166504155996</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6513750290726031</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.893547474470874</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.477157933901059</v>
+      </c>
+      <c r="L37" t="n">
+        <v>16.06042716245127</v>
+      </c>
+      <c r="M37" t="n">
+        <v>82.60768981812728</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7.707672668899513</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-16043.51675191806</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-25.40345952532857</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000001428e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8149999008664018</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1660.743</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7860731345742051</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2246.749575460708</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7958508878474788</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.66758e-08</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-85.01600000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1377992568548741</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8762971873701927</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.998365500248114</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.513496791042947</v>
+      </c>
+      <c r="L38" t="n">
+        <v>14.62220492627065</v>
+      </c>
+      <c r="M38" t="n">
+        <v>82.63848551794553</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7.740276334518517</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-15988.56842160121</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-25.18433887682681</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000049384e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8152138345291587</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1636.787</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7747341326865803</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2224.57180679877</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7879950070351014</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6.66753e-08</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-85.06399999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.02655801514781532</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7082250939778825</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.538852989939429</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.165731556708198</v>
+      </c>
+      <c r="L39" t="n">
+        <v>15.0133880260605</v>
+      </c>
+      <c r="M39" t="n">
+        <v>82.26139441669933</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7.358813126005243</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-15020.97071327513</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-23.18743525783202</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000470609e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8154361702375132</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1627.471</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7703246260249879</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2210.431550203152</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7829861996945208</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.66815e-08</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.13</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2564876377721994</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.311710739826169</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.264759311502441</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.321101042772916</v>
+      </c>
+      <c r="L40" t="n">
+        <v>10.17954756538399</v>
+      </c>
+      <c r="M40" t="n">
+        <v>82.65286823427783</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.755596552276817</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-15768.30395494532</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-24.64531756826295</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000001431337e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8156650072255058</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1610.084</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7620949037917214</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2186.337993423386</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7744517022302678</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.669580000000001e-08</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.191</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4041347779387621</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9885907263208565</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.03488031465544</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.521479353136618</v>
+      </c>
+      <c r="L41" t="n">
+        <v>9.462410376914907</v>
+      </c>
+      <c r="M41" t="n">
+        <v>82.6918934023077</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.797467595315508</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-15725.08428232545</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-21.64959849942147</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000115598e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8159059118651605</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1599.406</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7570407268775429</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2172.004163009984</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7693743265470334</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6.66883e-08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.236</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6769081605682188</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.081698154366681</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.477570224587692</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.420716546159114</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>82.9750707414034</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>8.115154580887042</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-16279.86037098733</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-23.08231022992618</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000122447e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8161470324889236</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1579.482</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7476101761341368</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2150.051154652211</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7615980610551957</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.670460000000001e-08</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.282</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3236187105159638</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.006439306796309</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.934430624337532</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.735956474553339</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6.138305574860983</v>
+      </c>
+      <c r="M43" t="n">
+        <v>82.74285413621382</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7.85281886875032</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-15583.04995540379</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-20.90792303976855</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000651405e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8163970762775339</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1.000000000042788e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8141579711116839</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2567.581</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3427.655688943062</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.91829e-08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-78.08799999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1507859628811743</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6177702821860518</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.414045305593257</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.873604743728017</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14.98246298996102</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.48188522029676</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.65505037353319</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-38450.90750279372</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-136.5790187984694</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.00000000011803e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8117315975817562</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2137.53</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8325073288827112</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3180.655157769012</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9279389315645602</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.82448e-08</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.959</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.366529369684826</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.18735328371593</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.421192071913405</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.212501709435249</v>
+      </c>
+      <c r="L13" t="n">
+        <v>51.19744776468411</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.88601646475465</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>27.0909290628736</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-70861.41668822135</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-215.5095740180307</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.00000000032086e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.81292692789788</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2026.95</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7894395541951745</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3043.951903081101</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8880564967188177</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.7658e-08</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.965</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1582738692751219</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8906564995293111</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.941097417989595</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.833620391452242</v>
+      </c>
+      <c r="L14" t="n">
+        <v>104.1681940172663</v>
+      </c>
+      <c r="M14" t="n">
+        <v>88.11393833010669</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>30.36755574589671</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-76005.01470573906</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-202.0630388738357</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8131766875636037</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1991.235</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7755295743347533</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2995.279490845884</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8738565838185154</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.74376e-08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.40900000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2857586519309162</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.202547601720134</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.466333956844432</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.08227940907242</v>
+      </c>
+      <c r="L15" t="n">
+        <v>232.4892354275298</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.03663367816085</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>29.17099614082921</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-71552.84095192752</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-203.2437479127625</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8132854401415903</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1963.62</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7647743148122689</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2964.15531326739</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8647762734247688</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.73161e-08</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.669</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3432175223911441</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.439450354451037</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.979532990486014</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.266523352283243</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.75455022508199</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>25.50332842970365</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-61388.75708529154</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-206.8168805461355</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000067729e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8133819292230474</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1925.438</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7499035083995405</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2818.069382395477</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8221564935725633</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.72919e-08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.875</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3014830486555876</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.317913560757482</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.818844475697312</v>
+      </c>
+      <c r="K17" t="n">
+        <v>388.6483740889115</v>
+      </c>
+      <c r="L17" t="n">
+        <v>29.7077924193736</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.82365294782925</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>18.01977871742763</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-42135.53109468762</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-160.7893409597841</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000131622e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8134824101818988</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1883.437</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7335453097682216</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2722.100578746029</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7941581144007508</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.72747e-08</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.03100000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.189237962850408</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6481616128829926</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.810399884598161</v>
+      </c>
+      <c r="K18" t="n">
+        <v>542.7333257581946</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.17988428401341</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.56209972795442</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.88473141078554</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-29135.04419632994</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-133.8025253182518</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000059907e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.813631498832315</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1853.945</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7220590119649586</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2625.041523480382</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7658416602193289</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.73049e-08</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.164</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7507441875963021</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.998280013819313</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.33630994868374</v>
+      </c>
+      <c r="M19" t="n">
+        <v>83.4304374773666</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.683145826163905</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-18746.46588649466</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-104.5372913316755</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000002254781e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8137990104894609</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1835.76</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7149764700704672</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2535.905388861751</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.739836675265278</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.735029999999999e-08</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.28</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.339959095832626</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.089457285798444</v>
+      </c>
+      <c r="J20" t="n">
+        <v>685.2920039241777</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.53124288802452</v>
+      </c>
+      <c r="L20" t="n">
+        <v>24.131877218872</v>
+      </c>
+      <c r="M20" t="n">
+        <v>76.36115780742992</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.121277994429851</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-7718.772412372305</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-77.34094791428288</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000144727e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8139823526587866</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1804.907</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7029601013561014</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2415.049938813725</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7045777516698065</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.73891e-08</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.383</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1080129742320917</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8061938340154953</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.199025840572133</v>
+      </c>
+      <c r="L21" t="n">
+        <v>19.64202469201001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>56.86706397072344</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.53207107049978</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-1625.861673355688</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-34.77993077212432</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000042788e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8141579711116839</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>1.000000000039001e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8183732794413768</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2113.974</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2808.271264811571</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.92013e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.962</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.149019776143625</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9020912942264847</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.922770461998279</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.947341720341467</v>
+      </c>
+      <c r="L23" t="n">
+        <v>51.69585794131459</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.82536700448766</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>26.33468020358896</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-68198.24688085998</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-71.96488029774946</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.00000000000209e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8142497834061933</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1970.511</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9321358730050605</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2974.039866523735</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.059028699894234</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.80859e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.355</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2568897387725408</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9268745436661409</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.452055849352705</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.138375679620622</v>
+      </c>
+      <c r="L24" t="n">
+        <v>217.198129114172</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.13974500407826</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>30.78913674077157</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-74739.21361180568</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-206.0704898157217</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.00000000000826e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8148335769186714</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1914.942</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9058493623857247</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2797.403288413397</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9961300118922438</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.778620000000001e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.776</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2356139946578558</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8521226995791511</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.170401919061648</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.295420168987744</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.44616200928361</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>22.42030650413371</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-52595.86030621087</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-154.9416561790958</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000172454e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8149709646965708</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1902.173</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8998090799603022</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2733.978423679943</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9735449911614531</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.76946e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.989</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5720529013685448</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.492957437111186</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.110204491806964</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>39.02498526963041</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.36506850289545</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.74139441019557</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-35860.55058012691</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-142.3631782595585</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000161538e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8150196790466799</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1868.581</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.883918629084369</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2469.310137069524</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8792990079023616</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.76566e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.14700000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3254002834221367</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.169477700922569</v>
+      </c>
+      <c r="J27" t="n">
+        <v>597.1456948160962</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.580254778789731</v>
+      </c>
+      <c r="L27" t="n">
+        <v>28.08332207557138</v>
+      </c>
+      <c r="M27" t="n">
+        <v>83.45830143272448</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.720456612515639</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-18705.0035130191</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-36.56221317909376</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000051283e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8150958478252835</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1838.446</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8696634868735376</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2578.935005477291</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9183354321187104</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.76498e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.256</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.335790419329053</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.015795867225263</v>
+      </c>
+      <c r="J28" t="n">
+        <v>825.8650751434966</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.528706184254155</v>
+      </c>
+      <c r="L28" t="n">
+        <v>23.80400877783512</v>
+      </c>
+      <c r="M28" t="n">
+        <v>79.02687767896758</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>5.157469801801515</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10140.51409358245</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-97.68384412296814</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000070569e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8151890374926833</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1817.64</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8598213601491786</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2494.826640269338</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8883852039260657</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7673e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.35599999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3752798538672363</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9513848585906586</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.639053780187206</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23.54241683501726</v>
+      </c>
+      <c r="M29" t="n">
+        <v>49.39061239768655</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.166333217617545</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-720.8756938429007</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-70.40839146289568</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000136758e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8153074815972636</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1803.327</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8530506997720879</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2397.104414860492</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8535872032366976</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.76783e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.43300000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4530159373364709</v>
+      </c>
+      <c r="I30" t="n">
+        <v>841.1356626291577</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.388960142340645</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.741530698407517</v>
+      </c>
+      <c r="L30" t="n">
+        <v>20.06123553208269</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-71.43905883096647</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-2.978154267140878</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>8953.91573369358</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-35.79370934457461</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000123253e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8154335627502167</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1772.581</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8385065284625071</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2371.723106907708</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8445491490177841</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.77146e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.505</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1725916255981519</v>
+      </c>
+      <c r="I31" t="n">
+        <v>870.6151578699885</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.712578809096599</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.283714745821711</v>
+      </c>
+      <c r="L31" t="n">
+        <v>18.94923716760701</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-66.9712138136609</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-2.352565425792377</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>7306.178078909699</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-33.7737960160166</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.23751993603162e-06</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.5000346600109846</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1767.578</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8361398957603073</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2346.593610726416</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8356007626933672</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.77324e-08</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.578</v>
+      </c>
+      <c r="H32" t="n">
+        <v>998.4767946535482</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.12038720749781</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.513404792485672</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.845466429092866</v>
+      </c>
+      <c r="L32" t="n">
+        <v>15.87043411487534</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-83.93837649205827</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-9.416925354614641</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>23491.01751536819</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-30.91871123513852</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.238171565523057e-06</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.5000167426251596</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1732.769</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.819673751900449</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2323.402446887241</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8273425989861191</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6.77558e-08</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.626</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.03657034054935201</v>
+      </c>
+      <c r="I33" t="n">
+        <v>148.9019984030941</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.392727779805485</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.769887471428</v>
+      </c>
+      <c r="L33" t="n">
+        <v>18.38891638791599</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-77.73337620723176</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-4.599284565993265</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>12203.16032319662</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-27.96157816057507</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.244512812326237e-06</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.5000455978319578</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1724.228</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8156334940732477</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2309.671252925561</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8224530449983206</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6.77394e-08</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.694</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1239.616648331558</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.732800894764317</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.591674627416158</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.459706020377286</v>
+      </c>
+      <c r="L34" t="n">
+        <v>18.40495000334692</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-83.56554620747558</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-8.867063216188333</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>21744.6586949834</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-28.92559000450228</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.248090006956523e-06</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.5000900777831849</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1709.091</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8084730464991527</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2292.260954393402</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8162533951460019</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.77677e-08</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.746</v>
+      </c>
+      <c r="H35" t="n">
+        <v>395.6789696188638</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6215045798424088</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.841838478171974</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.459130873142708</v>
+      </c>
+      <c r="L35" t="n">
+        <v>17.90725685315073</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-84.57163450077203</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>-10.52328622758085</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>25276.47871324407</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-28.59700268676397</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.252345813924323e-06</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.5001469922418816</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1695.075</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.801842879808361</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2273.817442518402</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8096858273664563</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.77724e-08</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.794</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8081998909903286</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.798960099853693</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.338672632768938</v>
+      </c>
+      <c r="L36" t="n">
+        <v>17.21761121296656</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-85.01465463204343</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-11.46382235952968</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>27172.02773873126</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-27.71306230202458</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000401e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8164955951202296</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1687.281</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7981559848891233</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2217.482542147584</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7896254788250923</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.779280000000001e-08</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.855</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6648349606413062</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.318603758969618</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.514313476228472</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5.252830268963025</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>83.04760759347671</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8.200673050021281</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-17039.26185377737</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-10.45829017682536</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000370885e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8167523881424483</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1650.533</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7807726112052465</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2235.04152118328</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7958780724600857</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.77997e-08</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.90600000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8256388811553174</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.160303032824029</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.496818193287538</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-84.87169996115252</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-11.14261904276159</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>25895.83522968648</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-25.44901165802457</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000003167629e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8170067791979968</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1647.34</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7792621858168548</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2218.491562373428</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7899847818021541</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6.78108e-08</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.968</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4320753514346465</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.218701549364747</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.211765834399351</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.329884495467545</v>
+      </c>
+      <c r="L39" t="n">
+        <v>9.778934440490884</v>
+      </c>
+      <c r="M39" t="n">
+        <v>82.85972290162067</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7.98272404014578</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-16280.10041114738</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-26.17675504112981</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000562e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.817265665735262</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1630.251</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7711783588634487</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2195.560946897655</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7818193970107701</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.782240000000001e-08</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.036</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3223028079771063</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9678492693181057</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.249760011366952</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.236942156605306</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4.943119772395903</v>
+      </c>
+      <c r="M40" t="n">
+        <v>82.79080654594047</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.905613393486639</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-15977.31195387075</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-23.95916786037492</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000001017485e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8175398446551458</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1608.278</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7607841912909051</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2178.290701190712</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7756696187029037</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.7829e-08</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.074</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1960312090680863</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8295135783392453</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.747012412154817</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.579603760540048</v>
+      </c>
+      <c r="L41" t="n">
+        <v>11.84242384179716</v>
+      </c>
+      <c r="M41" t="n">
+        <v>82.60370770065516</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.703476481506846</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-15401.09675989566</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-24.04914692751299</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000091103e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8178109244701777</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1597.924</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7558863070217514</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2154.895348667831</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7673387452520262</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6.78533e-08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.15000000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6397224988899025</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.086644017967895</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.154492310862361</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.06658635293568</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.938371026378151</v>
+      </c>
+      <c r="M42" t="n">
+        <v>82.94408448505635</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>8.079156170029071</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-16066.36387276008</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-22.1433341708539</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000644234e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8180944798607266</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1572.524</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7438710220655503</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2137.521319905845</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7611520107368502</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.78604e-08</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.19799999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2640462351083021</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9879814495532626</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.040348336571709</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.429614059870137</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.701145127078962</v>
+      </c>
+      <c r="M43" t="n">
+        <v>82.68646213065504</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7.791613631966008</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-15307.75665610602</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-23.15809030915761</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000039001e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8183732794413768</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.8855000882939355</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2010.119</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2905.401709731422</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7.01467e-08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-80.991</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4267624522103485</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.102701408200988</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.22603756486703</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.020908154463403</v>
+      </c>
+      <c r="L12" t="n">
+        <v>26.56756768901168</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.03140294551621</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>19.28335164375076</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-48579.76033740994</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-169.1362035972265</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.239915336039771e-06</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.5000510379219727</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1650.378</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.821034973551317</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2922.952327200788</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.006040685324367</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.901170000000001e-08</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.79900000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3059311414599616</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.037202371463649</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.150801384362104</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.744932581537854</v>
+      </c>
+      <c r="L13" t="n">
+        <v>101.1404161628298</v>
+      </c>
+      <c r="M13" t="n">
+        <v>88.33591378870584</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>34.42109415070531</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-74058.00108082524</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-350.2025853587556</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000119147e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8151763217885174</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1566.011</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7790638265694717</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2855.182157676176</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9827151089341485</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.871849999999999e-08</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-84.41</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.483120916666645</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9828615346316528</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.154426128745831</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.708559918519405</v>
+      </c>
+      <c r="L14" t="n">
+        <v>128.8231460712351</v>
+      </c>
+      <c r="M14" t="n">
+        <v>88.12244898454843</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>30.50530654230801</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-62609.48196086705</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-362.0276460394259</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000630069e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.81544558927731</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1517.161</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7547617827601252</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2698.723562029678</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9288641749574624</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.859489999999999e-08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-84.70099999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1099357458289902</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8962108437912022</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.302543450741216</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.637925908124771</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.30883991372554</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21.27470579155565</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-42130.12097098723</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-308.906657846813</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000059433e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8156291108516524</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1495.033</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7437534792716252</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2314.495410741291</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7966180383900321</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.85015e-08</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-84.901</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4107056104855488</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.091831608113072</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.276186969290611</v>
+      </c>
+      <c r="K16" t="n">
+        <v>714.149801440537</v>
+      </c>
+      <c r="L16" t="n">
+        <v>20.92784147262004</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.86794355697477</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13.84211807723732</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-26346.40992308271</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-140.037773027357</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000045021e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8158345403340916</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1462.876</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7277559189281828</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2129.48733263015</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7329407584147811</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.84917e-08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-85.036</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4533791679066642</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.255517993071364</v>
+      </c>
+      <c r="J17" t="n">
+        <v>538.7038099188688</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.222394279477252</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21.46772212690485</v>
+      </c>
+      <c r="M17" t="n">
+        <v>83.65473983312367</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.99275199847958</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-16231.46414564901</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-64.73196470926746</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.630490183183693e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8649589617869202</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1428.973</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7108897532932129</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2017.99581350393</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6945668844156065</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.84907e-08</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-85.169</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3586923193976381</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.14278178015128</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.266579218978331</v>
+      </c>
+      <c r="L18" t="n">
+        <v>22.29757453523105</v>
+      </c>
+      <c r="M18" t="n">
+        <v>74.7550085595128</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.669221436867571</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-5512.859662034151</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-24.50018977086359</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.562612724679226e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8714784495588442</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1406.718</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6998182694656385</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1987.081322706801</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6839265345137036</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.850089999999999e-08</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-85.262</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5757036115365949</v>
+      </c>
+      <c r="I19" t="n">
+        <v>801.2488493911743</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.628870449363887</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.160138365996004</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-4.423922731858651</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.07736582249354416</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1903.285491749938</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-23.7884878236365</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.510729130812662e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.876697387913545</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1368.721</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6809154084907411</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1960.211708994464</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6746783766351083</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.853689999999999e-08</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-85.349</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.07703503292990613</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9195799478776939</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.399311406553563</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18.42329063236644</v>
+      </c>
+      <c r="M20" t="n">
+        <v>22.16267462696134</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4073326997882372</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>835.0519703303619</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-23.53964947547115</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.467170916714975e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8812835313565098</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1358.596</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6758783932692541</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1932.065130642774</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6649907047866975</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.85614e-08</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-85.43899999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5787937372500107</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.564752128530336</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.393767800667235</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-82.14450195535515</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-7.247958175298677</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>15461.40481727142</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-21.82720004918156</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.428077054446047e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8855000882939355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 53.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1684,6 +1684,566 @@
         <v>1.000000000000467e-08</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.814230204809796</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2132.121</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3189.619437900127</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.61225e-08</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-82.506</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2343743442742951</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9244809474002373</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.000964525761355</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.51104332856812</v>
+      </c>
+      <c r="L22" t="n">
+        <v>70.38157436576104</v>
+      </c>
+      <c r="M22" t="n">
+        <v>88.05130521994244</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>29.3907932384448</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-76840.01227654665</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-215.2625026570679</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.000000000024562e-08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8126238409191623</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2067.484</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9696841783369705</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3119.328700403459</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9779626570300362</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.50528e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-83.354</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2208548089908971</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.928123848445807</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.471708876600364</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.691970342702316</v>
+      </c>
+      <c r="L23" t="n">
+        <v>223.0329343442915</v>
+      </c>
+      <c r="M23" t="n">
+        <v>88.104591265172</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>30.21769193406556</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-76671.13656891391</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-215.9079065880567</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000112659e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8127361061187315</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2021.42</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9480794007469557</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3075.982502601671</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9643728860101037</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.45043e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.764</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3485611616468593</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.032955248312594</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.327046050758152</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.148091272999795</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.69000005984699</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>24.78992790574833</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-61176.13245778675</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-221.4207763972358</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000001930405e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8128312407084796</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1972.845</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9252969226418201</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2867.093629970189</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8988826679140532</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.417e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.044</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.07252787191573158</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8703976778886107</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.110336336973675</v>
+      </c>
+      <c r="K25" t="n">
+        <v>412.004742687768</v>
+      </c>
+      <c r="L25" t="n">
+        <v>26.16149309536137</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.63989011974138</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.03220488645321</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-40546.82309079404</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-154.9100226451631</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000127682e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8129965467384119</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1933.767</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9069686945534517</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2771.46466314225</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8689013586419677</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.395500000000001e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.253</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1826653508224224</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8847209752962711</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.275462215865676</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>23.23593455563406</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.55807236546769</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.49690275613332</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-23748.45357520839</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-132.5218987392977</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000001034e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8132103789963276</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1906.642</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.89424662108764</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2657.43964217258</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8331525731866289</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.38219e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.42</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3410522827334818</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.213144910882809</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.657552267463065</v>
+      </c>
+      <c r="L27" t="n">
+        <v>21.52771544897151</v>
+      </c>
+      <c r="M27" t="n">
+        <v>74.19145667576016</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3.531914860784846</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-6398.589481440563</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-99.12457857067284</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000026023e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8134185748916484</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1859.01</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8719064255734078</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2583.316103360994</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8099135817474544</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.372e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.559</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1960542176726415</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7785697247593172</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.004897586342347</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20.06744247813327</v>
+      </c>
+      <c r="M28" t="n">
+        <v>45.98535052200963</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.035000599110234</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-420.6473918224783</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-82.02092224711146</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000016933e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8136481426912326</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1833.137</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.85977156080729</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2455.727009386663</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7699122284642774</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.364490000000001e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.68899999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.264161670762313</v>
+      </c>
+      <c r="I29" t="n">
+        <v>987.7210559440875</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.383235449790547</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.342407330990516</v>
+      </c>
+      <c r="L29" t="n">
+        <v>18.8528027549354</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-76.78609877128874</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-4.258873648679776</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>12090.36223906311</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-37.72094734345342</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000025275e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.813854540302587</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1797.168</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.842901505120957</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2424.146309226416</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7600111412734376</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.357000000000001e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.812</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.05923809152265091</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.488137063290126</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.12536331376819</v>
+      </c>
+      <c r="L30" t="n">
+        <v>16.27770217327346</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-82.43159977400823</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-7.526312565517713</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>19482.54587506013</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-37.05022364773436</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000116808e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8140451335626275</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1780.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.834990134237222</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2393.806126478762</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7504989774124008</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.35288e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.929</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3421487716741068</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6703626165829071</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.093152184851112</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.937072895074832</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.471852087896089</v>
+      </c>
+      <c r="M31" t="n">
+        <v>82.65589182473957</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7.758824819299897</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-16897.91057253166</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-35.02774451035589</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000467e-08</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.814230204809796</v>
       </c>
     </row>
@@ -1698,7 +2258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4192,6 +4752,1182 @@
         <v>1.000000000435508e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.8179412466224817</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2058.602</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2812.991613620723</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.74794e-08</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-83.813</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.4543801584321411</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9215050861285461</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.820639936678351</v>
+      </c>
+      <c r="L44" t="n">
+        <v>17.66907044972603</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-65.70931508433515</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>-2.215714894342073</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>7974.760763267007</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-106.2286164155344</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.000000001899757e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8140293700987243</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1919.579</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9324672763360764</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2638.972722285769</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.938137429741226</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.77274e-08</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-84.069</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.1037725819299271</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9180530997660872</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.662100870717262</v>
+      </c>
+      <c r="L45" t="n">
+        <v>22.8034049699186</v>
+      </c>
+      <c r="M45" t="n">
+        <v>68.25430857777698</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.507067546178828</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-4105.444491448474</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-82.60946672708087</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.000000000067825e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.814521829023492</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1887.444</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9168571681170035</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2552.1143787942</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9072598604406301</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6.78196e-08</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-84.193</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.2950387924040814</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.152452908789304</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4.227845063926751</v>
+      </c>
+      <c r="L46" t="n">
+        <v>29.61479762259942</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-33.53220000703727</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>-0.6626940644601449</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3667.350732222937</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-64.36713091428282</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.00000000001881e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8146754569102467</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1857.86</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.9024862503776833</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2463.050490149349</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.8755982343577093</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6.78706e-08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-84.27500000000001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.397687786448148</v>
+      </c>
+      <c r="I47" t="n">
+        <v>730.2180776780416</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.242644028281791</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4.393072511955302</v>
+      </c>
+      <c r="L47" t="n">
+        <v>28.82280802736893</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-66.6106641159671</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>-2.312044204314832</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>7557.655430969498</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-38.18907165460018</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.000000000615846e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8147582496974379</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1834.953</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8913587959207266</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2872.315879623764</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.021089386017288</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.92236e-08</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-83.755</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.4752620989306149</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.145349964446096</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.513414921905881</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5.239048494630296</v>
+      </c>
+      <c r="L48" t="n">
+        <v>245.8475369518642</v>
+      </c>
+      <c r="M48" t="n">
+        <v>88.00077382004689</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>28.64734623184315</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-65630.98061932939</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-231.2580607331029</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.000000001421993e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8148045760751251</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1813.986</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8811737285789092</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2900.245835091564</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.031018301316061</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.90902e-08</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-83.917</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.3492574154833302</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.288621630941714</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.438124475179138</v>
+      </c>
+      <c r="K49" t="n">
+        <v>5.115440013575289</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>87.72752814586424</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>25.19975443342456</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-56895.36174195277</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-256.1375206803079</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.000000000706327e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8148714646566978</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1773.481</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8614977543012198</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2781.327358355878</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9887435657072265</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6.90448e-08</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.009</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.06576810302047548</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.6311631942841991</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.336571488270056</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.958910848646772</v>
+      </c>
+      <c r="L50" t="n">
+        <v>14.29256977800766</v>
+      </c>
+      <c r="M50" t="n">
+        <v>87.3188431259309</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>21.35419690208468</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-47327.05424900413</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-214.3819748332485</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.000000000070395e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8149580221425988</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1765.362</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8575538156477065</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2351.693597957975</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8360115922745353</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.89808e-08</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.083</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4057434292168398</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.201337701024349</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.11348226407737</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.502531234474674</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>87.42226254303172</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>22.21215999573946</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-48963.4742857961</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-29.11721698637666</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.000000000034529e-08</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8150450636151971</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1750.148</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8501633632921759</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2617.314151392094</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9304379503724277</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.896299999999999e-08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.14700000000001</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.4170430816817713</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.104176681605816</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.184520022376841</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.475583762612138</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>87.36773313344881</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>21.75139013265514</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-47516.06608020557</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-159.7788356266835</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000004330382e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8151516295079959</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1733.737</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8421914483712732</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2602.985893314182</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9253443489523122</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6.89257e-08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.194</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.3267231200034272</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.167394342512154</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.087083520332675</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4.461072396555181</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>87.39339591616216</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>21.96583911005257</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-47657.55043392426</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-161.3941392715255</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000022788e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8152982860708917</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1708.16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8297669972146144</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2648.731150209597</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9416064866259237</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6.88937e-08</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-84.246</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.07923899417197085</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.768895196648223</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.867679425326893</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.376577545247151</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>87.14813825231388</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>20.07406396717945</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-43038.86747210872</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-189.1163911258977</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.000000000379033e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8154835925613381</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1704.881</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8281741686834073</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2582.379064388451</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9180187569292323</v>
+      </c>
+      <c r="F55" t="n">
+        <v>6.88594e-08</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-84.271</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3396301654230586</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.311910016073335</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.490980897022942</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.529336409683285</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>87.51984458494603</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>23.08725841649229</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-49505.18196301869</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-166.1730487695222</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000140426e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8156713198400521</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1677.718</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8149792917717945</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2577.266044999988</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9162011121969459</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6.88173e-08</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-84.32299999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1615815026312842</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.8175045119208715</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.901732320712659</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.24644200621972</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>87.30288265207135</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>21.2276459961044</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-44963.83211327767</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-171.8575956792299</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.000000003581505e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8159098350356051</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1676.577</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.8144250321334574</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2254.603912895018</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8014968484008455</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.84767e-08</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-84.633</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.3950762642919339</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.06886658176147</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.911590063092414</v>
+      </c>
+      <c r="L57" t="n">
+        <v>19.36734462883731</v>
+      </c>
+      <c r="M57" t="n">
+        <v>38.01064789776142</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.7815849494580217</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>243.5865482251355</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-29.0033442609415</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.000000002325532e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8161456690907986</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1654.581</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.8037401110073729</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2236.724581631821</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7951408638409826</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.84863e-08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-84.70399999999999</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.340441269891429</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.868853761696838</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.396633520415679</v>
+      </c>
+      <c r="L58" t="n">
+        <v>17.88554306623543</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-44.80258112615174</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-0.9931324171214956</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>4049.962157504391</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-28.39849443273829</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.000000000321449e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8163903954638848</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1640.194</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.796751387592162</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2377.78503759817</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8452869273000142</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6.854860000000001e-08</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-84.622</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.3350962199162855</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.011986509205258</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.14446529658988</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>18.04726569633489</v>
+      </c>
+      <c r="M59" t="n">
+        <v>84.32949883650566</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>10.07117145654693</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-19840.82956715482</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-102.7828112546911</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.000000000049537e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8166355055745373</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1629.852</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7917275898886719</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2197.547898975689</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7812138110668343</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.841669999999999e-08</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-84.845</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.5057244567015815</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.533178215643016</v>
+      </c>
+      <c r="K60" t="n">
+        <v>4.171655739701199</v>
+      </c>
+      <c r="L60" t="n">
+        <v>14.46562109079477</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-83.05180615951504</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>-8.205677411610846</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>19519.92006611818</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-26.42696082643965</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.00000000036226e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8168914354971314</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1603.71</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7790286806288927</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2177.327402683619</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7740255577516943</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6.840150000000001e-08</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-84.911</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.03489195936144598</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.769939064847059</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.977302990787715</v>
+      </c>
+      <c r="L61" t="n">
+        <v>16.7810493556606</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-81.85952438131247</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-6.990959076751902</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>16628.51016872962</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-24.9668642739332</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000000344816e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8171500330217488</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1584.776</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7698311766917547</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2164.617626444844</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7695073159705127</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6.8376e-08</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-84.94199999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.2196242105599186</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.949549549663012</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.295906355342668</v>
+      </c>
+      <c r="L62" t="n">
+        <v>16.65922768774281</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-80.39838400769001</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-5.911341075263284</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>14239.27019081562</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-27.2396491170889</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000338555e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8174073760261732</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1565.679</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.760554492806283</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2145.602215795323</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7627474626679124</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6.84333e-08</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-84.949</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1186803508687396</v>
+      </c>
+      <c r="I63" t="n">
+        <v>465.0771447642225</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.216270597819965</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.576697513857683</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-63.09955057614199</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-1.971069359565729</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>5873.204082927272</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-27.02742287050432</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000135527e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8176774955586625</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1548.366</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.7521444164534959</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2123.889530930061</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7550287461384609</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.84467e-08</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-84.998</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.1275635332353491</v>
+      </c>
+      <c r="I64" t="n">
+        <v>345.3732642513999</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.273493165225116</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4.824408559035502</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-69.62958949863966</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-2.693175278695681</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>7324.253338262391</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-24.69454050274294</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.000000000435508e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.8179412466224817</v>
       </c>
     </row>
@@ -4206,7 +5942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6700,6 +8436,1182 @@
         <v>1.000000000089927e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.8170488691685506</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2130</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2828.102594364345</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.740070000000001e-08</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-81.35899999999999</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1580295787236385</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.069636761434954</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.316777065036722</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5.359598161451792</v>
+      </c>
+      <c r="L44" t="n">
+        <v>30.40500353390687</v>
+      </c>
+      <c r="M44" t="n">
+        <v>87.40808114583562</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>22.09046401895205</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-57612.37529112391</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-75.23480821967223</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.000000000353349e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8130108639113784</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1990.322</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9344234741784037</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3048.529502085019</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.077941623532302</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.55186e-08</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-83.377</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.15597662669536</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.804448181899402</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.964976895865203</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.839260274199415</v>
+      </c>
+      <c r="L45" t="n">
+        <v>136.0127590362873</v>
+      </c>
+      <c r="M45" t="n">
+        <v>88.23777067129679</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>32.5029839488345</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-80256.39060911685</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-221.0534672194676</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.000000000160544e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8133994860999627</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1963.209</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9216943661971831</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2832.983499810754</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.001725858692727</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6.47311e-08</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-84.00700000000001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.4214937090948205</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.532845405562863</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.303454962172879</v>
+      </c>
+      <c r="K46" t="n">
+        <v>322.4729132133072</v>
+      </c>
+      <c r="L46" t="n">
+        <v>34.29149545690387</v>
+      </c>
+      <c r="M46" t="n">
+        <v>87.34884385921778</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>21.5961941619497</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-51535.25844373357</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-151.8131924648724</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.000000000092494e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8135096614813595</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1928.942</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.9056065727699532</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2722.708978417177</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.962733453815576</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6.434270000000001e-08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-84.289</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.3990947454883627</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.04718887486033</v>
+      </c>
+      <c r="J47" t="n">
+        <v>562.4458520221332</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4.348477644807508</v>
+      </c>
+      <c r="L47" t="n">
+        <v>20.25388086006874</v>
+      </c>
+      <c r="M47" t="n">
+        <v>82.20491213081031</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>7.304835606516962</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-15732.08497911205</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-118.3792067745319</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.000000000130792e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8135940824648769</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1890.948</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8877690140845069</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2598.516533908582</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9188197553676916</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.414810000000001e-08</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.47</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.1958259552771341</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7575991155664278</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.197567526764884</v>
+      </c>
+      <c r="L48" t="n">
+        <v>19.87413801614347</v>
+      </c>
+      <c r="M48" t="n">
+        <v>10.14312710119752</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.1789038273068075</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1610.646372966079</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-75.03147763158881</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.000000000141992e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8137013118070346</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1865.042</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.875606572769953</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2505.249223996454</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8858409977731178</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.399980000000001e-08</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.622</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.1630152208283609</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.686931970383128</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.216059520728476</v>
+      </c>
+      <c r="L49" t="n">
+        <v>17.3349869625258</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-82.04743849485872</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>-7.158369266781004</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>19151.64821697749</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-44.00739275724436</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.000000000168204e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.813818146844563</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1854.873</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8708323943661972</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2471.394457046254</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8738701566099775</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6.39136e-08</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.72799999999999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.293593661308444</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.062945521271499</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.316385048721868</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4.562918941348437</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>82.6468918039423</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>7.749223325492801</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-17379.51475196866</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-39.07730208790917</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.000000000858937e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8139686487906279</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1837.504</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8626779342723004</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2434.476526685094</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8608161993614929</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.385170000000001e-08</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.837</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.658982534001837</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.296508888095846</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.53453796222686</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5.806789448732688</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>83.03672626642278</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>8.187731310842549</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-18265.96631159286</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-32.54801634049272</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.000000000152786e-08</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8141281714136135</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1811.805</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8506126760563381</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2412.432404627066</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8530215309141898</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.38007e-08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.902</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.32984824405361</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.296957869396333</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.423771901983319</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.625267641330924</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>82.79216215529004</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>7.907116044594668</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-17429.16732465491</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-32.66794953416752</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000000450889e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8143032206753101</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1783.946</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8375333333333334</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2386.288366547039</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8437771569186621</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6.37627e-08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.2729264226267282</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.03906723245154</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.078088519867189</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4.024956456466199</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>82.56310257964626</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>7.660943623567285</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-16688.27394000787</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-30.25615837425676</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.00000000000717e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8144778646036316</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1757.436</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.825087323943662</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2359.809840461939</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8344145099843303</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6.373989999999999e-08</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-85.056</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.06609625557926974</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.712282329320996</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.821712515724188</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.601343412375206</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6.49972096216698</v>
+      </c>
+      <c r="M54" t="n">
+        <v>82.23306190620703</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>7.331639520279781</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-15769.0620547541</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-27.75923357900911</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.00000000052814e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8146771151968254</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1746.766</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8200779342723004</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2336.704532981253</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8262446127794946</v>
+      </c>
+      <c r="F55" t="n">
+        <v>6.3729e-08</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-85.133</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3933404076447223</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.071486841442027</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.472536317713148</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.153526135518121</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>82.50606800820141</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>7.601975363329343</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-16253.52181116075</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-26.57544568689036</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000209167e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8148807343212996</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1731.362</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8128460093896713</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2317.571615201233</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8194793285857223</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6.3716e-08</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-85.203</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.4654544198926757</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.555597913374986</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.521592688617574</v>
+      </c>
+      <c r="K56" t="n">
+        <v>84.86890251743107</v>
+      </c>
+      <c r="L56" t="n">
+        <v>22.42573878765785</v>
+      </c>
+      <c r="M56" t="n">
+        <v>82.75603483147846</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>7.867261230982351</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-16715.06673198813</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-27.03246557662692</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.000000003700823e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8151006963176228</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1710.801</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.8031929577464788</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2292.273513080904</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8105340724373981</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.36922e-08</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-85.25700000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1584921865606517</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.175420956246815</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.117284836218874</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.387009919038376</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>82.57422742846562</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>7.672550623320563</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-16117.76919812736</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-25.0834098484795</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.000000000114633e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8153244681154601</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1685.238</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7911915492957747</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2271.500433271888</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8031888368542155</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.36945e-08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-85.322</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.2133279147626263</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.8213329672743404</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.990190307023456</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.950945897487208</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>82.31096173310172</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>7.406831651867853</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-15374.21500809582</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-24.78850735269248</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.00000000642978e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8155510463640283</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1666.843</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7825553990610328</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2249.2275997659</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7953132974199774</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6.36918e-08</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-85.401</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.3419949327900979</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.857407207973485</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.003504997896159</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.842874762838925</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>82.39128011185888</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>7.4859605965272</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-15401.70994721583</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-23.66552046277957</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.00000000006778e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8157929667660343</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1640.389</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7701356807511737</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2228.23362902894</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7878899561385134</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.36817e-08</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-85.45</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1967301522627209</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.6414688705217806</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.813678695379959</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.134069767441859</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>82.07863491517216</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>7.186925443500214</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-14606.28364334215</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-23.27805834879996</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.000000001617385e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.816027122175902</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1624.023</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7624521126760562</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2207.17213402863</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7804427386852713</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6.36817e-08</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-85.50700000000001</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.1604204294412884</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.669975273499428</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.757336367665618</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.220499864432375</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>82.01049780865009</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>7.1248415104164</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-14335.54501288281</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-22.60075835923385</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000000075597e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8162853293675241</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1605.438</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7537267605633803</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2184.174878018974</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7723110478281277</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6.36643e-08</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-85.56399999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.04889432344159064</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.7731944817870466</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.675676841011736</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.281008539207324</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>82.03847132861051</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>7.150202160846341</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-14260.04878831147</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-20.80866304859228</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000010916e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8165295367997146</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1600.409</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.7513657276995306</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2168.513524727765</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7667732878747167</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6.36642e-08</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-85.619</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.6540865509207645</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.316073894541076</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.484518542411394</v>
+      </c>
+      <c r="K63" t="n">
+        <v>88.26794817049611</v>
+      </c>
+      <c r="L63" t="n">
+        <v>20.14386897762218</v>
+      </c>
+      <c r="M63" t="n">
+        <v>82.58977545658749</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>7.688830565337469</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-15288.69473552221</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-22.31062851937622</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000005916e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8167862150656783</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1576.464</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.7401239436619718</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2145.035785114358</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7584717009166648</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.366399999999999e-08</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-85.66800000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.397888051238116</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.9804175531918452</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.135804950262686</v>
+      </c>
+      <c r="K64" t="n">
+        <v>106.2490284567456</v>
+      </c>
+      <c r="L64" t="n">
+        <v>16.91258002358736</v>
+      </c>
+      <c r="M64" t="n">
+        <v>82.28823448463952</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>7.384738378755111</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-14503.35821236979</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-20.17255028545333</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.000000000089927e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.8170488691685506</v>
       </c>
     </row>
@@ -6714,7 +9626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7976,6 +10888,566 @@
         <v>1.000000000023074e-08</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.8137422252644344</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2635.925</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3459.681233894288</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.807770000000001e-08</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-77.313</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.04550344814309736</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5580797666755246</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.418663878511529</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.766487141873533</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12.40332360891977</v>
+      </c>
+      <c r="M22" t="n">
+        <v>84.79996252394287</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>10.98807051125864</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-33913.17346430986</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-115.5314203880368</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.000000000185512e-08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.811194722778607</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2242.776</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8508497017176135</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2913.116084783756</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8420186392446025</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.74003e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.084</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3245242578422265</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8567645075295822</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.780614927576904</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.002013520060604</v>
+      </c>
+      <c r="L23" t="n">
+        <v>28.80511722086773</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.39422175177619</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>21.97281024128023</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-59676.98683048016</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-59.91660437868882</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000007171e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8123093237459992</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2148.145</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8149492113774103</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3148.246781345115</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9099817493305254</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.617129999999999e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.651</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3970203475726921</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9920027205718991</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.88447485836918</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.574334311713713</v>
+      </c>
+      <c r="L24" t="n">
+        <v>70.40106069079212</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.30846062536317</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>33.86213351235661</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-88793.05783803968</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-198.7200451608683</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000011272e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8125806612880909</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2077.364</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7880967781708509</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3093.770369116862</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8942356708494934</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.55808e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.285</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.222679911297436</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8959392974463951</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.153423847076427</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.626900353123343</v>
+      </c>
+      <c r="L25" t="n">
+        <v>216.2076776011839</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.14230204396958</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>30.83154641646207</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-78445.74332960373</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-200.4009151988932</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.00000000001852e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8127328977220692</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2042.015</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7746863055663573</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2695.285028624283</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7790558859061172</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.53113e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.646</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4112659140558896</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.289500538285351</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.050059766324692</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6.326048107358549</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.86450806269114</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>26.81782363821599</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-66733.2851430825</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-53.79135226498465</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000149396e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8128842293572777</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1988.128</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7542430076728283</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2830.567301616297</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.818158411210085</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.51838e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.913</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.08243634189666081</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7861537736643299</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.134458874961983</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.302076675158259</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.64282388502379</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>17.04712313695595</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-40833.41244077377</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-131.8807726640603</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000152931e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8130514773053217</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1951.536</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.740360973851684</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2745.603046220148</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7936000054923097</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.51042e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.09699999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1230264301439157</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9809079507791082</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.129788354064586</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>23.80932746228655</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.03898339160779</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.52032484958182</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-26478.52027116762</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-112.9339259174455</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000125036e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8132137327329829</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1924.12</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.729960070942838</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2693.861410989606</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7786443978127258</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.50668e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.259</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3359268731767412</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.248549101683565</v>
+      </c>
+      <c r="J29" t="n">
+        <v>255.8684253981218</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.390230129602131</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21.97194545176075</v>
+      </c>
+      <c r="M29" t="n">
+        <v>77.96061947910844</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>4.688781213721339</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9327.408867039567</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-106.6940925262718</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.00000000026676e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8133796058844598</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1894.526</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7187328926278252</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2606.977707879221</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7535311873067432</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.50538e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.387</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4156084745312651</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.511120816133291</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.44365165026855</v>
+      </c>
+      <c r="L30" t="n">
+        <v>19.01463507159734</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-24.75953327825828</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-0.4612080787200517</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3264.069165949725</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-83.07667295031433</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000002224216e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8135550389336141</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1865.824</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7078441154433455</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2518.349302224149</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7279136810501595</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.50517e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.497</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4801716831424558</v>
+      </c>
+      <c r="I31" t="n">
+        <v>233.9765723461011</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.267426904202037</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.625076270868216</v>
+      </c>
+      <c r="L31" t="n">
+        <v>12.35932724304997</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-78.31701812655305</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-4.836050560703918</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>13687.38722258985</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-56.98337200860601</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000023074e-08</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.8137422252644344</v>
       </c>
     </row>
@@ -7990,7 +11462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10484,6 +13956,1182 @@
         <v>1.0000000000519e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.8178419656413997</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2115.868</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2806.796892493367</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.68646e-08</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-82.277</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.5224662395404657</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8596903279918767</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.779849853921197</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.451980227520143</v>
+      </c>
+      <c r="L44" t="n">
+        <v>49.58616221477614</v>
+      </c>
+      <c r="M44" t="n">
+        <v>88.10408525269288</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>30.20962105852097</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-78594.54834015714</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-74.27994813402665</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.000000000000923e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8127349193393201</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1994.89</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9428234653579525</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3033.165948476659</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.080650315877399</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.56379e-08</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-83.631</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.2299875267411905</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9765537385766515</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.435031411780813</v>
+      </c>
+      <c r="K45" t="n">
+        <v>5.15973285987229</v>
+      </c>
+      <c r="L45" t="n">
+        <v>300.4750651305349</v>
+      </c>
+      <c r="M45" t="n">
+        <v>88.00266796165695</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>28.67453559113178</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-70461.33876678524</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-215.5865585964525</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.000000002362421e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8130220748634609</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1947.371</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9203650700327243</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2764.837816330763</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.985050904012748</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6.53195e-08</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-84.038</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.2186282747559263</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.006599740111411</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.01788693361006</v>
+      </c>
+      <c r="K46" t="n">
+        <v>454.9545991151126</v>
+      </c>
+      <c r="L46" t="n">
+        <v>24.2013184924612</v>
+      </c>
+      <c r="M46" t="n">
+        <v>86.09871374465523</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>14.66367803259995</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-34260.85119992684</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-122.7968825307535</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.000000000626478e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8131284198321581</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1922.022</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.9083846440326147</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2656.926244043025</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9466043842177667</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6.51826e-08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-84.254</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.2132916421850715</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.074112447211002</v>
+      </c>
+      <c r="J47" t="n">
+        <v>701.332437404939</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.768126543859957</v>
+      </c>
+      <c r="L47" t="n">
+        <v>23.27308236530344</v>
+      </c>
+      <c r="M47" t="n">
+        <v>78.10228108292959</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>4.746276572635655</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-9528.855288247358</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-89.48785663239119</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.000000000459937e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8132293587807676</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1896.409</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8962794465439243</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2586.090468427834</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9213671553307613</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.51337e-08</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.405</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.150290940774579</v>
+      </c>
+      <c r="I48" t="n">
+        <v>997.7145411517471</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.110722426395651</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.957266499651763</v>
+      </c>
+      <c r="L48" t="n">
+        <v>21.91682704374759</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-69.68331444941018</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>-2.700933705203028</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>8611.958834524094</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-69.98620983400428</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.000000000139599e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8133959097042963</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1877.361</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.887276994595126</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2491.516362014866</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8876724812822392</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.51319e-08</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.51600000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>963.9600873800287</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.056855734435787</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.375406652913493</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4.566344750190809</v>
+      </c>
+      <c r="L49" t="n">
+        <v>15.23016660033596</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-84.17006358102275</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>-9.793916039797647</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>25634.43472015978</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-38.55498098183944</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.000000000130665e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.813588395598457</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1847.789</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8733006973970022</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2467.576692162034</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8791433034436656</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6.512e-08</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="H50" t="n">
+        <v>859.7398174529048</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9450573178502284</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.691040537328041</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.82080385896931</v>
+      </c>
+      <c r="L50" t="n">
+        <v>18.46936484995584</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-84.17881511505529</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>-9.808742199680122</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>25320.98282286995</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-38.81827452781181</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.000000002077736e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8138108417260976</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1826.097</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8630486400852984</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2435.102746947951</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8675735509970482</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.512470000000001e-08</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.68899999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2159452420063499</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.192938989066114</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.363034497360235</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.954927296358205</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.604128231278341</v>
+      </c>
+      <c r="M51" t="n">
+        <v>82.72326703628727</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>7.831453004417508</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-17405.60786540977</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-34.82964645475636</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.000000000059899e-08</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8140396719454193</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1793.836</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8478014696568973</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2404.298960198047</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8565988392776904</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.51447e-08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.785</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1539813821686699</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.7247079262969177</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.738583694049607</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.333325695998801</v>
+      </c>
+      <c r="L52" t="n">
+        <v>18.38893480456041</v>
+      </c>
+      <c r="M52" t="n">
+        <v>82.2923416967986</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>7.388721433240787</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-16172.14336217859</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-31.29192626394638</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.000000003111544e-08</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8142978253090731</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1772.736</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8378292029559501</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2378.853283124959</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8475331041897187</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6.5148e-08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.87</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0570491373193269</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.689910969529472</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.677377225359953</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.386536921154347</v>
+      </c>
+      <c r="L53" t="n">
+        <v>17.29287226173624</v>
+      </c>
+      <c r="M53" t="n">
+        <v>82.32897058829273</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>7.424430556842815</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-16097.17823252997</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-30.38932168361521</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.000000000013651e-08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.814566077357348</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1772.46</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.8376987600360704</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2353.995971239091</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8386769906774273</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6.514770000000001e-08</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-84.919</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.6926409794846983</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.378933562063089</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.876763641746646</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6.020939149231372</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>83.32285369878258</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>8.541996977027232</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-18538.40743180953</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-29.07066766962384</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.000000000019037e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8148507923077259</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1732.818</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8189631867394375</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2329.502979431457</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8299506763961411</v>
+      </c>
+      <c r="F55" t="n">
+        <v>6.51546e-08</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-85.005</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.08430795675470899</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8693581035100446</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.892837839986041</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.346879071618357</v>
+      </c>
+      <c r="L55" t="n">
+        <v>12.68698203670818</v>
+      </c>
+      <c r="M55" t="n">
+        <v>82.36623349893193</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>7.461107298526787</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-15863.74319316536</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-27.90069457430218</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000029963e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8151318643277632</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1725.676</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8155877398779131</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2304.348314525935</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8209886225429402</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6.515700000000001e-08</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-85.078</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.4538014456128008</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.270728528200539</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.588698396316813</v>
+      </c>
+      <c r="K56" t="n">
+        <v>5.264117793118986</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>83.07434174599595</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>8.232641241472745</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-17467.62813982737</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-26.46303235969253</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.000000000000496e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.815424033264312</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1699.515</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.8032235470265632</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2278.623286803886</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8118233609627923</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.51468e-08</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-85.13800000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.2807208115207647</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.9320509599010536</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.562637252825413</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.090386287698845</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>82.72754687888354</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>7.836111738943879</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-16404.74254993359</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-24.56810908166813</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.00000000008681e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8157111145780713</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1685.338</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7965232235659313</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2255.002148410209</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8034076688773227</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.51408e-08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-85.209</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.4671266925861034</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.507284691641977</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.600534237754687</v>
+      </c>
+      <c r="K58" t="n">
+        <v>5.478308216028103</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>83.11804821964103</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>8.28543693889398</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-17247.90450462234</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-23.1865363533484</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.000000003920471e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8160036355184819</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1653.387</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7814225651127575</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2235.525105579844</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7964684268956689</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6.516190000000001e-08</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-85.26900000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1924618333284086</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8569416684325321</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.891929918773218</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.760301571238977</v>
+      </c>
+      <c r="L59" t="n">
+        <v>3.464175592813915</v>
+      </c>
+      <c r="M59" t="n">
+        <v>82.54717801170752</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>7.644388848204028</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-15655.70638275604</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-24.22198273955769</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.000000001989374e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8163055244018254</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1631.66</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7711539661264315</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2209.153707003426</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7870728775964138</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.514720000000001e-08</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-85.339</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.2192511755180279</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.069544199669198</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.262563459775259</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.933499878697754</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>82.53719370838013</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>7.634045252253546</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-15475.9528379699</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-21.94800508521917</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.000000000003885e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8166031456178153</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1598.629</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.755542878856337</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2187.69409422905</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.779427289548426</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6.516729999999999e-08</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-85.413</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.01077199133467825</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.5623969768540781</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.925911354952493</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4.351554236717937</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>81.78827322698132</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>6.92947253069374</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-13788.50815160075</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-22.04325611011723</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000000080488e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8169071089293406</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1601.069</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7566960698871574</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2160.776902389359</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.769837286113664</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6.51763e-08</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-85.47799999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.3230803326864015</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.11745834705278</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.710850112336614</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4.586149634659372</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>82.94100422387126</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>8.075594846681611</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-16107.91924259595</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-19.46475045721036</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000008409e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8172039036849513</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1573.746</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.7437826934383431</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2140.440098979822</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7625917303472576</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6.517709999999999e-08</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-85.536</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.4063705285693058</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.753871161041425</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.212174743685456</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.686132008045209</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>82.68857782797556</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>7.793892956118331</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-15340.87843996631</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-20.31491346235293</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000080993e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.817526089437753</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1549.245</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.7322030485833709</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2117.344812237791</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7543633876396685</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.51972e-08</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-85.59399999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.2336070175640058</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.800136050538975</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.651468209523168</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.352616131184802</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>82.33801949786105</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>7.433304519653019</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-14424.35012449286</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-19.83166407985686</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.0000000000519e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.8178419656413997</v>
       </c>
     </row>
@@ -10498,7 +15146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11760,6 +16408,566 @@
         <v>1.000000000097333e-08</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.8136157439402472</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2657.887</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3508.690894027779</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.869109999999999e-08</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-77.56399999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.368670535899603</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.018778616827501</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.104693583118042</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.079354626743005</v>
+      </c>
+      <c r="L22" t="n">
+        <v>13.73429738230535</v>
+      </c>
+      <c r="M22" t="n">
+        <v>85.20881726625123</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>11.93070085217297</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-37181.95774067543</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-137.8472729825344</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.000000000006821e-08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8109729998283166</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2193.718</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8253616500626249</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2872.281087497064</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8186190161082691</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.773579999999999e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.58</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1428075333806495</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.112463845473705</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.433034428350365</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.253716394962943</v>
+      </c>
+      <c r="L23" t="n">
+        <v>40.92582888887071</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.68078154358194</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>24.6912849006731</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-66059.70141254611</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-60.38762120898787</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000001999e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8122060551240007</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2092.929</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.7874409258181405</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3103.428282241298</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8844974880869992</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.68213e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.824</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3060606607977521</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.26235226147249</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.621115819462565</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.907755154428532</v>
+      </c>
+      <c r="L24" t="n">
+        <v>114.5159154914054</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.24301206018693</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>32.60000687122984</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-83852.57578949022</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-200.9543207064928</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000005625e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8124861103466645</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2036.818</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7663297950590072</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3049.835382911667</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8692231590143378</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.6444e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.35599999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1474345053483577</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9258873759680991</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.281035562291068</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.711910285079546</v>
+      </c>
+      <c r="L25" t="n">
+        <v>248.6927140617362</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.06285369564924</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>29.56614394701412</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-74013.20132172584</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-201.8614941675137</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000004289e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8126131828785502</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1992.979</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.749835865858857</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3014.270517406017</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8590869382471604</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.62592e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.666</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1076303433884637</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7515393588475775</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.036844956890463</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.904420255761019</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.46376315789631</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>22.57610603262578</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-55004.40421502014</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-205.7233137859641</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000004206e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8127358872415184</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1973.083</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7423502203065818</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2796.671816160657</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7970698760956498</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.61719e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.893</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4700390066022139</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.407290598965406</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.87943595928412</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>37.20917935819942</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.66071576043031</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>17.1386704082084</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-40656.91250923482</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-132.0690246431341</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000029043e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8128738039469225</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1933.396</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7274184342675215</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2739.834111177273</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7808707560534347</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.61369e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.071</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.339361609702095</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.291496295870567</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.824557720328762</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>27.60731814421631</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.41402179195856</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.22455327739217</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-23038.00394133735</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-123.1546713698674</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000001490659e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8130346229438706</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1894.82</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7129046494452173</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2660.34576001564</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7582160527574183</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.6136e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.217</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2804282024296779</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.015041879947511</v>
+      </c>
+      <c r="J29" t="n">
+        <v>775.7964998472776</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.818694001047188</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23.11977899084852</v>
+      </c>
+      <c r="M29" t="n">
+        <v>79.19560156564935</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>5.239998094337719</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10650.116553725</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-102.8640501191705</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000002348099e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8132137836730984</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1874.924</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.705419003892942</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2508.283645289495</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7148773491443491</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.61349e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.33799999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4938244097451646</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.385171385396958</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.376952961017122</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.40035351755466</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-21.92849277603647</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-0.4025751942797905</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3080.166053908959</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-48.04208357758284</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000497801e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8134093161771635</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1840.192</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6923514807062904</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2452.475242539742</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.698971587013879</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.61646e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.455</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3549174609987874</v>
+      </c>
+      <c r="I31" t="n">
+        <v>569.5643109027702</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.156861594970937</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.68174851275586</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20.14222002904654</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-75.28400969379423</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-3.807443826322291</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>11047.61525274087</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-35.52836531138291</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000097333e-08</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.8136157439402472</v>
       </c>
     </row>
@@ -11774,7 +16982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14268,6 +19476,1182 @@
         <v>1.000000000651405e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.8163970762775339</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2112.708</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2823.078556257497</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.923909999999999e-08</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-81.149</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.02004990114195903</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8035893550285281</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.057892972621946</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4.016597909889322</v>
+      </c>
+      <c r="L44" t="n">
+        <v>29.87246431620744</v>
+      </c>
+      <c r="M44" t="n">
+        <v>87.26965780233698</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>20.96894774203287</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-54464.96287665951</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-76.52156452472195</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.000000000068123e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8126956674502752</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1977.818</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9361530320328223</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3012.414794770176</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.067067293644028</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.73327e-08</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-83.215</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.2966307433737653</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.118247964962843</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.424259341866376</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.820198313833394</v>
+      </c>
+      <c r="L45" t="n">
+        <v>144.6082177062939</v>
+      </c>
+      <c r="M45" t="n">
+        <v>88.25526778769634</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>32.82914605098639</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-80669.62904581991</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-217.7725480110171</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.0000000037225e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8130326148565623</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1933.114</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9149934586322388</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2884.376599858653</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.021713190894134</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6.688940000000001e-08</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-83.748</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.2816896166728754</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.095836514455185</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.393509347176842</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5.351802816360049</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>87.76978611891255</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>25.6777344837205</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-61257.09970802224</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-184.968175278837</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.000000000018462e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8131080792903281</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1911.507</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.9047662999335448</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2768.082903828097</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9805192624528637</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6.67038e-08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-84.01000000000001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.6222679677783994</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.606568660345036</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.024282822529965</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>38.47842985017402</v>
+      </c>
+      <c r="M47" t="n">
+        <v>86.51862535185441</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>16.43754459421508</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-37930.7087741549</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-149.4808334467918</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.000000000016909e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8131771093337712</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1870.091</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8851630230017588</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2615.707762795005</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9265444480803254</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.66288e-08</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.17700000000001</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.1964211091759708</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.8676938478135484</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.399829657718957</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>23.04510424740899</v>
+      </c>
+      <c r="M48" t="n">
+        <v>83.72447086690875</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>9.093492854115269</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-19817.84052044459</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-94.27902473251015</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.000000001365048e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.813283468521506</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1848.106</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8747569470082944</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2558.684142143844</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9063453570827458</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.66054e-08</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.309</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.3621063804832538</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.059122115772579</v>
+      </c>
+      <c r="J49" t="n">
+        <v>308.5689945119358</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.803049152916322</v>
+      </c>
+      <c r="L49" t="n">
+        <v>23.09022103703036</v>
+      </c>
+      <c r="M49" t="n">
+        <v>73.19361397958819</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>3.310826101955204</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-5842.658061940697</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-79.76205344096888</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.000000000016682e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.813419236779981</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1826.383</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8644748824731102</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2438.099999165542</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.863631652672707</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6.65822e-08</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.413</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.2268032068809779</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.186848658609656</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.813202662031709</v>
+      </c>
+      <c r="L50" t="n">
+        <v>23.36606636500764</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-40.3947259605872</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>-0.8509079992515665</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>4033.184208893517</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-35.3686300385782</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.000000000106446e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8135655042494276</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1806.192</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8549179536405409</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2405.916448864974</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8522314915864236</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.65943e-08</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.501</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2826317231400974</v>
+      </c>
+      <c r="I51" t="n">
+        <v>109.2245808686943</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.963253499786657</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.718578786218772</v>
+      </c>
+      <c r="L51" t="n">
+        <v>22.01638682371835</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-77.34308860832034</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>-4.452961774792365</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>12418.75004068838</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-30.65176389408384</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.211874841429044e-06</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.5000563328564563</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1789.047</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8468027763420216</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2386.444454284232</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8453340588041931</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.66098e-08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.58</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.2315372922585823</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.08247889450443</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.978139712027799</v>
+      </c>
+      <c r="L52" t="n">
+        <v>21.59286806384119</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-82.75673564432105</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>-7.868030589990516</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>20229.59207957098</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-31.14592012486673</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.217394013992102e-06</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.5001064745672358</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1777.308</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8412464003544265</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2365.32092582185</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8378516143587275</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6.66092e-08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.649</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.299504293409823</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.436665893629074</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4.433580754824138</v>
+      </c>
+      <c r="L53" t="n">
+        <v>11.81036933400633</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-85.45352960590004</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>-12.57579365416156</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>30999.36380989699</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-30.4642188812968</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.223676434887456e-06</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.50017299514923</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1747.524</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.827148853509335</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2344.1454603911</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8303507726326574</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6.66359e-08</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-84.724</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.8551203760470256</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.138101622679569</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.392742334305396</v>
+      </c>
+      <c r="L54" t="n">
+        <v>18.61633231269152</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-84.77772390229033</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-10.94102024882034</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>26805.84484575409</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-29.45823111706522</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.000000000125491e-08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.814220548455625</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1729.993</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.818850972306632</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2281.413081092723</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8081295067173582</v>
+      </c>
+      <c r="F55" t="n">
+        <v>6.66293e-08</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-84.788</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3556182464170944</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.9013461880111284</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.06800882454366</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.006150566351298</v>
+      </c>
+      <c r="L55" t="n">
+        <v>15.56188178462839</v>
+      </c>
+      <c r="M55" t="n">
+        <v>82.6544099938159</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>7.757242348223084</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-16552.66532110814</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-9.896565633882574</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.000000000079327e-08</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.814409419532958</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1706.314</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.807643081769937</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2301.402071894668</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8152100715700924</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6.66455e-08</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-84.834</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.09067411212974082</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.7301172327593519</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.834602953475233</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.661961976684862</v>
+      </c>
+      <c r="L56" t="n">
+        <v>16.93992091927861</v>
+      </c>
+      <c r="M56" t="n">
+        <v>82.44241758664617</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>7.537211873363496</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-15918.01141821042</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-26.51640165076174</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.000000000677394e-08</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8145926991059536</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1703.838</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.8064711261565726</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2284.20925519762</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8091199765357411</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.66379e-08</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-84.90000000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.6009831210715595</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.29942970736833</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.349827811549894</v>
+      </c>
+      <c r="K57" t="n">
+        <v>5.20014064547841</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>83.03310516837367</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>8.183433467878601</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-17260.47574685215</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-26.43644279677369</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.000000000339211e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8147965180180896</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1674.799</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7927262073130787</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2264.639341571865</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8021878585532722</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.665789999999999e-08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-84.953</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.06389166504155996</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.6513750290726031</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.893547474470874</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.477157933901059</v>
+      </c>
+      <c r="L58" t="n">
+        <v>16.06042716245127</v>
+      </c>
+      <c r="M58" t="n">
+        <v>82.60768981812728</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>7.707672668899513</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-16043.51675191806</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-25.40345952532857</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.000000000001428e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8149999008664018</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1660.743</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7860731345742051</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2246.749575460708</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7958508878474788</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6.66758e-08</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-85.01600000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1377992568548741</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8762971873701927</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.998365500248114</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.513496791042947</v>
+      </c>
+      <c r="L59" t="n">
+        <v>14.62220492627065</v>
+      </c>
+      <c r="M59" t="n">
+        <v>82.63848551794553</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>7.740276334518517</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-15988.56842160121</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-25.18433887682681</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.000000000049384e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8152138345291587</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1636.787</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7747341326865803</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2224.57180679877</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7879950070351014</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.66753e-08</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-85.06399999999999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.02655801514781532</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.7082250939778825</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.538852989939429</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.165731556708198</v>
+      </c>
+      <c r="L60" t="n">
+        <v>15.0133880260605</v>
+      </c>
+      <c r="M60" t="n">
+        <v>82.26139441669933</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>7.358813126005243</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-15020.97071327513</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-23.18743525783202</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.000000000470609e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8154361702375132</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1627.471</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7703246260249879</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2210.431550203152</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7829861996945208</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6.66815e-08</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-85.13</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.2564876377721994</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.311710739826169</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.264759311502441</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.321101042772916</v>
+      </c>
+      <c r="L61" t="n">
+        <v>10.17954756538399</v>
+      </c>
+      <c r="M61" t="n">
+        <v>82.65286823427783</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>7.755596552276817</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-15768.30395494532</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-24.64531756826295</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000001431337e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8156650072255058</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1610.084</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7620949037917214</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2186.337993423386</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7744517022302678</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6.669580000000001e-08</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-85.191</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.4041347779387621</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.9885907263208565</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.03488031465544</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.521479353136618</v>
+      </c>
+      <c r="L62" t="n">
+        <v>9.462410376914907</v>
+      </c>
+      <c r="M62" t="n">
+        <v>82.6918934023077</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>7.797467595315508</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-15725.08428232545</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-21.64959849942147</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000115598e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8159059118651605</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1599.406</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.7570407268775429</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2172.004163009984</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7693743265470334</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6.66883e-08</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-85.236</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.6769081605682188</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.081698154366681</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.477570224587692</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.420716546159114</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>82.9750707414034</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>8.115154580887042</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-16279.86037098733</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-23.08231022992618</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000122447e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8161470324889236</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1579.482</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.7476101761341368</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2150.051154652211</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7615980610551957</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.670460000000001e-08</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-85.282</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.3236187105159638</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.006439306796309</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.934430624337532</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.735956474553339</v>
+      </c>
+      <c r="L64" t="n">
+        <v>6.138305574860983</v>
+      </c>
+      <c r="M64" t="n">
+        <v>82.74285413621382</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>7.85281886875032</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-15583.04995540379</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-20.90792303976855</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.000000000651405e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.8163970762775339</v>
       </c>
     </row>
@@ -14282,7 +20666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15544,6 +21928,566 @@
         <v>1.000000000042788e-08</v>
       </c>
       <c r="AD21" t="n">
+        <v>0.8141579711116839</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2567.581</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3427.655688943062</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.91829e-08</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-78.08799999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.1507859628811743</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6177702821860518</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.414045305593257</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.873604743728017</v>
+      </c>
+      <c r="L22" t="n">
+        <v>14.98246298996102</v>
+      </c>
+      <c r="M22" t="n">
+        <v>85.48188522029676</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12.65505037353319</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-38450.90750279372</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-136.5790187984694</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.00000000011803e-08</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8117315975817562</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2137.53</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8325073288827112</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3180.655157769012</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9279389315645602</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.82448e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.959</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.366529369684826</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.18735328371593</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.421192071913405</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.212501709435249</v>
+      </c>
+      <c r="L23" t="n">
+        <v>51.19744776468411</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.88601646475465</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>27.0909290628736</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-70861.41668822135</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-215.5095740180307</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.00000000032086e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.81292692789788</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2026.95</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.7894395541951745</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3043.951903081101</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8880564967188177</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.7658e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.965</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1582738692751219</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8906564995293111</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.941097417989595</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.833620391452242</v>
+      </c>
+      <c r="L24" t="n">
+        <v>104.1681940172663</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.11393833010669</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>30.36755574589671</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-76005.01470573906</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-202.0630388738357</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8131766875636037</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1991.235</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7755295743347533</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2995.279490845884</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8738565838185154</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.74376e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.40900000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2857586519309162</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.202547601720134</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.466333956844432</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.08227940907242</v>
+      </c>
+      <c r="L25" t="n">
+        <v>232.4892354275298</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.03663367816085</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>29.17099614082921</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-71552.84095192752</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-203.2437479127625</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8132854401415903</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1963.62</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7647743148122689</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2964.15531326739</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8647762734247688</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.73161e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.669</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3432175223911441</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.439450354451037</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.979532990486014</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6.266523352283243</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.75455022508199</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>25.50332842970365</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-61388.75708529154</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-206.8168805461355</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000067729e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8133819292230474</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1925.438</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7499035083995405</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2818.069382395477</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8221564935725633</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.72919e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.875</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3014830486555876</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.317913560757482</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.818844475697312</v>
+      </c>
+      <c r="K27" t="n">
+        <v>388.6483740889115</v>
+      </c>
+      <c r="L27" t="n">
+        <v>29.7077924193736</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.82365294782925</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.01977871742763</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-42135.53109468762</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-160.7893409597841</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000131622e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8134824101818988</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1883.437</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7335453097682216</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2722.100578746029</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7941581144007508</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.72747e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.03100000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.189237962850408</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6481616128829926</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.810399884598161</v>
+      </c>
+      <c r="K28" t="n">
+        <v>542.7333257581946</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20.17988428401341</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.56209972795442</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>12.88473141078554</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-29135.04419632994</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-133.8025253182518</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000059907e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.813631498832315</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1853.945</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7220590119649586</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2625.041523480382</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7658416602193289</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.73049e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.164</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7507441875963021</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.998280013819313</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>20.33630994868374</v>
+      </c>
+      <c r="M29" t="n">
+        <v>83.4304374773666</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8.683145826163905</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-18746.46588649466</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-104.5372913316755</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000002254781e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8137990104894609</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1835.76</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7149764700704672</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2535.905388861751</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.739836675265278</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.735029999999999e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.28</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.339959095832626</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.089457285798444</v>
+      </c>
+      <c r="J30" t="n">
+        <v>685.2920039241777</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.53124288802452</v>
+      </c>
+      <c r="L30" t="n">
+        <v>24.131877218872</v>
+      </c>
+      <c r="M30" t="n">
+        <v>76.36115780742992</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>4.121277994429851</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7718.772412372305</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-77.34094791428288</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000144727e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8139823526587866</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1804.907</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7029601013561014</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2415.049938813725</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7045777516698065</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.73891e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.383</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1080129742320917</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8061938340154953</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.199025840572133</v>
+      </c>
+      <c r="L31" t="n">
+        <v>19.64202469201001</v>
+      </c>
+      <c r="M31" t="n">
+        <v>56.86706397072344</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.53207107049978</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-1625.861673355688</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-34.77993077212432</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000042788e-08</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.8141579711116839</v>
       </c>
     </row>
@@ -15558,7 +22502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18052,6 +24996,1182 @@
         <v>1.000000000039001e-08</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.8183732794413768</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2113.974</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2808.271264811571</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.92013e-08</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-81.962</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.149019776143625</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9020912942264847</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.922770461998279</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.947341720341467</v>
+      </c>
+      <c r="L44" t="n">
+        <v>51.69585794131459</v>
+      </c>
+      <c r="M44" t="n">
+        <v>87.82536700448766</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>26.33468020358896</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-68198.24688085998</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-71.96488029774946</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.00000000000209e-08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8142497834061933</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1970.511</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9321358730050605</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2974.039866523735</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.059028699894234</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.80859e-08</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-83.355</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.2568897387725408</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9268745436661409</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.452055849352705</v>
+      </c>
+      <c r="K45" t="n">
+        <v>5.138375679620622</v>
+      </c>
+      <c r="L45" t="n">
+        <v>217.198129114172</v>
+      </c>
+      <c r="M45" t="n">
+        <v>88.13974500407826</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>30.78913674077157</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-74739.21361180568</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-206.0704898157217</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.00000000000826e-08</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8148335769186714</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1914.942</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9058493623857247</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2797.403288413397</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9961300118922438</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6.778620000000001e-08</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-83.776</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.2356139946578558</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.8521226995791511</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.170401919061648</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4.295420168987744</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>87.44616200928361</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>22.42030650413371</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-52595.86030621087</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-154.9416561790958</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.000000000172454e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8149709646965708</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1902.173</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8998090799603022</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2733.978423679943</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9735449911614531</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6.76946e-08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-83.989</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5720529013685448</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.492957437111186</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.110204491806964</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>39.02498526963041</v>
+      </c>
+      <c r="M47" t="n">
+        <v>86.36506850289545</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>15.74139441019557</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-35860.55058012691</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-142.3631782595585</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.000000000161538e-08</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8150196790466799</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1868.581</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.883918629084369</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2469.310137069524</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8792990079023616</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.76566e-08</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-84.14700000000001</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3254002834221367</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.169477700922569</v>
+      </c>
+      <c r="J48" t="n">
+        <v>597.1456948160962</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4.580254778789731</v>
+      </c>
+      <c r="L48" t="n">
+        <v>28.08332207557138</v>
+      </c>
+      <c r="M48" t="n">
+        <v>83.45830143272448</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>8.720456612515639</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-18705.0035130191</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-36.56221317909376</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.000000000051283e-08</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8150958478252835</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1838.446</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8696634868735376</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2578.935005477291</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9183354321187104</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.76498e-08</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-84.256</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.335790419329053</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.015795867225263</v>
+      </c>
+      <c r="J49" t="n">
+        <v>825.8650751434966</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.528706184254155</v>
+      </c>
+      <c r="L49" t="n">
+        <v>23.80400877783512</v>
+      </c>
+      <c r="M49" t="n">
+        <v>79.02687767896758</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>5.157469801801515</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-10140.51409358245</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-97.68384412296814</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.000000000070569e-08</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8151890374926833</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1817.64</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.8598213601491786</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2494.826640269338</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8883852039260657</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6.7673e-08</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-84.35599999999999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3752798538672363</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9513848585906586</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.639053780187206</v>
+      </c>
+      <c r="L50" t="n">
+        <v>23.54241683501726</v>
+      </c>
+      <c r="M50" t="n">
+        <v>49.39061239768655</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.166333217617545</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-720.8756938429007</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-70.40839146289568</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.000000000136758e-08</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8153074815972636</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1803.327</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8530506997720879</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2397.104414860492</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8535872032366976</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.76783e-08</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-84.43300000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4530159373364709</v>
+      </c>
+      <c r="I51" t="n">
+        <v>841.1356626291577</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.388960142340645</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.741530698407517</v>
+      </c>
+      <c r="L51" t="n">
+        <v>20.06123553208269</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-71.43905883096647</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>-2.978154267140878</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>8953.91573369358</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-35.79370934457461</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.000000000123253e-08</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8154335627502167</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1772.581</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.8385065284625071</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2371.723106907708</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8445491490177841</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.77146e-08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-84.505</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1725916255981519</v>
+      </c>
+      <c r="I52" t="n">
+        <v>870.6151578699885</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.712578809096599</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.283714745821711</v>
+      </c>
+      <c r="L52" t="n">
+        <v>18.94923716760701</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-66.9712138136609</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>-2.352565425792377</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>7306.178078909699</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-33.7737960160166</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.23751993603162e-06</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.5000346600109846</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1767.578</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.8361398957603073</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2346.593610726416</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8356007626933672</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6.77324e-08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-84.578</v>
+      </c>
+      <c r="H53" t="n">
+        <v>998.4767946535482</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.12038720749781</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.513404792485672</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4.845466429092866</v>
+      </c>
+      <c r="L53" t="n">
+        <v>15.87043411487534</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-83.93837649205827</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>-9.416925354614641</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>23491.01751536819</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-30.91871123513852</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.238171565523057e-06</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.5000167426251596</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1732.769</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.819673751900449</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2323.402446887241</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8273425989861191</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6.77558e-08</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-84.626</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.03657034054935201</v>
+      </c>
+      <c r="I54" t="n">
+        <v>148.9019984030941</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.392727779805485</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.769887471428</v>
+      </c>
+      <c r="L54" t="n">
+        <v>18.38891638791599</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-77.73337620723176</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-4.599284565993265</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>12203.16032319662</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-27.96157816057507</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.244512812326237e-06</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.5000455978319578</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1724.228</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8156334940732477</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2309.671252925561</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8224530449983206</v>
+      </c>
+      <c r="F55" t="n">
+        <v>6.77394e-08</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-84.694</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1239.616648331558</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.732800894764317</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.591674627416158</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.459706020377286</v>
+      </c>
+      <c r="L55" t="n">
+        <v>18.40495000334692</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-83.56554620747558</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>-8.867063216188333</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>21744.6586949834</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-28.92559000450228</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.248090006956523e-06</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.5000900777831849</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1709.091</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8084730464991527</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2292.260954393402</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8162533951460019</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6.77677e-08</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-84.746</v>
+      </c>
+      <c r="H56" t="n">
+        <v>395.6789696188638</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.6215045798424088</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.841838478171974</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.459130873142708</v>
+      </c>
+      <c r="L56" t="n">
+        <v>17.90725685315073</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-84.57163450077203</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>-10.52328622758085</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>25276.47871324407</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-28.59700268676397</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.252345813924323e-06</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.5001469922418816</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1695.075</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.801842879808361</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2273.817442518402</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8096858273664563</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.77724e-08</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-84.794</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.8081998909903286</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.798960099853693</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.338672632768938</v>
+      </c>
+      <c r="L57" t="n">
+        <v>17.21761121296656</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-85.01465463204343</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>-11.46382235952968</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>27172.02773873126</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-27.71306230202458</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.000000000000401e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8164955951202296</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1687.281</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7981559848891233</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2217.482542147584</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7896254788250923</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.779280000000001e-08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-84.855</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.6648349606413062</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.318603758969618</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.514313476228472</v>
+      </c>
+      <c r="K58" t="n">
+        <v>5.252830268963025</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>83.04760759347671</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>8.200673050021281</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-17039.26185377737</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-10.45829017682536</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.000000000370885e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8167523881424483</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1650.533</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7807726112052465</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2235.04152118328</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7958780724600857</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6.77997e-08</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-84.90600000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8256388811553174</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.160303032824029</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4.496818193287538</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-84.87169996115252</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>-11.14261904276159</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>25895.83522968648</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-25.44901165802457</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.000000003167629e-08</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8170067791979968</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1647.34</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7792621858168548</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2218.491562373428</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7899847818021541</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.78108e-08</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-84.968</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.4320753514346465</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.218701549364747</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.211765834399351</v>
+      </c>
+      <c r="K60" t="n">
+        <v>4.329884495467545</v>
+      </c>
+      <c r="L60" t="n">
+        <v>9.778934440490884</v>
+      </c>
+      <c r="M60" t="n">
+        <v>82.85972290162067</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>7.98272404014578</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-16280.10041114738</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-26.17675504112981</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.000000000000562e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.817265665735262</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1630.251</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7711783588634487</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2195.560946897655</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7818193970107701</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6.782240000000001e-08</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-85.036</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.3223028079771063</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9678492693181057</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.249760011366952</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4.236942156605306</v>
+      </c>
+      <c r="L61" t="n">
+        <v>4.943119772395903</v>
+      </c>
+      <c r="M61" t="n">
+        <v>82.79080654594047</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>7.905613393486639</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-15977.31195387075</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-23.95916786037492</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.000000001017485e-08</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8175398446551458</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1608.278</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7607841912909051</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2178.290701190712</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7756696187029037</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6.7829e-08</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-85.074</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.1960312090680863</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.8295135783392453</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.747012412154817</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.579603760540048</v>
+      </c>
+      <c r="L62" t="n">
+        <v>11.84242384179716</v>
+      </c>
+      <c r="M62" t="n">
+        <v>82.60370770065516</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>7.703476481506846</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-15401.09675989566</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-24.04914692751299</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.000000000091103e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8178109244701777</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1597.924</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.7558863070217514</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2154.895348667831</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7673387452520262</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6.78533e-08</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-85.15000000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.6397224988899025</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.086644017967895</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.154492310862361</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.06658635293568</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.938371026378151</v>
+      </c>
+      <c r="M63" t="n">
+        <v>82.94408448505635</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>8.079156170029071</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-16066.36387276008</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-22.1433341708539</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.000000000644234e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8180944798607266</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1572.524</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.7438710220655503</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2137.521319905845</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7611520107368502</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.78604e-08</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-85.19799999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.2640462351083021</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.9879814495532626</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.040348336571709</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.429614059870137</v>
+      </c>
+      <c r="L64" t="n">
+        <v>7.701145127078962</v>
+      </c>
+      <c r="M64" t="n">
+        <v>82.68646213065504</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>7.791613631966008</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-15307.75665610602</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-23.15809030915761</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.000000000039001e-08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>0.8183732794413768</v>
       </c>
     </row>
@@ -18066,7 +26186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19331,6 +27451,566 @@
         <v>0.8855000882939355</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2010.119</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2905.401709731422</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7.01467e-08</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-80.991</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4267624522103485</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.102701408200988</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.22603756486703</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.020908154463403</v>
+      </c>
+      <c r="L22" t="n">
+        <v>26.56756768901168</v>
+      </c>
+      <c r="M22" t="n">
+        <v>87.03140294551621</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>19.28335164375076</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-48579.76033740994</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-169.1362035972265</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.239915336039771e-06</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.5000510379219727</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1650.378</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.821034973551317</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2922.952327200788</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.006040685324367</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.901170000000001e-08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-83.79900000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3059311414599616</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.037202371463649</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.150801384362104</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.744932581537854</v>
+      </c>
+      <c r="L23" t="n">
+        <v>101.1404161628298</v>
+      </c>
+      <c r="M23" t="n">
+        <v>88.33591378870584</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>34.42109415070531</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-74058.00108082524</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-350.2025853587556</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000119147e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8151763217885174</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1566.011</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.7790638265694717</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2855.182157676176</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9827151089341485</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.871849999999999e-08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-84.41</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.483120916666645</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9828615346316528</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.154426128745831</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.708559918519405</v>
+      </c>
+      <c r="L24" t="n">
+        <v>128.8231460712351</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.12244898454843</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>30.50530654230801</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-62609.48196086705</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-362.0276460394259</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000630069e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.81544558927731</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1517.161</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7547617827601252</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2698.723562029678</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9288641749574624</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.859489999999999e-08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-84.70099999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1099357458289902</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8962108437912022</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.302543450741216</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.637925908124771</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.30883991372554</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21.27470579155565</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-42130.12097098723</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-308.906657846813</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000059433e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8156291108516524</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1495.033</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7437534792716252</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2314.495410741291</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7966180383900321</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.85015e-08</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.901</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4107056104855488</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.091831608113072</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.276186969290611</v>
+      </c>
+      <c r="K26" t="n">
+        <v>714.149801440537</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.92784147262004</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.86794355697477</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.84211807723732</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-26346.40992308271</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-140.037773027357</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000045021e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8158345403340916</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1462.876</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7277559189281828</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2129.48733263015</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7329407584147811</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.84917e-08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-85.036</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4533791679066642</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.255517993071364</v>
+      </c>
+      <c r="J27" t="n">
+        <v>538.7038099188688</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.222394279477252</v>
+      </c>
+      <c r="L27" t="n">
+        <v>21.46772212690485</v>
+      </c>
+      <c r="M27" t="n">
+        <v>83.65473983312367</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.99275199847958</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-16231.46414564901</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-64.73196470926746</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.630490183183693e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8649589617869202</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1428.973</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7108897532932129</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2017.99581350393</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6945668844156065</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.84907e-08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-85.169</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3586923193976381</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.14278178015128</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.266579218978331</v>
+      </c>
+      <c r="L28" t="n">
+        <v>22.29757453523105</v>
+      </c>
+      <c r="M28" t="n">
+        <v>74.7550085595128</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>3.669221436867571</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-5512.859662034151</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-24.50018977086359</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.562612724679226e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8714784495588442</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1406.718</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6998182694656385</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1987.081322706801</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6839265345137036</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.850089999999999e-08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-85.262</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5757036115365949</v>
+      </c>
+      <c r="I29" t="n">
+        <v>801.2488493911743</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.628870449363887</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.160138365996004</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-4.423922731858651</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.07736582249354416</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1903.285491749938</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-23.7884878236365</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.510729130812662e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.876697387913545</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1368.721</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6809154084907411</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1960.211708994464</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6746783766351083</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.853689999999999e-08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-85.349</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.07703503292990613</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9195799478776939</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.399311406553563</v>
+      </c>
+      <c r="L30" t="n">
+        <v>18.42329063236644</v>
+      </c>
+      <c r="M30" t="n">
+        <v>22.16267462696134</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.4073326997882372</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>835.0519703303619</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-23.53964947547115</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.467170916714975e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8812835313565098</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1358.596</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6758783932692541</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1932.065130642774</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6649907047866975</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.85614e-08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-85.43899999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5787937372500107</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.564752128530336</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.393767800667235</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-82.14450195535515</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-7.247958175298677</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>15461.40481727142</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-21.82720004918156</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.428077054446047e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8855000882939355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
